--- a/gratis/archivos/cronograma-tesis/Cronograma_de_Tesis_MixShopDigital_EJEMPLO.xlsx
+++ b/gratis/archivos/cronograma-tesis/Cronograma_de_Tesis_MixShopDigital_EJEMPLO.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="169" formatCode="0;-0;&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="0%;-0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,12 @@
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B2A7A"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -217,7 +223,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -244,20 +250,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7A00"/>
+        <bgColor rgb="00FF7A00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB800"/>
+        <bgColor rgb="00FFB800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000094FB"/>
+        <bgColor rgb="000094FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CC"/>
         <bgColor rgb="00FFF3CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3EF"/>
-        <bgColor rgb="00EEF3EF"/>
+        <fgColor rgb="002ECC40"/>
+        <bgColor rgb="002ECC40"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="008727E2"/>
+        <bgColor rgb="008727E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3EF"/>
+        <bgColor rgb="00EEF3EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -327,12 +363,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -341,180 +378,185 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="20" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="21" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="23" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="26" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,6 +962,151 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1231,125 +1418,142 @@
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>CRONOGRAMA DE TESIS</t>
         </is>
       </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tu tesis, de un vistazo</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>El panel se arma solo con lo que anotás en CRONOGRAMA y REUNIONES. No hace falta escribir nada acá.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>+ Cronograma</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Reuniones</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Ajustes</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Ayuda</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="10">
+      <c r="B6" s="16">
         <f>"Trabajo: "&amp;TituloTesis&amp;IF(Estudiante="","","   ·   Estudiante: "&amp;Estudiante)&amp;IF(Tutor="","","   ·   Tutor: "&amp;Tutor)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>AVANCE GENERAL</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>DÍAS PARA TU ENTREGA</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>TAREAS COMPLETADAS</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>TAREAS ATRASADAS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="15">
+      <c r="B9" s="21">
         <f>IFERROR(SUMPRODUCT(((CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0)</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="22">
         <f>IF(N(FechaFin)=0,"-",FechaFin-TODAY())</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="23">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,"Completada")&amp;" de "&amp;COUNTA(CRONOGRAMA!$D$7:$D$46)</f>
         <v/>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="24">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,"Atrasada")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>ponderado por duración de cada tarea</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>negativo = fecha vencida</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>tareas</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr">
         <is>
           <t>pasó su fecha sin completarse</t>
         </is>
@@ -1357,388 +1561,388 @@
     </row>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="23">
+      <c r="B12" s="29">
         <f>IF(COUNTA(CRONOGRAMA!$D$7:$D$46)=0,"Cargá tus tareas en la hoja CRONOGRAMA para ver tu panel.",IF(K9&gt;0,"⚠ Tenés "&amp;K9&amp;" tarea(s) atrasada(s). Revisalas en CRONOGRAMA.",IF(D14+0.1&lt;D13,"⚠ Tu avance está por detrás del tiempo transcurrido. Conviene ajustar el plan.","✔ Vas bien: tu avance acompaña el tiempo transcurrido.")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Tiempo transcurrido</t>
         </is>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="31">
         <f>IF(OR(N(FechaIni)=0,N(FechaFin)&lt;=N(FechaIni)),0,MAX(0,MIN(1,(TODAY()-FechaIni)/(FechaFin-FechaIni))))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Avance real</t>
         </is>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="31">
         <f>B9</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>AVANCE POR ETAPA</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Tareas</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Avance</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>Atrasadas</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="28">
+      <c r="B18" s="34">
         <f>IF('AJUSTES'!$B$15="","",'AJUSTES'!$B$15)</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="35">
         <f>IF(B18="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B18,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="36">
         <f>IF(B18="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B18)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B18)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="35">
         <f>IF(B18="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B18,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="28">
+      <c r="B19" s="34">
         <f>IF('AJUSTES'!$B$16="","",'AJUSTES'!$B$16)</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="35">
         <f>IF(B19="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B19,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="36">
         <f>IF(B19="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B19)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B19)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="35">
         <f>IF(B19="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B19,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="28">
+      <c r="B20" s="34">
         <f>IF('AJUSTES'!$B$17="","",'AJUSTES'!$B$17)</f>
         <v/>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="35">
         <f>IF(B20="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B20,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="36">
         <f>IF(B20="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B20)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B20)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="35">
         <f>IF(B20="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B20,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="28">
+      <c r="B21" s="34">
         <f>IF('AJUSTES'!$B$18="","",'AJUSTES'!$B$18)</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="35">
         <f>IF(B21="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B21,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="36">
         <f>IF(B21="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B21)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B21)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="35">
         <f>IF(B21="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B21,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="28">
+      <c r="B22" s="34">
         <f>IF('AJUSTES'!$B$19="","",'AJUSTES'!$B$19)</f>
         <v/>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="35">
         <f>IF(B22="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B22,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="36">
         <f>IF(B22="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B22)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B22)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="35">
         <f>IF(B22="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B22,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="28">
+      <c r="B23" s="34">
         <f>IF('AJUSTES'!$B$20="","",'AJUSTES'!$B$20)</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="35">
         <f>IF(B23="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B23,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="36">
         <f>IF(B23="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B23)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B23)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="35">
         <f>IF(B23="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B23,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="28">
+      <c r="B24" s="34">
         <f>IF('AJUSTES'!$B$21="","",'AJUSTES'!$B$21)</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="35">
         <f>IF(B24="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B24,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="36">
         <f>IF(B24="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B24)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B24)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="35">
         <f>IF(B24="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B24,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="28">
+      <c r="B25" s="34">
         <f>IF('AJUSTES'!$B$22="","",'AJUSTES'!$B$22)</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="35">
         <f>IF(B25="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B25,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="36">
         <f>IF(B25="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B25)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B25)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="35">
         <f>IF(B25="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B25,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="28">
+      <c r="B26" s="34">
         <f>IF('AJUSTES'!$B$23="","",'AJUSTES'!$B$23)</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="35">
         <f>IF(B26="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B26,CRONOGRAMA!$D$7:$D$46,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="36">
         <f>IF(B26="",0,IFERROR(SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B26)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))*CRONOGRAMA!$G$7:$G$46)/SUMPRODUCT(((CRONOGRAMA!$C$7:$C$46=B26)*(CRONOGRAMA!$D$7:$D$46&lt;&gt;"")*(CRONOGRAMA!$F$7:$F$46-CRONOGRAMA!$E$7:$E$46+1))),0))</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="35">
         <f>IF(B26="",0,COUNTIFS(CRONOGRAMA!$C$7:$C$46,B26,CRONOGRAMA!$H$7:$H$46,"Atrasada"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="38">
         <f>SUM(D18:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="39">
         <f>B9</f>
         <v/>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="38">
         <f>SUM(F18:F26)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>ESTADO DE LAS TAREAS</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>Tareas</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Completada</t>
         </is>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="42">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,B31)</f>
         <v/>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="43">
         <f>IF($D$35=0,0,D31/$D$35)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="42">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,B32)</f>
         <v/>
       </c>
-      <c r="E32" s="37">
+      <c r="E32" s="43">
         <f>IF($D$35=0,0,D32/$D$35)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>Por empezar</t>
         </is>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="42">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,B33)</f>
         <v/>
       </c>
-      <c r="E33" s="37">
+      <c r="E33" s="43">
         <f>IF($D$35=0,0,D33/$D$35)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>Atrasada</t>
         </is>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="42">
         <f>COUNTIF(CRONOGRAMA!$H$7:$H$46,B34)</f>
         <v/>
       </c>
-      <c r="E34" s="37">
+      <c r="E34" s="43">
         <f>IF($D$35=0,0,D34/$D$35)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="44">
         <f>SUM(D31:D34)</f>
         <v/>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="45">
         <f>SUM(E31:E34)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>ÚLTIMA REUNIÓN CON TU TUTOR</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>PRÓXIMA REUNIÓN</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="40">
+      <c r="B38" s="46">
         <f>IF(COUNTIFS(REUNIONES!$B$7:$B$66,"&gt;0",REUNIONES!$B$7:$B$66,"&lt;="&amp;TODAY())=0,"-",SUMPRODUCT(MAX((REUNIONES!$B$7:$B$66&lt;=TODAY())*REUNIONES!$B$7:$B$66)))</f>
         <v/>
       </c>
-      <c r="E38" s="41">
+      <c r="E38" s="47">
         <f>IFERROR(SMALL(REUNIONES!$B$7:$B$66,COUNTIF(REUNIONES!$B$7:$B$66,"&lt;"&amp;TODAY())+1),"-")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>según REUNIONES</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>agendada en REUNIONES</t>
         </is>
       </c>
     </row>
     <row r="46" ht="8" customHeight="1">
-      <c r="B46" s="42" t="n"/>
+      <c r="B46" s="48" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B47" s="49" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="50" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY  →  mixshopdigital.com.py</t>
         </is>
@@ -1746,7 +1950,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="B962"/>
-  <mergeCells count="56">
+  <mergeCells count="55">
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="B48:M48"/>
     <mergeCell ref="B25:C25"/>
@@ -1789,7 +1993,6 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B3:M3"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="E39:G39"/>
@@ -1942,3416 +2145,3447 @@
     <col width="2.6" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>CRONOGRAMA</t>
         </is>
       </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tu plan, semana a semana</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="9" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="11" t="n"/>
+      <c r="T3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="51" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Una fila por tarea. Completá las celdas amarillas: el estado y el diagrama de barras se arman solos. Deslizá hacia la derecha para ver las semanas.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>←  Volver al PANEL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="D6" s="46" t="inlineStr">
+      <c r="D6" s="52" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>Inicio</t>
         </is>
       </c>
-      <c r="F6" s="46" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>Fin</t>
         </is>
       </c>
-      <c r="G6" s="46" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>Avance</t>
         </is>
       </c>
-      <c r="H6" s="46" t="inlineStr">
+      <c r="H6" s="52" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I6" s="46" t="inlineStr">
+      <c r="I6" s="52" t="inlineStr">
         <is>
           <t>Días que faltan</t>
         </is>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="53">
         <f>IF(N(FechaIni)=0,"",FechaIni-WEEKDAY(FechaIni,2)+1)</f>
         <v/>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="53">
         <f>IF(J6="","",J6+7)</f>
         <v/>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="53">
         <f>IF(K6="","",K6+7)</f>
         <v/>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="53">
         <f>IF(L6="","",L6+7)</f>
         <v/>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="53">
         <f>IF(M6="","",M6+7)</f>
         <v/>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="53">
         <f>IF(N6="","",N6+7)</f>
         <v/>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="53">
         <f>IF(O6="","",O6+7)</f>
         <v/>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="53">
         <f>IF(P6="","",P6+7)</f>
         <v/>
       </c>
-      <c r="R6" s="47">
+      <c r="R6" s="53">
         <f>IF(Q6="","",Q6+7)</f>
         <v/>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="53">
         <f>IF(R6="","",R6+7)</f>
         <v/>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="53">
         <f>IF(S6="","",S6+7)</f>
         <v/>
       </c>
-      <c r="U6" s="47">
+      <c r="U6" s="53">
         <f>IF(T6="","",T6+7)</f>
         <v/>
       </c>
-      <c r="V6" s="47">
+      <c r="V6" s="53">
         <f>IF(U6="","",U6+7)</f>
         <v/>
       </c>
-      <c r="W6" s="47">
+      <c r="W6" s="53">
         <f>IF(V6="","",V6+7)</f>
         <v/>
       </c>
-      <c r="X6" s="47">
+      <c r="X6" s="53">
         <f>IF(W6="","",W6+7)</f>
         <v/>
       </c>
-      <c r="Y6" s="47">
+      <c r="Y6" s="53">
         <f>IF(X6="","",X6+7)</f>
         <v/>
       </c>
-      <c r="Z6" s="47">
+      <c r="Z6" s="53">
         <f>IF(Y6="","",Y6+7)</f>
         <v/>
       </c>
-      <c r="AA6" s="47">
+      <c r="AA6" s="53">
         <f>IF(Z6="","",Z6+7)</f>
         <v/>
       </c>
-      <c r="AB6" s="47">
+      <c r="AB6" s="53">
         <f>IF(AA6="","",AA6+7)</f>
         <v/>
       </c>
-      <c r="AC6" s="47">
+      <c r="AC6" s="53">
         <f>IF(AB6="","",AB6+7)</f>
         <v/>
       </c>
-      <c r="AD6" s="47">
+      <c r="AD6" s="53">
         <f>IF(AC6="","",AC6+7)</f>
         <v/>
       </c>
-      <c r="AE6" s="47">
+      <c r="AE6" s="53">
         <f>IF(AD6="","",AD6+7)</f>
         <v/>
       </c>
-      <c r="AF6" s="47">
+      <c r="AF6" s="53">
         <f>IF(AE6="","",AE6+7)</f>
         <v/>
       </c>
-      <c r="AG6" s="47">
+      <c r="AG6" s="53">
         <f>IF(AF6="","",AF6+7)</f>
         <v/>
       </c>
-      <c r="AH6" s="47">
+      <c r="AH6" s="53">
         <f>IF(AG6="","",AG6+7)</f>
         <v/>
       </c>
-      <c r="AI6" s="47">
+      <c r="AI6" s="53">
         <f>IF(AH6="","",AH6+7)</f>
         <v/>
       </c>
-      <c r="AJ6" s="47">
+      <c r="AJ6" s="53">
         <f>IF(AI6="","",AI6+7)</f>
         <v/>
       </c>
-      <c r="AK6" s="47">
+      <c r="AK6" s="53">
         <f>IF(AJ6="","",AJ6+7)</f>
         <v/>
       </c>
-      <c r="AL6" s="47">
+      <c r="AL6" s="53">
         <f>IF(AK6="","",AK6+7)</f>
         <v/>
       </c>
-      <c r="AM6" s="47">
+      <c r="AM6" s="53">
         <f>IF(AL6="","",AL6+7)</f>
         <v/>
       </c>
-      <c r="AN6" s="47">
+      <c r="AN6" s="53">
         <f>IF(AM6="","",AM6+7)</f>
         <v/>
       </c>
-      <c r="AO6" s="47">
+      <c r="AO6" s="53">
         <f>IF(AN6="","",AN6+7)</f>
         <v/>
       </c>
-      <c r="AP6" s="47">
+      <c r="AP6" s="53">
         <f>IF(AO6="","",AO6+7)</f>
         <v/>
       </c>
-      <c r="AQ6" s="47">
+      <c r="AQ6" s="53">
         <f>IF(AP6="","",AP6+7)</f>
         <v/>
       </c>
-      <c r="AR6" s="47">
+      <c r="AR6" s="53">
         <f>IF(AQ6="","",AQ6+7)</f>
         <v/>
       </c>
-      <c r="AS6" s="47">
+      <c r="AS6" s="53">
         <f>IF(AR6="","",AR6+7)</f>
         <v/>
       </c>
-      <c r="AT6" s="47">
+      <c r="AT6" s="53">
         <f>IF(AS6="","",AS6+7)</f>
         <v/>
       </c>
-      <c r="AU6" s="47">
+      <c r="AU6" s="53">
         <f>IF(AT6="","",AT6+7)</f>
         <v/>
       </c>
-      <c r="AV6" s="47">
+      <c r="AV6" s="53">
         <f>IF(AU6="","",AU6+7)</f>
         <v/>
       </c>
-      <c r="AW6" s="47">
+      <c r="AW6" s="53">
         <f>IF(AV6="","",AV6+7)</f>
         <v/>
       </c>
-      <c r="AX6" s="47">
+      <c r="AX6" s="53">
         <f>IF(AW6="","",AW6+7)</f>
         <v/>
       </c>
-      <c r="AY6" s="47">
+      <c r="AY6" s="53">
         <f>IF(AX6="","",AX6+7)</f>
         <v/>
       </c>
-      <c r="AZ6" s="47">
+      <c r="AZ6" s="53">
         <f>IF(AY6="","",AY6+7)</f>
         <v/>
       </c>
-      <c r="BA6" s="47">
+      <c r="BA6" s="53">
         <f>IF(AZ6="","",AZ6+7)</f>
         <v/>
       </c>
-      <c r="BB6" s="47">
+      <c r="BB6" s="53">
         <f>IF(BA6="","",BA6+7)</f>
         <v/>
       </c>
-      <c r="BC6" s="47">
+      <c r="BC6" s="53">
         <f>IF(BB6="","",BB6+7)</f>
         <v/>
       </c>
-      <c r="BD6" s="47">
+      <c r="BD6" s="53">
         <f>IF(BC6="","",BC6+7)</f>
         <v/>
       </c>
-      <c r="BE6" s="47">
+      <c r="BE6" s="53">
         <f>IF(BD6="","",BD6+7)</f>
         <v/>
       </c>
-      <c r="BF6" s="47">
+      <c r="BF6" s="53">
         <f>IF(BE6="","",BE6+7)</f>
         <v/>
       </c>
-      <c r="BG6" s="47">
+      <c r="BG6" s="53">
         <f>IF(BF6="","",BF6+7)</f>
         <v/>
       </c>
-      <c r="BH6" s="47">
+      <c r="BH6" s="53">
         <f>IF(BG6="","",BG6+7)</f>
         <v/>
       </c>
-      <c r="BI6" s="47">
+      <c r="BI6" s="53">
         <f>IF(BH6="","",BH6+7)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="B7" s="48">
+      <c r="B7" s="54">
         <f>IF(D7="","",1)</f>
         <v/>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Tema y proyecto</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>Elegir el tema y definir el problema</t>
         </is>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="56" t="n">
         <v>46174</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="56" t="n">
         <v>46193</v>
       </c>
-      <c r="G7" s="51" t="n">
+      <c r="G7" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="58">
         <f>IF(D7="","",IF(N(G7)&gt;=1,"Completada",IF(AND(N(F7)&gt;0,F7&lt;TODAY()),"Atrasada",IF(AND(N(E7)&gt;0,E7&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="59">
         <f>IF(OR(D7="",N(F7)=0,N(G7)&gt;=1),"",F7-TODAY())</f>
         <v/>
       </c>
-      <c r="J7" s="54" t="n"/>
-      <c r="K7" s="54" t="n"/>
-      <c r="L7" s="54" t="n"/>
-      <c r="M7" s="54" t="n"/>
-      <c r="N7" s="54" t="n"/>
-      <c r="O7" s="54" t="n"/>
-      <c r="P7" s="54" t="n"/>
-      <c r="Q7" s="54" t="n"/>
-      <c r="R7" s="54" t="n"/>
-      <c r="S7" s="54" t="n"/>
-      <c r="T7" s="54" t="n"/>
-      <c r="U7" s="54" t="n"/>
-      <c r="V7" s="54" t="n"/>
-      <c r="W7" s="54" t="n"/>
-      <c r="X7" s="54" t="n"/>
-      <c r="Y7" s="54" t="n"/>
-      <c r="Z7" s="54" t="n"/>
-      <c r="AA7" s="54" t="n"/>
-      <c r="AB7" s="54" t="n"/>
-      <c r="AC7" s="54" t="n"/>
-      <c r="AD7" s="54" t="n"/>
-      <c r="AE7" s="54" t="n"/>
-      <c r="AF7" s="54" t="n"/>
-      <c r="AG7" s="54" t="n"/>
-      <c r="AH7" s="54" t="n"/>
-      <c r="AI7" s="54" t="n"/>
-      <c r="AJ7" s="54" t="n"/>
-      <c r="AK7" s="54" t="n"/>
-      <c r="AL7" s="54" t="n"/>
-      <c r="AM7" s="54" t="n"/>
-      <c r="AN7" s="54" t="n"/>
-      <c r="AO7" s="54" t="n"/>
-      <c r="AP7" s="54" t="n"/>
-      <c r="AQ7" s="54" t="n"/>
-      <c r="AR7" s="54" t="n"/>
-      <c r="AS7" s="54" t="n"/>
-      <c r="AT7" s="54" t="n"/>
-      <c r="AU7" s="54" t="n"/>
-      <c r="AV7" s="54" t="n"/>
-      <c r="AW7" s="54" t="n"/>
-      <c r="AX7" s="54" t="n"/>
-      <c r="AY7" s="54" t="n"/>
-      <c r="AZ7" s="54" t="n"/>
-      <c r="BA7" s="54" t="n"/>
-      <c r="BB7" s="54" t="n"/>
-      <c r="BC7" s="54" t="n"/>
-      <c r="BD7" s="54" t="n"/>
-      <c r="BE7" s="54" t="n"/>
-      <c r="BF7" s="54" t="n"/>
-      <c r="BG7" s="54" t="n"/>
-      <c r="BH7" s="54" t="n"/>
-      <c r="BI7" s="54" t="n"/>
+      <c r="J7" s="60" t="n"/>
+      <c r="K7" s="60" t="n"/>
+      <c r="L7" s="60" t="n"/>
+      <c r="M7" s="60" t="n"/>
+      <c r="N7" s="60" t="n"/>
+      <c r="O7" s="60" t="n"/>
+      <c r="P7" s="60" t="n"/>
+      <c r="Q7" s="60" t="n"/>
+      <c r="R7" s="60" t="n"/>
+      <c r="S7" s="60" t="n"/>
+      <c r="T7" s="60" t="n"/>
+      <c r="U7" s="60" t="n"/>
+      <c r="V7" s="60" t="n"/>
+      <c r="W7" s="60" t="n"/>
+      <c r="X7" s="60" t="n"/>
+      <c r="Y7" s="60" t="n"/>
+      <c r="Z7" s="60" t="n"/>
+      <c r="AA7" s="60" t="n"/>
+      <c r="AB7" s="60" t="n"/>
+      <c r="AC7" s="60" t="n"/>
+      <c r="AD7" s="60" t="n"/>
+      <c r="AE7" s="60" t="n"/>
+      <c r="AF7" s="60" t="n"/>
+      <c r="AG7" s="60" t="n"/>
+      <c r="AH7" s="60" t="n"/>
+      <c r="AI7" s="60" t="n"/>
+      <c r="AJ7" s="60" t="n"/>
+      <c r="AK7" s="60" t="n"/>
+      <c r="AL7" s="60" t="n"/>
+      <c r="AM7" s="60" t="n"/>
+      <c r="AN7" s="60" t="n"/>
+      <c r="AO7" s="60" t="n"/>
+      <c r="AP7" s="60" t="n"/>
+      <c r="AQ7" s="60" t="n"/>
+      <c r="AR7" s="60" t="n"/>
+      <c r="AS7" s="60" t="n"/>
+      <c r="AT7" s="60" t="n"/>
+      <c r="AU7" s="60" t="n"/>
+      <c r="AV7" s="60" t="n"/>
+      <c r="AW7" s="60" t="n"/>
+      <c r="AX7" s="60" t="n"/>
+      <c r="AY7" s="60" t="n"/>
+      <c r="AZ7" s="60" t="n"/>
+      <c r="BA7" s="60" t="n"/>
+      <c r="BB7" s="60" t="n"/>
+      <c r="BC7" s="60" t="n"/>
+      <c r="BD7" s="60" t="n"/>
+      <c r="BE7" s="60" t="n"/>
+      <c r="BF7" s="60" t="n"/>
+      <c r="BG7" s="60" t="n"/>
+      <c r="BH7" s="60" t="n"/>
+      <c r="BI7" s="60" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="B8" s="48">
+      <c r="B8" s="54">
         <f>IF(D8="","",2)</f>
         <v/>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
         <is>
           <t>Tema y proyecto</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>Redactar el anteproyecto</t>
         </is>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="56" t="n">
         <v>46194</v>
       </c>
-      <c r="F8" s="50" t="n">
+      <c r="F8" s="56" t="n">
         <v>46234</v>
       </c>
-      <c r="G8" s="51" t="n">
+      <c r="G8" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="58">
         <f>IF(D8="","",IF(N(G8)&gt;=1,"Completada",IF(AND(N(F8)&gt;0,F8&lt;TODAY()),"Atrasada",IF(AND(N(E8)&gt;0,E8&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="59">
         <f>IF(OR(D8="",N(F8)=0,N(G8)&gt;=1),"",F8-TODAY())</f>
         <v/>
       </c>
-      <c r="J8" s="54" t="n"/>
-      <c r="K8" s="54" t="n"/>
-      <c r="L8" s="54" t="n"/>
-      <c r="M8" s="54" t="n"/>
-      <c r="N8" s="54" t="n"/>
-      <c r="O8" s="54" t="n"/>
-      <c r="P8" s="54" t="n"/>
-      <c r="Q8" s="54" t="n"/>
-      <c r="R8" s="54" t="n"/>
-      <c r="S8" s="54" t="n"/>
-      <c r="T8" s="54" t="n"/>
-      <c r="U8" s="54" t="n"/>
-      <c r="V8" s="54" t="n"/>
-      <c r="W8" s="54" t="n"/>
-      <c r="X8" s="54" t="n"/>
-      <c r="Y8" s="54" t="n"/>
-      <c r="Z8" s="54" t="n"/>
-      <c r="AA8" s="54" t="n"/>
-      <c r="AB8" s="54" t="n"/>
-      <c r="AC8" s="54" t="n"/>
-      <c r="AD8" s="54" t="n"/>
-      <c r="AE8" s="54" t="n"/>
-      <c r="AF8" s="54" t="n"/>
-      <c r="AG8" s="54" t="n"/>
-      <c r="AH8" s="54" t="n"/>
-      <c r="AI8" s="54" t="n"/>
-      <c r="AJ8" s="54" t="n"/>
-      <c r="AK8" s="54" t="n"/>
-      <c r="AL8" s="54" t="n"/>
-      <c r="AM8" s="54" t="n"/>
-      <c r="AN8" s="54" t="n"/>
-      <c r="AO8" s="54" t="n"/>
-      <c r="AP8" s="54" t="n"/>
-      <c r="AQ8" s="54" t="n"/>
-      <c r="AR8" s="54" t="n"/>
-      <c r="AS8" s="54" t="n"/>
-      <c r="AT8" s="54" t="n"/>
-      <c r="AU8" s="54" t="n"/>
-      <c r="AV8" s="54" t="n"/>
-      <c r="AW8" s="54" t="n"/>
-      <c r="AX8" s="54" t="n"/>
-      <c r="AY8" s="54" t="n"/>
-      <c r="AZ8" s="54" t="n"/>
-      <c r="BA8" s="54" t="n"/>
-      <c r="BB8" s="54" t="n"/>
-      <c r="BC8" s="54" t="n"/>
-      <c r="BD8" s="54" t="n"/>
-      <c r="BE8" s="54" t="n"/>
-      <c r="BF8" s="54" t="n"/>
-      <c r="BG8" s="54" t="n"/>
-      <c r="BH8" s="54" t="n"/>
-      <c r="BI8" s="54" t="n"/>
+      <c r="J8" s="60" t="n"/>
+      <c r="K8" s="60" t="n"/>
+      <c r="L8" s="60" t="n"/>
+      <c r="M8" s="60" t="n"/>
+      <c r="N8" s="60" t="n"/>
+      <c r="O8" s="60" t="n"/>
+      <c r="P8" s="60" t="n"/>
+      <c r="Q8" s="60" t="n"/>
+      <c r="R8" s="60" t="n"/>
+      <c r="S8" s="60" t="n"/>
+      <c r="T8" s="60" t="n"/>
+      <c r="U8" s="60" t="n"/>
+      <c r="V8" s="60" t="n"/>
+      <c r="W8" s="60" t="n"/>
+      <c r="X8" s="60" t="n"/>
+      <c r="Y8" s="60" t="n"/>
+      <c r="Z8" s="60" t="n"/>
+      <c r="AA8" s="60" t="n"/>
+      <c r="AB8" s="60" t="n"/>
+      <c r="AC8" s="60" t="n"/>
+      <c r="AD8" s="60" t="n"/>
+      <c r="AE8" s="60" t="n"/>
+      <c r="AF8" s="60" t="n"/>
+      <c r="AG8" s="60" t="n"/>
+      <c r="AH8" s="60" t="n"/>
+      <c r="AI8" s="60" t="n"/>
+      <c r="AJ8" s="60" t="n"/>
+      <c r="AK8" s="60" t="n"/>
+      <c r="AL8" s="60" t="n"/>
+      <c r="AM8" s="60" t="n"/>
+      <c r="AN8" s="60" t="n"/>
+      <c r="AO8" s="60" t="n"/>
+      <c r="AP8" s="60" t="n"/>
+      <c r="AQ8" s="60" t="n"/>
+      <c r="AR8" s="60" t="n"/>
+      <c r="AS8" s="60" t="n"/>
+      <c r="AT8" s="60" t="n"/>
+      <c r="AU8" s="60" t="n"/>
+      <c r="AV8" s="60" t="n"/>
+      <c r="AW8" s="60" t="n"/>
+      <c r="AX8" s="60" t="n"/>
+      <c r="AY8" s="60" t="n"/>
+      <c r="AZ8" s="60" t="n"/>
+      <c r="BA8" s="60" t="n"/>
+      <c r="BB8" s="60" t="n"/>
+      <c r="BC8" s="60" t="n"/>
+      <c r="BD8" s="60" t="n"/>
+      <c r="BE8" s="60" t="n"/>
+      <c r="BF8" s="60" t="n"/>
+      <c r="BG8" s="60" t="n"/>
+      <c r="BH8" s="60" t="n"/>
+      <c r="BI8" s="60" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="B9" s="48">
+      <c r="B9" s="54">
         <f>IF(D9="","",3)</f>
         <v/>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>Marco teórico</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>Buscar y leer antecedentes</t>
         </is>
       </c>
-      <c r="E9" s="50" t="n">
+      <c r="E9" s="56" t="n">
         <v>46218</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="56" t="n">
         <v>46265</v>
       </c>
-      <c r="G9" s="51" t="n">
+      <c r="G9" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="58">
         <f>IF(D9="","",IF(N(G9)&gt;=1,"Completada",IF(AND(N(F9)&gt;0,F9&lt;TODAY()),"Atrasada",IF(AND(N(E9)&gt;0,E9&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="59">
         <f>IF(OR(D9="",N(F9)=0,N(G9)&gt;=1),"",F9-TODAY())</f>
         <v/>
       </c>
-      <c r="J9" s="54" t="n"/>
-      <c r="K9" s="54" t="n"/>
-      <c r="L9" s="54" t="n"/>
-      <c r="M9" s="54" t="n"/>
-      <c r="N9" s="54" t="n"/>
-      <c r="O9" s="54" t="n"/>
-      <c r="P9" s="54" t="n"/>
-      <c r="Q9" s="54" t="n"/>
-      <c r="R9" s="54" t="n"/>
-      <c r="S9" s="54" t="n"/>
-      <c r="T9" s="54" t="n"/>
-      <c r="U9" s="54" t="n"/>
-      <c r="V9" s="54" t="n"/>
-      <c r="W9" s="54" t="n"/>
-      <c r="X9" s="54" t="n"/>
-      <c r="Y9" s="54" t="n"/>
-      <c r="Z9" s="54" t="n"/>
-      <c r="AA9" s="54" t="n"/>
-      <c r="AB9" s="54" t="n"/>
-      <c r="AC9" s="54" t="n"/>
-      <c r="AD9" s="54" t="n"/>
-      <c r="AE9" s="54" t="n"/>
-      <c r="AF9" s="54" t="n"/>
-      <c r="AG9" s="54" t="n"/>
-      <c r="AH9" s="54" t="n"/>
-      <c r="AI9" s="54" t="n"/>
-      <c r="AJ9" s="54" t="n"/>
-      <c r="AK9" s="54" t="n"/>
-      <c r="AL9" s="54" t="n"/>
-      <c r="AM9" s="54" t="n"/>
-      <c r="AN9" s="54" t="n"/>
-      <c r="AO9" s="54" t="n"/>
-      <c r="AP9" s="54" t="n"/>
-      <c r="AQ9" s="54" t="n"/>
-      <c r="AR9" s="54" t="n"/>
-      <c r="AS9" s="54" t="n"/>
-      <c r="AT9" s="54" t="n"/>
-      <c r="AU9" s="54" t="n"/>
-      <c r="AV9" s="54" t="n"/>
-      <c r="AW9" s="54" t="n"/>
-      <c r="AX9" s="54" t="n"/>
-      <c r="AY9" s="54" t="n"/>
-      <c r="AZ9" s="54" t="n"/>
-      <c r="BA9" s="54" t="n"/>
-      <c r="BB9" s="54" t="n"/>
-      <c r="BC9" s="54" t="n"/>
-      <c r="BD9" s="54" t="n"/>
-      <c r="BE9" s="54" t="n"/>
-      <c r="BF9" s="54" t="n"/>
-      <c r="BG9" s="54" t="n"/>
-      <c r="BH9" s="54" t="n"/>
-      <c r="BI9" s="54" t="n"/>
+      <c r="J9" s="60" t="n"/>
+      <c r="K9" s="60" t="n"/>
+      <c r="L9" s="60" t="n"/>
+      <c r="M9" s="60" t="n"/>
+      <c r="N9" s="60" t="n"/>
+      <c r="O9" s="60" t="n"/>
+      <c r="P9" s="60" t="n"/>
+      <c r="Q9" s="60" t="n"/>
+      <c r="R9" s="60" t="n"/>
+      <c r="S9" s="60" t="n"/>
+      <c r="T9" s="60" t="n"/>
+      <c r="U9" s="60" t="n"/>
+      <c r="V9" s="60" t="n"/>
+      <c r="W9" s="60" t="n"/>
+      <c r="X9" s="60" t="n"/>
+      <c r="Y9" s="60" t="n"/>
+      <c r="Z9" s="60" t="n"/>
+      <c r="AA9" s="60" t="n"/>
+      <c r="AB9" s="60" t="n"/>
+      <c r="AC9" s="60" t="n"/>
+      <c r="AD9" s="60" t="n"/>
+      <c r="AE9" s="60" t="n"/>
+      <c r="AF9" s="60" t="n"/>
+      <c r="AG9" s="60" t="n"/>
+      <c r="AH9" s="60" t="n"/>
+      <c r="AI9" s="60" t="n"/>
+      <c r="AJ9" s="60" t="n"/>
+      <c r="AK9" s="60" t="n"/>
+      <c r="AL9" s="60" t="n"/>
+      <c r="AM9" s="60" t="n"/>
+      <c r="AN9" s="60" t="n"/>
+      <c r="AO9" s="60" t="n"/>
+      <c r="AP9" s="60" t="n"/>
+      <c r="AQ9" s="60" t="n"/>
+      <c r="AR9" s="60" t="n"/>
+      <c r="AS9" s="60" t="n"/>
+      <c r="AT9" s="60" t="n"/>
+      <c r="AU9" s="60" t="n"/>
+      <c r="AV9" s="60" t="n"/>
+      <c r="AW9" s="60" t="n"/>
+      <c r="AX9" s="60" t="n"/>
+      <c r="AY9" s="60" t="n"/>
+      <c r="AZ9" s="60" t="n"/>
+      <c r="BA9" s="60" t="n"/>
+      <c r="BB9" s="60" t="n"/>
+      <c r="BC9" s="60" t="n"/>
+      <c r="BD9" s="60" t="n"/>
+      <c r="BE9" s="60" t="n"/>
+      <c r="BF9" s="60" t="n"/>
+      <c r="BG9" s="60" t="n"/>
+      <c r="BH9" s="60" t="n"/>
+      <c r="BI9" s="60" t="n"/>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="B10" s="48">
+      <c r="B10" s="54">
         <f>IF(D10="","",4)</f>
         <v/>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
         <is>
           <t>Marco teórico</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>Redactar el marco teórico</t>
         </is>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="56" t="n">
         <v>46266</v>
       </c>
-      <c r="F10" s="50" t="n">
+      <c r="F10" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="G10" s="51" t="n">
+      <c r="G10" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="58">
         <f>IF(D10="","",IF(N(G10)&gt;=1,"Completada",IF(AND(N(F10)&gt;0,F10&lt;TODAY()),"Atrasada",IF(AND(N(E10)&gt;0,E10&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I10" s="53">
+      <c r="I10" s="59">
         <f>IF(OR(D10="",N(F10)=0,N(G10)&gt;=1),"",F10-TODAY())</f>
         <v/>
       </c>
-      <c r="J10" s="54" t="n"/>
-      <c r="K10" s="54" t="n"/>
-      <c r="L10" s="54" t="n"/>
-      <c r="M10" s="54" t="n"/>
-      <c r="N10" s="54" t="n"/>
-      <c r="O10" s="54" t="n"/>
-      <c r="P10" s="54" t="n"/>
-      <c r="Q10" s="54" t="n"/>
-      <c r="R10" s="54" t="n"/>
-      <c r="S10" s="54" t="n"/>
-      <c r="T10" s="54" t="n"/>
-      <c r="U10" s="54" t="n"/>
-      <c r="V10" s="54" t="n"/>
-      <c r="W10" s="54" t="n"/>
-      <c r="X10" s="54" t="n"/>
-      <c r="Y10" s="54" t="n"/>
-      <c r="Z10" s="54" t="n"/>
-      <c r="AA10" s="54" t="n"/>
-      <c r="AB10" s="54" t="n"/>
-      <c r="AC10" s="54" t="n"/>
-      <c r="AD10" s="54" t="n"/>
-      <c r="AE10" s="54" t="n"/>
-      <c r="AF10" s="54" t="n"/>
-      <c r="AG10" s="54" t="n"/>
-      <c r="AH10" s="54" t="n"/>
-      <c r="AI10" s="54" t="n"/>
-      <c r="AJ10" s="54" t="n"/>
-      <c r="AK10" s="54" t="n"/>
-      <c r="AL10" s="54" t="n"/>
-      <c r="AM10" s="54" t="n"/>
-      <c r="AN10" s="54" t="n"/>
-      <c r="AO10" s="54" t="n"/>
-      <c r="AP10" s="54" t="n"/>
-      <c r="AQ10" s="54" t="n"/>
-      <c r="AR10" s="54" t="n"/>
-      <c r="AS10" s="54" t="n"/>
-      <c r="AT10" s="54" t="n"/>
-      <c r="AU10" s="54" t="n"/>
-      <c r="AV10" s="54" t="n"/>
-      <c r="AW10" s="54" t="n"/>
-      <c r="AX10" s="54" t="n"/>
-      <c r="AY10" s="54" t="n"/>
-      <c r="AZ10" s="54" t="n"/>
-      <c r="BA10" s="54" t="n"/>
-      <c r="BB10" s="54" t="n"/>
-      <c r="BC10" s="54" t="n"/>
-      <c r="BD10" s="54" t="n"/>
-      <c r="BE10" s="54" t="n"/>
-      <c r="BF10" s="54" t="n"/>
-      <c r="BG10" s="54" t="n"/>
-      <c r="BH10" s="54" t="n"/>
-      <c r="BI10" s="54" t="n"/>
+      <c r="J10" s="60" t="n"/>
+      <c r="K10" s="60" t="n"/>
+      <c r="L10" s="60" t="n"/>
+      <c r="M10" s="60" t="n"/>
+      <c r="N10" s="60" t="n"/>
+      <c r="O10" s="60" t="n"/>
+      <c r="P10" s="60" t="n"/>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="60" t="n"/>
+      <c r="T10" s="60" t="n"/>
+      <c r="U10" s="60" t="n"/>
+      <c r="V10" s="60" t="n"/>
+      <c r="W10" s="60" t="n"/>
+      <c r="X10" s="60" t="n"/>
+      <c r="Y10" s="60" t="n"/>
+      <c r="Z10" s="60" t="n"/>
+      <c r="AA10" s="60" t="n"/>
+      <c r="AB10" s="60" t="n"/>
+      <c r="AC10" s="60" t="n"/>
+      <c r="AD10" s="60" t="n"/>
+      <c r="AE10" s="60" t="n"/>
+      <c r="AF10" s="60" t="n"/>
+      <c r="AG10" s="60" t="n"/>
+      <c r="AH10" s="60" t="n"/>
+      <c r="AI10" s="60" t="n"/>
+      <c r="AJ10" s="60" t="n"/>
+      <c r="AK10" s="60" t="n"/>
+      <c r="AL10" s="60" t="n"/>
+      <c r="AM10" s="60" t="n"/>
+      <c r="AN10" s="60" t="n"/>
+      <c r="AO10" s="60" t="n"/>
+      <c r="AP10" s="60" t="n"/>
+      <c r="AQ10" s="60" t="n"/>
+      <c r="AR10" s="60" t="n"/>
+      <c r="AS10" s="60" t="n"/>
+      <c r="AT10" s="60" t="n"/>
+      <c r="AU10" s="60" t="n"/>
+      <c r="AV10" s="60" t="n"/>
+      <c r="AW10" s="60" t="n"/>
+      <c r="AX10" s="60" t="n"/>
+      <c r="AY10" s="60" t="n"/>
+      <c r="AZ10" s="60" t="n"/>
+      <c r="BA10" s="60" t="n"/>
+      <c r="BB10" s="60" t="n"/>
+      <c r="BC10" s="60" t="n"/>
+      <c r="BD10" s="60" t="n"/>
+      <c r="BE10" s="60" t="n"/>
+      <c r="BF10" s="60" t="n"/>
+      <c r="BG10" s="60" t="n"/>
+      <c r="BH10" s="60" t="n"/>
+      <c r="BI10" s="60" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="B11" s="48">
+      <c r="B11" s="54">
         <f>IF(D11="","",5)</f>
         <v/>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>Metodología</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="55" t="inlineStr">
         <is>
           <t>Diseñar la encuesta</t>
         </is>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="56" t="n">
         <v>46280</v>
       </c>
-      <c r="F11" s="50" t="n">
+      <c r="F11" s="56" t="n">
         <v>46305</v>
       </c>
-      <c r="G11" s="51" t="n">
+      <c r="G11" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="58">
         <f>IF(D11="","",IF(N(G11)&gt;=1,"Completada",IF(AND(N(F11)&gt;0,F11&lt;TODAY()),"Atrasada",IF(AND(N(E11)&gt;0,E11&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="59">
         <f>IF(OR(D11="",N(F11)=0,N(G11)&gt;=1),"",F11-TODAY())</f>
         <v/>
       </c>
-      <c r="J11" s="54" t="n"/>
-      <c r="K11" s="54" t="n"/>
-      <c r="L11" s="54" t="n"/>
-      <c r="M11" s="54" t="n"/>
-      <c r="N11" s="54" t="n"/>
-      <c r="O11" s="54" t="n"/>
-      <c r="P11" s="54" t="n"/>
-      <c r="Q11" s="54" t="n"/>
-      <c r="R11" s="54" t="n"/>
-      <c r="S11" s="54" t="n"/>
-      <c r="T11" s="54" t="n"/>
-      <c r="U11" s="54" t="n"/>
-      <c r="V11" s="54" t="n"/>
-      <c r="W11" s="54" t="n"/>
-      <c r="X11" s="54" t="n"/>
-      <c r="Y11" s="54" t="n"/>
-      <c r="Z11" s="54" t="n"/>
-      <c r="AA11" s="54" t="n"/>
-      <c r="AB11" s="54" t="n"/>
-      <c r="AC11" s="54" t="n"/>
-      <c r="AD11" s="54" t="n"/>
-      <c r="AE11" s="54" t="n"/>
-      <c r="AF11" s="54" t="n"/>
-      <c r="AG11" s="54" t="n"/>
-      <c r="AH11" s="54" t="n"/>
-      <c r="AI11" s="54" t="n"/>
-      <c r="AJ11" s="54" t="n"/>
-      <c r="AK11" s="54" t="n"/>
-      <c r="AL11" s="54" t="n"/>
-      <c r="AM11" s="54" t="n"/>
-      <c r="AN11" s="54" t="n"/>
-      <c r="AO11" s="54" t="n"/>
-      <c r="AP11" s="54" t="n"/>
-      <c r="AQ11" s="54" t="n"/>
-      <c r="AR11" s="54" t="n"/>
-      <c r="AS11" s="54" t="n"/>
-      <c r="AT11" s="54" t="n"/>
-      <c r="AU11" s="54" t="n"/>
-      <c r="AV11" s="54" t="n"/>
-      <c r="AW11" s="54" t="n"/>
-      <c r="AX11" s="54" t="n"/>
-      <c r="AY11" s="54" t="n"/>
-      <c r="AZ11" s="54" t="n"/>
-      <c r="BA11" s="54" t="n"/>
-      <c r="BB11" s="54" t="n"/>
-      <c r="BC11" s="54" t="n"/>
-      <c r="BD11" s="54" t="n"/>
-      <c r="BE11" s="54" t="n"/>
-      <c r="BF11" s="54" t="n"/>
-      <c r="BG11" s="54" t="n"/>
-      <c r="BH11" s="54" t="n"/>
-      <c r="BI11" s="54" t="n"/>
+      <c r="J11" s="60" t="n"/>
+      <c r="K11" s="60" t="n"/>
+      <c r="L11" s="60" t="n"/>
+      <c r="M11" s="60" t="n"/>
+      <c r="N11" s="60" t="n"/>
+      <c r="O11" s="60" t="n"/>
+      <c r="P11" s="60" t="n"/>
+      <c r="Q11" s="60" t="n"/>
+      <c r="R11" s="60" t="n"/>
+      <c r="S11" s="60" t="n"/>
+      <c r="T11" s="60" t="n"/>
+      <c r="U11" s="60" t="n"/>
+      <c r="V11" s="60" t="n"/>
+      <c r="W11" s="60" t="n"/>
+      <c r="X11" s="60" t="n"/>
+      <c r="Y11" s="60" t="n"/>
+      <c r="Z11" s="60" t="n"/>
+      <c r="AA11" s="60" t="n"/>
+      <c r="AB11" s="60" t="n"/>
+      <c r="AC11" s="60" t="n"/>
+      <c r="AD11" s="60" t="n"/>
+      <c r="AE11" s="60" t="n"/>
+      <c r="AF11" s="60" t="n"/>
+      <c r="AG11" s="60" t="n"/>
+      <c r="AH11" s="60" t="n"/>
+      <c r="AI11" s="60" t="n"/>
+      <c r="AJ11" s="60" t="n"/>
+      <c r="AK11" s="60" t="n"/>
+      <c r="AL11" s="60" t="n"/>
+      <c r="AM11" s="60" t="n"/>
+      <c r="AN11" s="60" t="n"/>
+      <c r="AO11" s="60" t="n"/>
+      <c r="AP11" s="60" t="n"/>
+      <c r="AQ11" s="60" t="n"/>
+      <c r="AR11" s="60" t="n"/>
+      <c r="AS11" s="60" t="n"/>
+      <c r="AT11" s="60" t="n"/>
+      <c r="AU11" s="60" t="n"/>
+      <c r="AV11" s="60" t="n"/>
+      <c r="AW11" s="60" t="n"/>
+      <c r="AX11" s="60" t="n"/>
+      <c r="AY11" s="60" t="n"/>
+      <c r="AZ11" s="60" t="n"/>
+      <c r="BA11" s="60" t="n"/>
+      <c r="BB11" s="60" t="n"/>
+      <c r="BC11" s="60" t="n"/>
+      <c r="BD11" s="60" t="n"/>
+      <c r="BE11" s="60" t="n"/>
+      <c r="BF11" s="60" t="n"/>
+      <c r="BG11" s="60" t="n"/>
+      <c r="BH11" s="60" t="n"/>
+      <c r="BI11" s="60" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="B12" s="48">
+      <c r="B12" s="54">
         <f>IF(D12="","",6)</f>
         <v/>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>Metodología</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="55" t="inlineStr">
         <is>
           <t>Validar la encuesta con el tutor</t>
         </is>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="56" t="n">
         <v>46306</v>
       </c>
-      <c r="F12" s="50" t="n">
+      <c r="F12" s="56" t="n">
         <v>46320</v>
       </c>
-      <c r="G12" s="51" t="n">
+      <c r="G12" s="57" t="n">
         <v>0.8</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12" s="58">
         <f>IF(D12="","",IF(N(G12)&gt;=1,"Completada",IF(AND(N(F12)&gt;0,F12&lt;TODAY()),"Atrasada",IF(AND(N(E12)&gt;0,E12&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I12" s="53">
+      <c r="I12" s="59">
         <f>IF(OR(D12="",N(F12)=0,N(G12)&gt;=1),"",F12-TODAY())</f>
         <v/>
       </c>
-      <c r="J12" s="54" t="n"/>
-      <c r="K12" s="54" t="n"/>
-      <c r="L12" s="54" t="n"/>
-      <c r="M12" s="54" t="n"/>
-      <c r="N12" s="54" t="n"/>
-      <c r="O12" s="54" t="n"/>
-      <c r="P12" s="54" t="n"/>
-      <c r="Q12" s="54" t="n"/>
-      <c r="R12" s="54" t="n"/>
-      <c r="S12" s="54" t="n"/>
-      <c r="T12" s="54" t="n"/>
-      <c r="U12" s="54" t="n"/>
-      <c r="V12" s="54" t="n"/>
-      <c r="W12" s="54" t="n"/>
-      <c r="X12" s="54" t="n"/>
-      <c r="Y12" s="54" t="n"/>
-      <c r="Z12" s="54" t="n"/>
-      <c r="AA12" s="54" t="n"/>
-      <c r="AB12" s="54" t="n"/>
-      <c r="AC12" s="54" t="n"/>
-      <c r="AD12" s="54" t="n"/>
-      <c r="AE12" s="54" t="n"/>
-      <c r="AF12" s="54" t="n"/>
-      <c r="AG12" s="54" t="n"/>
-      <c r="AH12" s="54" t="n"/>
-      <c r="AI12" s="54" t="n"/>
-      <c r="AJ12" s="54" t="n"/>
-      <c r="AK12" s="54" t="n"/>
-      <c r="AL12" s="54" t="n"/>
-      <c r="AM12" s="54" t="n"/>
-      <c r="AN12" s="54" t="n"/>
-      <c r="AO12" s="54" t="n"/>
-      <c r="AP12" s="54" t="n"/>
-      <c r="AQ12" s="54" t="n"/>
-      <c r="AR12" s="54" t="n"/>
-      <c r="AS12" s="54" t="n"/>
-      <c r="AT12" s="54" t="n"/>
-      <c r="AU12" s="54" t="n"/>
-      <c r="AV12" s="54" t="n"/>
-      <c r="AW12" s="54" t="n"/>
-      <c r="AX12" s="54" t="n"/>
-      <c r="AY12" s="54" t="n"/>
-      <c r="AZ12" s="54" t="n"/>
-      <c r="BA12" s="54" t="n"/>
-      <c r="BB12" s="54" t="n"/>
-      <c r="BC12" s="54" t="n"/>
-      <c r="BD12" s="54" t="n"/>
-      <c r="BE12" s="54" t="n"/>
-      <c r="BF12" s="54" t="n"/>
-      <c r="BG12" s="54" t="n"/>
-      <c r="BH12" s="54" t="n"/>
-      <c r="BI12" s="54" t="n"/>
+      <c r="J12" s="60" t="n"/>
+      <c r="K12" s="60" t="n"/>
+      <c r="L12" s="60" t="n"/>
+      <c r="M12" s="60" t="n"/>
+      <c r="N12" s="60" t="n"/>
+      <c r="O12" s="60" t="n"/>
+      <c r="P12" s="60" t="n"/>
+      <c r="Q12" s="60" t="n"/>
+      <c r="R12" s="60" t="n"/>
+      <c r="S12" s="60" t="n"/>
+      <c r="T12" s="60" t="n"/>
+      <c r="U12" s="60" t="n"/>
+      <c r="V12" s="60" t="n"/>
+      <c r="W12" s="60" t="n"/>
+      <c r="X12" s="60" t="n"/>
+      <c r="Y12" s="60" t="n"/>
+      <c r="Z12" s="60" t="n"/>
+      <c r="AA12" s="60" t="n"/>
+      <c r="AB12" s="60" t="n"/>
+      <c r="AC12" s="60" t="n"/>
+      <c r="AD12" s="60" t="n"/>
+      <c r="AE12" s="60" t="n"/>
+      <c r="AF12" s="60" t="n"/>
+      <c r="AG12" s="60" t="n"/>
+      <c r="AH12" s="60" t="n"/>
+      <c r="AI12" s="60" t="n"/>
+      <c r="AJ12" s="60" t="n"/>
+      <c r="AK12" s="60" t="n"/>
+      <c r="AL12" s="60" t="n"/>
+      <c r="AM12" s="60" t="n"/>
+      <c r="AN12" s="60" t="n"/>
+      <c r="AO12" s="60" t="n"/>
+      <c r="AP12" s="60" t="n"/>
+      <c r="AQ12" s="60" t="n"/>
+      <c r="AR12" s="60" t="n"/>
+      <c r="AS12" s="60" t="n"/>
+      <c r="AT12" s="60" t="n"/>
+      <c r="AU12" s="60" t="n"/>
+      <c r="AV12" s="60" t="n"/>
+      <c r="AW12" s="60" t="n"/>
+      <c r="AX12" s="60" t="n"/>
+      <c r="AY12" s="60" t="n"/>
+      <c r="AZ12" s="60" t="n"/>
+      <c r="BA12" s="60" t="n"/>
+      <c r="BB12" s="60" t="n"/>
+      <c r="BC12" s="60" t="n"/>
+      <c r="BD12" s="60" t="n"/>
+      <c r="BE12" s="60" t="n"/>
+      <c r="BF12" s="60" t="n"/>
+      <c r="BG12" s="60" t="n"/>
+      <c r="BH12" s="60" t="n"/>
+      <c r="BI12" s="60" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="B13" s="48">
+      <c r="B13" s="54">
         <f>IF(D13="","",7)</f>
         <v/>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>Trabajo de campo</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="55" t="inlineStr">
         <is>
           <t>Aplicar las encuestas</t>
         </is>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="56" t="n">
         <v>46315</v>
       </c>
-      <c r="F13" s="50" t="n">
+      <c r="F13" s="56" t="n">
         <v>46356</v>
       </c>
-      <c r="G13" s="51" t="n">
+      <c r="G13" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="H13" s="52">
+      <c r="H13" s="58">
         <f>IF(D13="","",IF(N(G13)&gt;=1,"Completada",IF(AND(N(F13)&gt;0,F13&lt;TODAY()),"Atrasada",IF(AND(N(E13)&gt;0,E13&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I13" s="53">
+      <c r="I13" s="59">
         <f>IF(OR(D13="",N(F13)=0,N(G13)&gt;=1),"",F13-TODAY())</f>
         <v/>
       </c>
-      <c r="J13" s="54" t="n"/>
-      <c r="K13" s="54" t="n"/>
-      <c r="L13" s="54" t="n"/>
-      <c r="M13" s="54" t="n"/>
-      <c r="N13" s="54" t="n"/>
-      <c r="O13" s="54" t="n"/>
-      <c r="P13" s="54" t="n"/>
-      <c r="Q13" s="54" t="n"/>
-      <c r="R13" s="54" t="n"/>
-      <c r="S13" s="54" t="n"/>
-      <c r="T13" s="54" t="n"/>
-      <c r="U13" s="54" t="n"/>
-      <c r="V13" s="54" t="n"/>
-      <c r="W13" s="54" t="n"/>
-      <c r="X13" s="54" t="n"/>
-      <c r="Y13" s="54" t="n"/>
-      <c r="Z13" s="54" t="n"/>
-      <c r="AA13" s="54" t="n"/>
-      <c r="AB13" s="54" t="n"/>
-      <c r="AC13" s="54" t="n"/>
-      <c r="AD13" s="54" t="n"/>
-      <c r="AE13" s="54" t="n"/>
-      <c r="AF13" s="54" t="n"/>
-      <c r="AG13" s="54" t="n"/>
-      <c r="AH13" s="54" t="n"/>
-      <c r="AI13" s="54" t="n"/>
-      <c r="AJ13" s="54" t="n"/>
-      <c r="AK13" s="54" t="n"/>
-      <c r="AL13" s="54" t="n"/>
-      <c r="AM13" s="54" t="n"/>
-      <c r="AN13" s="54" t="n"/>
-      <c r="AO13" s="54" t="n"/>
-      <c r="AP13" s="54" t="n"/>
-      <c r="AQ13" s="54" t="n"/>
-      <c r="AR13" s="54" t="n"/>
-      <c r="AS13" s="54" t="n"/>
-      <c r="AT13" s="54" t="n"/>
-      <c r="AU13" s="54" t="n"/>
-      <c r="AV13" s="54" t="n"/>
-      <c r="AW13" s="54" t="n"/>
-      <c r="AX13" s="54" t="n"/>
-      <c r="AY13" s="54" t="n"/>
-      <c r="AZ13" s="54" t="n"/>
-      <c r="BA13" s="54" t="n"/>
-      <c r="BB13" s="54" t="n"/>
-      <c r="BC13" s="54" t="n"/>
-      <c r="BD13" s="54" t="n"/>
-      <c r="BE13" s="54" t="n"/>
-      <c r="BF13" s="54" t="n"/>
-      <c r="BG13" s="54" t="n"/>
-      <c r="BH13" s="54" t="n"/>
-      <c r="BI13" s="54" t="n"/>
+      <c r="J13" s="60" t="n"/>
+      <c r="K13" s="60" t="n"/>
+      <c r="L13" s="60" t="n"/>
+      <c r="M13" s="60" t="n"/>
+      <c r="N13" s="60" t="n"/>
+      <c r="O13" s="60" t="n"/>
+      <c r="P13" s="60" t="n"/>
+      <c r="Q13" s="60" t="n"/>
+      <c r="R13" s="60" t="n"/>
+      <c r="S13" s="60" t="n"/>
+      <c r="T13" s="60" t="n"/>
+      <c r="U13" s="60" t="n"/>
+      <c r="V13" s="60" t="n"/>
+      <c r="W13" s="60" t="n"/>
+      <c r="X13" s="60" t="n"/>
+      <c r="Y13" s="60" t="n"/>
+      <c r="Z13" s="60" t="n"/>
+      <c r="AA13" s="60" t="n"/>
+      <c r="AB13" s="60" t="n"/>
+      <c r="AC13" s="60" t="n"/>
+      <c r="AD13" s="60" t="n"/>
+      <c r="AE13" s="60" t="n"/>
+      <c r="AF13" s="60" t="n"/>
+      <c r="AG13" s="60" t="n"/>
+      <c r="AH13" s="60" t="n"/>
+      <c r="AI13" s="60" t="n"/>
+      <c r="AJ13" s="60" t="n"/>
+      <c r="AK13" s="60" t="n"/>
+      <c r="AL13" s="60" t="n"/>
+      <c r="AM13" s="60" t="n"/>
+      <c r="AN13" s="60" t="n"/>
+      <c r="AO13" s="60" t="n"/>
+      <c r="AP13" s="60" t="n"/>
+      <c r="AQ13" s="60" t="n"/>
+      <c r="AR13" s="60" t="n"/>
+      <c r="AS13" s="60" t="n"/>
+      <c r="AT13" s="60" t="n"/>
+      <c r="AU13" s="60" t="n"/>
+      <c r="AV13" s="60" t="n"/>
+      <c r="AW13" s="60" t="n"/>
+      <c r="AX13" s="60" t="n"/>
+      <c r="AY13" s="60" t="n"/>
+      <c r="AZ13" s="60" t="n"/>
+      <c r="BA13" s="60" t="n"/>
+      <c r="BB13" s="60" t="n"/>
+      <c r="BC13" s="60" t="n"/>
+      <c r="BD13" s="60" t="n"/>
+      <c r="BE13" s="60" t="n"/>
+      <c r="BF13" s="60" t="n"/>
+      <c r="BG13" s="60" t="n"/>
+      <c r="BH13" s="60" t="n"/>
+      <c r="BI13" s="60" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="48">
+      <c r="B14" s="54">
         <f>IF(D14="","",8)</f>
         <v/>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="55" t="inlineStr">
         <is>
           <t>Trabajo de campo</t>
         </is>
       </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>Cargar los datos</t>
         </is>
       </c>
-      <c r="E14" s="50" t="n">
+      <c r="E14" s="56" t="n">
         <v>46341</v>
       </c>
-      <c r="F14" s="50" t="n">
+      <c r="F14" s="56" t="n">
         <v>46366</v>
       </c>
-      <c r="G14" s="51" t="n">
+      <c r="G14" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="58">
         <f>IF(D14="","",IF(N(G14)&gt;=1,"Completada",IF(AND(N(F14)&gt;0,F14&lt;TODAY()),"Atrasada",IF(AND(N(E14)&gt;0,E14&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="59">
         <f>IF(OR(D14="",N(F14)=0,N(G14)&gt;=1),"",F14-TODAY())</f>
         <v/>
       </c>
-      <c r="J14" s="54" t="n"/>
-      <c r="K14" s="54" t="n"/>
-      <c r="L14" s="54" t="n"/>
-      <c r="M14" s="54" t="n"/>
-      <c r="N14" s="54" t="n"/>
-      <c r="O14" s="54" t="n"/>
-      <c r="P14" s="54" t="n"/>
-      <c r="Q14" s="54" t="n"/>
-      <c r="R14" s="54" t="n"/>
-      <c r="S14" s="54" t="n"/>
-      <c r="T14" s="54" t="n"/>
-      <c r="U14" s="54" t="n"/>
-      <c r="V14" s="54" t="n"/>
-      <c r="W14" s="54" t="n"/>
-      <c r="X14" s="54" t="n"/>
-      <c r="Y14" s="54" t="n"/>
-      <c r="Z14" s="54" t="n"/>
-      <c r="AA14" s="54" t="n"/>
-      <c r="AB14" s="54" t="n"/>
-      <c r="AC14" s="54" t="n"/>
-      <c r="AD14" s="54" t="n"/>
-      <c r="AE14" s="54" t="n"/>
-      <c r="AF14" s="54" t="n"/>
-      <c r="AG14" s="54" t="n"/>
-      <c r="AH14" s="54" t="n"/>
-      <c r="AI14" s="54" t="n"/>
-      <c r="AJ14" s="54" t="n"/>
-      <c r="AK14" s="54" t="n"/>
-      <c r="AL14" s="54" t="n"/>
-      <c r="AM14" s="54" t="n"/>
-      <c r="AN14" s="54" t="n"/>
-      <c r="AO14" s="54" t="n"/>
-      <c r="AP14" s="54" t="n"/>
-      <c r="AQ14" s="54" t="n"/>
-      <c r="AR14" s="54" t="n"/>
-      <c r="AS14" s="54" t="n"/>
-      <c r="AT14" s="54" t="n"/>
-      <c r="AU14" s="54" t="n"/>
-      <c r="AV14" s="54" t="n"/>
-      <c r="AW14" s="54" t="n"/>
-      <c r="AX14" s="54" t="n"/>
-      <c r="AY14" s="54" t="n"/>
-      <c r="AZ14" s="54" t="n"/>
-      <c r="BA14" s="54" t="n"/>
-      <c r="BB14" s="54" t="n"/>
-      <c r="BC14" s="54" t="n"/>
-      <c r="BD14" s="54" t="n"/>
-      <c r="BE14" s="54" t="n"/>
-      <c r="BF14" s="54" t="n"/>
-      <c r="BG14" s="54" t="n"/>
-      <c r="BH14" s="54" t="n"/>
-      <c r="BI14" s="54" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
+      <c r="O14" s="60" t="n"/>
+      <c r="P14" s="60" t="n"/>
+      <c r="Q14" s="60" t="n"/>
+      <c r="R14" s="60" t="n"/>
+      <c r="S14" s="60" t="n"/>
+      <c r="T14" s="60" t="n"/>
+      <c r="U14" s="60" t="n"/>
+      <c r="V14" s="60" t="n"/>
+      <c r="W14" s="60" t="n"/>
+      <c r="X14" s="60" t="n"/>
+      <c r="Y14" s="60" t="n"/>
+      <c r="Z14" s="60" t="n"/>
+      <c r="AA14" s="60" t="n"/>
+      <c r="AB14" s="60" t="n"/>
+      <c r="AC14" s="60" t="n"/>
+      <c r="AD14" s="60" t="n"/>
+      <c r="AE14" s="60" t="n"/>
+      <c r="AF14" s="60" t="n"/>
+      <c r="AG14" s="60" t="n"/>
+      <c r="AH14" s="60" t="n"/>
+      <c r="AI14" s="60" t="n"/>
+      <c r="AJ14" s="60" t="n"/>
+      <c r="AK14" s="60" t="n"/>
+      <c r="AL14" s="60" t="n"/>
+      <c r="AM14" s="60" t="n"/>
+      <c r="AN14" s="60" t="n"/>
+      <c r="AO14" s="60" t="n"/>
+      <c r="AP14" s="60" t="n"/>
+      <c r="AQ14" s="60" t="n"/>
+      <c r="AR14" s="60" t="n"/>
+      <c r="AS14" s="60" t="n"/>
+      <c r="AT14" s="60" t="n"/>
+      <c r="AU14" s="60" t="n"/>
+      <c r="AV14" s="60" t="n"/>
+      <c r="AW14" s="60" t="n"/>
+      <c r="AX14" s="60" t="n"/>
+      <c r="AY14" s="60" t="n"/>
+      <c r="AZ14" s="60" t="n"/>
+      <c r="BA14" s="60" t="n"/>
+      <c r="BB14" s="60" t="n"/>
+      <c r="BC14" s="60" t="n"/>
+      <c r="BD14" s="60" t="n"/>
+      <c r="BE14" s="60" t="n"/>
+      <c r="BF14" s="60" t="n"/>
+      <c r="BG14" s="60" t="n"/>
+      <c r="BH14" s="60" t="n"/>
+      <c r="BI14" s="60" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="48">
+      <c r="B15" s="54">
         <f>IF(D15="","",9)</f>
         <v/>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
         <is>
           <t>Análisis de datos</t>
         </is>
       </c>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="D15" s="55" t="inlineStr">
         <is>
           <t>Procesar y analizar resultados</t>
         </is>
       </c>
-      <c r="E15" s="50" t="n">
+      <c r="E15" s="56" t="n">
         <v>46357</v>
       </c>
-      <c r="F15" s="50" t="n">
+      <c r="F15" s="56" t="n">
         <v>46402</v>
       </c>
-      <c r="G15" s="51" t="n">
+      <c r="G15" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="58">
         <f>IF(D15="","",IF(N(G15)&gt;=1,"Completada",IF(AND(N(F15)&gt;0,F15&lt;TODAY()),"Atrasada",IF(AND(N(E15)&gt;0,E15&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I15" s="53">
+      <c r="I15" s="59">
         <f>IF(OR(D15="",N(F15)=0,N(G15)&gt;=1),"",F15-TODAY())</f>
         <v/>
       </c>
-      <c r="J15" s="54" t="n"/>
-      <c r="K15" s="54" t="n"/>
-      <c r="L15" s="54" t="n"/>
-      <c r="M15" s="54" t="n"/>
-      <c r="N15" s="54" t="n"/>
-      <c r="O15" s="54" t="n"/>
-      <c r="P15" s="54" t="n"/>
-      <c r="Q15" s="54" t="n"/>
-      <c r="R15" s="54" t="n"/>
-      <c r="S15" s="54" t="n"/>
-      <c r="T15" s="54" t="n"/>
-      <c r="U15" s="54" t="n"/>
-      <c r="V15" s="54" t="n"/>
-      <c r="W15" s="54" t="n"/>
-      <c r="X15" s="54" t="n"/>
-      <c r="Y15" s="54" t="n"/>
-      <c r="Z15" s="54" t="n"/>
-      <c r="AA15" s="54" t="n"/>
-      <c r="AB15" s="54" t="n"/>
-      <c r="AC15" s="54" t="n"/>
-      <c r="AD15" s="54" t="n"/>
-      <c r="AE15" s="54" t="n"/>
-      <c r="AF15" s="54" t="n"/>
-      <c r="AG15" s="54" t="n"/>
-      <c r="AH15" s="54" t="n"/>
-      <c r="AI15" s="54" t="n"/>
-      <c r="AJ15" s="54" t="n"/>
-      <c r="AK15" s="54" t="n"/>
-      <c r="AL15" s="54" t="n"/>
-      <c r="AM15" s="54" t="n"/>
-      <c r="AN15" s="54" t="n"/>
-      <c r="AO15" s="54" t="n"/>
-      <c r="AP15" s="54" t="n"/>
-      <c r="AQ15" s="54" t="n"/>
-      <c r="AR15" s="54" t="n"/>
-      <c r="AS15" s="54" t="n"/>
-      <c r="AT15" s="54" t="n"/>
-      <c r="AU15" s="54" t="n"/>
-      <c r="AV15" s="54" t="n"/>
-      <c r="AW15" s="54" t="n"/>
-      <c r="AX15" s="54" t="n"/>
-      <c r="AY15" s="54" t="n"/>
-      <c r="AZ15" s="54" t="n"/>
-      <c r="BA15" s="54" t="n"/>
-      <c r="BB15" s="54" t="n"/>
-      <c r="BC15" s="54" t="n"/>
-      <c r="BD15" s="54" t="n"/>
-      <c r="BE15" s="54" t="n"/>
-      <c r="BF15" s="54" t="n"/>
-      <c r="BG15" s="54" t="n"/>
-      <c r="BH15" s="54" t="n"/>
-      <c r="BI15" s="54" t="n"/>
+      <c r="J15" s="60" t="n"/>
+      <c r="K15" s="60" t="n"/>
+      <c r="L15" s="60" t="n"/>
+      <c r="M15" s="60" t="n"/>
+      <c r="N15" s="60" t="n"/>
+      <c r="O15" s="60" t="n"/>
+      <c r="P15" s="60" t="n"/>
+      <c r="Q15" s="60" t="n"/>
+      <c r="R15" s="60" t="n"/>
+      <c r="S15" s="60" t="n"/>
+      <c r="T15" s="60" t="n"/>
+      <c r="U15" s="60" t="n"/>
+      <c r="V15" s="60" t="n"/>
+      <c r="W15" s="60" t="n"/>
+      <c r="X15" s="60" t="n"/>
+      <c r="Y15" s="60" t="n"/>
+      <c r="Z15" s="60" t="n"/>
+      <c r="AA15" s="60" t="n"/>
+      <c r="AB15" s="60" t="n"/>
+      <c r="AC15" s="60" t="n"/>
+      <c r="AD15" s="60" t="n"/>
+      <c r="AE15" s="60" t="n"/>
+      <c r="AF15" s="60" t="n"/>
+      <c r="AG15" s="60" t="n"/>
+      <c r="AH15" s="60" t="n"/>
+      <c r="AI15" s="60" t="n"/>
+      <c r="AJ15" s="60" t="n"/>
+      <c r="AK15" s="60" t="n"/>
+      <c r="AL15" s="60" t="n"/>
+      <c r="AM15" s="60" t="n"/>
+      <c r="AN15" s="60" t="n"/>
+      <c r="AO15" s="60" t="n"/>
+      <c r="AP15" s="60" t="n"/>
+      <c r="AQ15" s="60" t="n"/>
+      <c r="AR15" s="60" t="n"/>
+      <c r="AS15" s="60" t="n"/>
+      <c r="AT15" s="60" t="n"/>
+      <c r="AU15" s="60" t="n"/>
+      <c r="AV15" s="60" t="n"/>
+      <c r="AW15" s="60" t="n"/>
+      <c r="AX15" s="60" t="n"/>
+      <c r="AY15" s="60" t="n"/>
+      <c r="AZ15" s="60" t="n"/>
+      <c r="BA15" s="60" t="n"/>
+      <c r="BB15" s="60" t="n"/>
+      <c r="BC15" s="60" t="n"/>
+      <c r="BD15" s="60" t="n"/>
+      <c r="BE15" s="60" t="n"/>
+      <c r="BF15" s="60" t="n"/>
+      <c r="BG15" s="60" t="n"/>
+      <c r="BH15" s="60" t="n"/>
+      <c r="BI15" s="60" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="48">
+      <c r="B16" s="54">
         <f>IF(D16="","",10)</f>
         <v/>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="55" t="inlineStr">
         <is>
           <t>Análisis de datos</t>
         </is>
       </c>
-      <c r="D16" s="49" t="inlineStr">
+      <c r="D16" s="55" t="inlineStr">
         <is>
           <t>Elaborar tablas y gráficos</t>
         </is>
       </c>
-      <c r="E16" s="50" t="n">
+      <c r="E16" s="56" t="n">
         <v>46392</v>
       </c>
-      <c r="F16" s="50" t="n">
+      <c r="F16" s="56" t="n">
         <v>46418</v>
       </c>
-      <c r="G16" s="51" t="n">
+      <c r="G16" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="58">
         <f>IF(D16="","",IF(N(G16)&gt;=1,"Completada",IF(AND(N(F16)&gt;0,F16&lt;TODAY()),"Atrasada",IF(AND(N(E16)&gt;0,E16&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I16" s="53">
+      <c r="I16" s="59">
         <f>IF(OR(D16="",N(F16)=0,N(G16)&gt;=1),"",F16-TODAY())</f>
         <v/>
       </c>
-      <c r="J16" s="54" t="n"/>
-      <c r="K16" s="54" t="n"/>
-      <c r="L16" s="54" t="n"/>
-      <c r="M16" s="54" t="n"/>
-      <c r="N16" s="54" t="n"/>
-      <c r="O16" s="54" t="n"/>
-      <c r="P16" s="54" t="n"/>
-      <c r="Q16" s="54" t="n"/>
-      <c r="R16" s="54" t="n"/>
-      <c r="S16" s="54" t="n"/>
-      <c r="T16" s="54" t="n"/>
-      <c r="U16" s="54" t="n"/>
-      <c r="V16" s="54" t="n"/>
-      <c r="W16" s="54" t="n"/>
-      <c r="X16" s="54" t="n"/>
-      <c r="Y16" s="54" t="n"/>
-      <c r="Z16" s="54" t="n"/>
-      <c r="AA16" s="54" t="n"/>
-      <c r="AB16" s="54" t="n"/>
-      <c r="AC16" s="54" t="n"/>
-      <c r="AD16" s="54" t="n"/>
-      <c r="AE16" s="54" t="n"/>
-      <c r="AF16" s="54" t="n"/>
-      <c r="AG16" s="54" t="n"/>
-      <c r="AH16" s="54" t="n"/>
-      <c r="AI16" s="54" t="n"/>
-      <c r="AJ16" s="54" t="n"/>
-      <c r="AK16" s="54" t="n"/>
-      <c r="AL16" s="54" t="n"/>
-      <c r="AM16" s="54" t="n"/>
-      <c r="AN16" s="54" t="n"/>
-      <c r="AO16" s="54" t="n"/>
-      <c r="AP16" s="54" t="n"/>
-      <c r="AQ16" s="54" t="n"/>
-      <c r="AR16" s="54" t="n"/>
-      <c r="AS16" s="54" t="n"/>
-      <c r="AT16" s="54" t="n"/>
-      <c r="AU16" s="54" t="n"/>
-      <c r="AV16" s="54" t="n"/>
-      <c r="AW16" s="54" t="n"/>
-      <c r="AX16" s="54" t="n"/>
-      <c r="AY16" s="54" t="n"/>
-      <c r="AZ16" s="54" t="n"/>
-      <c r="BA16" s="54" t="n"/>
-      <c r="BB16" s="54" t="n"/>
-      <c r="BC16" s="54" t="n"/>
-      <c r="BD16" s="54" t="n"/>
-      <c r="BE16" s="54" t="n"/>
-      <c r="BF16" s="54" t="n"/>
-      <c r="BG16" s="54" t="n"/>
-      <c r="BH16" s="54" t="n"/>
-      <c r="BI16" s="54" t="n"/>
+      <c r="J16" s="60" t="n"/>
+      <c r="K16" s="60" t="n"/>
+      <c r="L16" s="60" t="n"/>
+      <c r="M16" s="60" t="n"/>
+      <c r="N16" s="60" t="n"/>
+      <c r="O16" s="60" t="n"/>
+      <c r="P16" s="60" t="n"/>
+      <c r="Q16" s="60" t="n"/>
+      <c r="R16" s="60" t="n"/>
+      <c r="S16" s="60" t="n"/>
+      <c r="T16" s="60" t="n"/>
+      <c r="U16" s="60" t="n"/>
+      <c r="V16" s="60" t="n"/>
+      <c r="W16" s="60" t="n"/>
+      <c r="X16" s="60" t="n"/>
+      <c r="Y16" s="60" t="n"/>
+      <c r="Z16" s="60" t="n"/>
+      <c r="AA16" s="60" t="n"/>
+      <c r="AB16" s="60" t="n"/>
+      <c r="AC16" s="60" t="n"/>
+      <c r="AD16" s="60" t="n"/>
+      <c r="AE16" s="60" t="n"/>
+      <c r="AF16" s="60" t="n"/>
+      <c r="AG16" s="60" t="n"/>
+      <c r="AH16" s="60" t="n"/>
+      <c r="AI16" s="60" t="n"/>
+      <c r="AJ16" s="60" t="n"/>
+      <c r="AK16" s="60" t="n"/>
+      <c r="AL16" s="60" t="n"/>
+      <c r="AM16" s="60" t="n"/>
+      <c r="AN16" s="60" t="n"/>
+      <c r="AO16" s="60" t="n"/>
+      <c r="AP16" s="60" t="n"/>
+      <c r="AQ16" s="60" t="n"/>
+      <c r="AR16" s="60" t="n"/>
+      <c r="AS16" s="60" t="n"/>
+      <c r="AT16" s="60" t="n"/>
+      <c r="AU16" s="60" t="n"/>
+      <c r="AV16" s="60" t="n"/>
+      <c r="AW16" s="60" t="n"/>
+      <c r="AX16" s="60" t="n"/>
+      <c r="AY16" s="60" t="n"/>
+      <c r="AZ16" s="60" t="n"/>
+      <c r="BA16" s="60" t="n"/>
+      <c r="BB16" s="60" t="n"/>
+      <c r="BC16" s="60" t="n"/>
+      <c r="BD16" s="60" t="n"/>
+      <c r="BE16" s="60" t="n"/>
+      <c r="BF16" s="60" t="n"/>
+      <c r="BG16" s="60" t="n"/>
+      <c r="BH16" s="60" t="n"/>
+      <c r="BI16" s="60" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="B17" s="48">
+      <c r="B17" s="54">
         <f>IF(D17="","",11)</f>
         <v/>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>Redacción</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="55" t="inlineStr">
         <is>
           <t>Redactar resultados y discusión</t>
         </is>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="56" t="n">
         <v>46402</v>
       </c>
-      <c r="F17" s="50" t="n">
+      <c r="F17" s="56" t="n">
         <v>46446</v>
       </c>
-      <c r="G17" s="51" t="n">
+      <c r="G17" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="58">
         <f>IF(D17="","",IF(N(G17)&gt;=1,"Completada",IF(AND(N(F17)&gt;0,F17&lt;TODAY()),"Atrasada",IF(AND(N(E17)&gt;0,E17&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I17" s="53">
+      <c r="I17" s="59">
         <f>IF(OR(D17="",N(F17)=0,N(G17)&gt;=1),"",F17-TODAY())</f>
         <v/>
       </c>
-      <c r="J17" s="54" t="n"/>
-      <c r="K17" s="54" t="n"/>
-      <c r="L17" s="54" t="n"/>
-      <c r="M17" s="54" t="n"/>
-      <c r="N17" s="54" t="n"/>
-      <c r="O17" s="54" t="n"/>
-      <c r="P17" s="54" t="n"/>
-      <c r="Q17" s="54" t="n"/>
-      <c r="R17" s="54" t="n"/>
-      <c r="S17" s="54" t="n"/>
-      <c r="T17" s="54" t="n"/>
-      <c r="U17" s="54" t="n"/>
-      <c r="V17" s="54" t="n"/>
-      <c r="W17" s="54" t="n"/>
-      <c r="X17" s="54" t="n"/>
-      <c r="Y17" s="54" t="n"/>
-      <c r="Z17" s="54" t="n"/>
-      <c r="AA17" s="54" t="n"/>
-      <c r="AB17" s="54" t="n"/>
-      <c r="AC17" s="54" t="n"/>
-      <c r="AD17" s="54" t="n"/>
-      <c r="AE17" s="54" t="n"/>
-      <c r="AF17" s="54" t="n"/>
-      <c r="AG17" s="54" t="n"/>
-      <c r="AH17" s="54" t="n"/>
-      <c r="AI17" s="54" t="n"/>
-      <c r="AJ17" s="54" t="n"/>
-      <c r="AK17" s="54" t="n"/>
-      <c r="AL17" s="54" t="n"/>
-      <c r="AM17" s="54" t="n"/>
-      <c r="AN17" s="54" t="n"/>
-      <c r="AO17" s="54" t="n"/>
-      <c r="AP17" s="54" t="n"/>
-      <c r="AQ17" s="54" t="n"/>
-      <c r="AR17" s="54" t="n"/>
-      <c r="AS17" s="54" t="n"/>
-      <c r="AT17" s="54" t="n"/>
-      <c r="AU17" s="54" t="n"/>
-      <c r="AV17" s="54" t="n"/>
-      <c r="AW17" s="54" t="n"/>
-      <c r="AX17" s="54" t="n"/>
-      <c r="AY17" s="54" t="n"/>
-      <c r="AZ17" s="54" t="n"/>
-      <c r="BA17" s="54" t="n"/>
-      <c r="BB17" s="54" t="n"/>
-      <c r="BC17" s="54" t="n"/>
-      <c r="BD17" s="54" t="n"/>
-      <c r="BE17" s="54" t="n"/>
-      <c r="BF17" s="54" t="n"/>
-      <c r="BG17" s="54" t="n"/>
-      <c r="BH17" s="54" t="n"/>
-      <c r="BI17" s="54" t="n"/>
+      <c r="J17" s="60" t="n"/>
+      <c r="K17" s="60" t="n"/>
+      <c r="L17" s="60" t="n"/>
+      <c r="M17" s="60" t="n"/>
+      <c r="N17" s="60" t="n"/>
+      <c r="O17" s="60" t="n"/>
+      <c r="P17" s="60" t="n"/>
+      <c r="Q17" s="60" t="n"/>
+      <c r="R17" s="60" t="n"/>
+      <c r="S17" s="60" t="n"/>
+      <c r="T17" s="60" t="n"/>
+      <c r="U17" s="60" t="n"/>
+      <c r="V17" s="60" t="n"/>
+      <c r="W17" s="60" t="n"/>
+      <c r="X17" s="60" t="n"/>
+      <c r="Y17" s="60" t="n"/>
+      <c r="Z17" s="60" t="n"/>
+      <c r="AA17" s="60" t="n"/>
+      <c r="AB17" s="60" t="n"/>
+      <c r="AC17" s="60" t="n"/>
+      <c r="AD17" s="60" t="n"/>
+      <c r="AE17" s="60" t="n"/>
+      <c r="AF17" s="60" t="n"/>
+      <c r="AG17" s="60" t="n"/>
+      <c r="AH17" s="60" t="n"/>
+      <c r="AI17" s="60" t="n"/>
+      <c r="AJ17" s="60" t="n"/>
+      <c r="AK17" s="60" t="n"/>
+      <c r="AL17" s="60" t="n"/>
+      <c r="AM17" s="60" t="n"/>
+      <c r="AN17" s="60" t="n"/>
+      <c r="AO17" s="60" t="n"/>
+      <c r="AP17" s="60" t="n"/>
+      <c r="AQ17" s="60" t="n"/>
+      <c r="AR17" s="60" t="n"/>
+      <c r="AS17" s="60" t="n"/>
+      <c r="AT17" s="60" t="n"/>
+      <c r="AU17" s="60" t="n"/>
+      <c r="AV17" s="60" t="n"/>
+      <c r="AW17" s="60" t="n"/>
+      <c r="AX17" s="60" t="n"/>
+      <c r="AY17" s="60" t="n"/>
+      <c r="AZ17" s="60" t="n"/>
+      <c r="BA17" s="60" t="n"/>
+      <c r="BB17" s="60" t="n"/>
+      <c r="BC17" s="60" t="n"/>
+      <c r="BD17" s="60" t="n"/>
+      <c r="BE17" s="60" t="n"/>
+      <c r="BF17" s="60" t="n"/>
+      <c r="BG17" s="60" t="n"/>
+      <c r="BH17" s="60" t="n"/>
+      <c r="BI17" s="60" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="B18" s="48">
+      <c r="B18" s="54">
         <f>IF(D18="","",12)</f>
         <v/>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
         <is>
           <t>Redacción</t>
         </is>
       </c>
-      <c r="D18" s="49" t="inlineStr">
+      <c r="D18" s="55" t="inlineStr">
         <is>
           <t>Redactar conclusiones</t>
         </is>
       </c>
-      <c r="E18" s="50" t="n">
+      <c r="E18" s="56" t="n">
         <v>46447</v>
       </c>
-      <c r="F18" s="50" t="n">
+      <c r="F18" s="56" t="n">
         <v>46461</v>
       </c>
-      <c r="G18" s="51" t="n">
+      <c r="G18" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="58">
         <f>IF(D18="","",IF(N(G18)&gt;=1,"Completada",IF(AND(N(F18)&gt;0,F18&lt;TODAY()),"Atrasada",IF(AND(N(E18)&gt;0,E18&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="59">
         <f>IF(OR(D18="",N(F18)=0,N(G18)&gt;=1),"",F18-TODAY())</f>
         <v/>
       </c>
-      <c r="J18" s="54" t="n"/>
-      <c r="K18" s="54" t="n"/>
-      <c r="L18" s="54" t="n"/>
-      <c r="M18" s="54" t="n"/>
-      <c r="N18" s="54" t="n"/>
-      <c r="O18" s="54" t="n"/>
-      <c r="P18" s="54" t="n"/>
-      <c r="Q18" s="54" t="n"/>
-      <c r="R18" s="54" t="n"/>
-      <c r="S18" s="54" t="n"/>
-      <c r="T18" s="54" t="n"/>
-      <c r="U18" s="54" t="n"/>
-      <c r="V18" s="54" t="n"/>
-      <c r="W18" s="54" t="n"/>
-      <c r="X18" s="54" t="n"/>
-      <c r="Y18" s="54" t="n"/>
-      <c r="Z18" s="54" t="n"/>
-      <c r="AA18" s="54" t="n"/>
-      <c r="AB18" s="54" t="n"/>
-      <c r="AC18" s="54" t="n"/>
-      <c r="AD18" s="54" t="n"/>
-      <c r="AE18" s="54" t="n"/>
-      <c r="AF18" s="54" t="n"/>
-      <c r="AG18" s="54" t="n"/>
-      <c r="AH18" s="54" t="n"/>
-      <c r="AI18" s="54" t="n"/>
-      <c r="AJ18" s="54" t="n"/>
-      <c r="AK18" s="54" t="n"/>
-      <c r="AL18" s="54" t="n"/>
-      <c r="AM18" s="54" t="n"/>
-      <c r="AN18" s="54" t="n"/>
-      <c r="AO18" s="54" t="n"/>
-      <c r="AP18" s="54" t="n"/>
-      <c r="AQ18" s="54" t="n"/>
-      <c r="AR18" s="54" t="n"/>
-      <c r="AS18" s="54" t="n"/>
-      <c r="AT18" s="54" t="n"/>
-      <c r="AU18" s="54" t="n"/>
-      <c r="AV18" s="54" t="n"/>
-      <c r="AW18" s="54" t="n"/>
-      <c r="AX18" s="54" t="n"/>
-      <c r="AY18" s="54" t="n"/>
-      <c r="AZ18" s="54" t="n"/>
-      <c r="BA18" s="54" t="n"/>
-      <c r="BB18" s="54" t="n"/>
-      <c r="BC18" s="54" t="n"/>
-      <c r="BD18" s="54" t="n"/>
-      <c r="BE18" s="54" t="n"/>
-      <c r="BF18" s="54" t="n"/>
-      <c r="BG18" s="54" t="n"/>
-      <c r="BH18" s="54" t="n"/>
-      <c r="BI18" s="54" t="n"/>
+      <c r="J18" s="60" t="n"/>
+      <c r="K18" s="60" t="n"/>
+      <c r="L18" s="60" t="n"/>
+      <c r="M18" s="60" t="n"/>
+      <c r="N18" s="60" t="n"/>
+      <c r="O18" s="60" t="n"/>
+      <c r="P18" s="60" t="n"/>
+      <c r="Q18" s="60" t="n"/>
+      <c r="R18" s="60" t="n"/>
+      <c r="S18" s="60" t="n"/>
+      <c r="T18" s="60" t="n"/>
+      <c r="U18" s="60" t="n"/>
+      <c r="V18" s="60" t="n"/>
+      <c r="W18" s="60" t="n"/>
+      <c r="X18" s="60" t="n"/>
+      <c r="Y18" s="60" t="n"/>
+      <c r="Z18" s="60" t="n"/>
+      <c r="AA18" s="60" t="n"/>
+      <c r="AB18" s="60" t="n"/>
+      <c r="AC18" s="60" t="n"/>
+      <c r="AD18" s="60" t="n"/>
+      <c r="AE18" s="60" t="n"/>
+      <c r="AF18" s="60" t="n"/>
+      <c r="AG18" s="60" t="n"/>
+      <c r="AH18" s="60" t="n"/>
+      <c r="AI18" s="60" t="n"/>
+      <c r="AJ18" s="60" t="n"/>
+      <c r="AK18" s="60" t="n"/>
+      <c r="AL18" s="60" t="n"/>
+      <c r="AM18" s="60" t="n"/>
+      <c r="AN18" s="60" t="n"/>
+      <c r="AO18" s="60" t="n"/>
+      <c r="AP18" s="60" t="n"/>
+      <c r="AQ18" s="60" t="n"/>
+      <c r="AR18" s="60" t="n"/>
+      <c r="AS18" s="60" t="n"/>
+      <c r="AT18" s="60" t="n"/>
+      <c r="AU18" s="60" t="n"/>
+      <c r="AV18" s="60" t="n"/>
+      <c r="AW18" s="60" t="n"/>
+      <c r="AX18" s="60" t="n"/>
+      <c r="AY18" s="60" t="n"/>
+      <c r="AZ18" s="60" t="n"/>
+      <c r="BA18" s="60" t="n"/>
+      <c r="BB18" s="60" t="n"/>
+      <c r="BC18" s="60" t="n"/>
+      <c r="BD18" s="60" t="n"/>
+      <c r="BE18" s="60" t="n"/>
+      <c r="BF18" s="60" t="n"/>
+      <c r="BG18" s="60" t="n"/>
+      <c r="BH18" s="60" t="n"/>
+      <c r="BI18" s="60" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="48">
+      <c r="B19" s="54">
         <f>IF(D19="","",13)</f>
         <v/>
       </c>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>Redacción</t>
         </is>
       </c>
-      <c r="D19" s="49" t="inlineStr">
+      <c r="D19" s="55" t="inlineStr">
         <is>
           <t>Introducción y resumen</t>
         </is>
       </c>
-      <c r="E19" s="50" t="n">
+      <c r="E19" s="56" t="n">
         <v>46456</v>
       </c>
-      <c r="F19" s="50" t="n">
+      <c r="F19" s="56" t="n">
         <v>46471</v>
       </c>
-      <c r="G19" s="51" t="n">
+      <c r="G19" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="58">
         <f>IF(D19="","",IF(N(G19)&gt;=1,"Completada",IF(AND(N(F19)&gt;0,F19&lt;TODAY()),"Atrasada",IF(AND(N(E19)&gt;0,E19&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I19" s="53">
+      <c r="I19" s="59">
         <f>IF(OR(D19="",N(F19)=0,N(G19)&gt;=1),"",F19-TODAY())</f>
         <v/>
       </c>
-      <c r="J19" s="54" t="n"/>
-      <c r="K19" s="54" t="n"/>
-      <c r="L19" s="54" t="n"/>
-      <c r="M19" s="54" t="n"/>
-      <c r="N19" s="54" t="n"/>
-      <c r="O19" s="54" t="n"/>
-      <c r="P19" s="54" t="n"/>
-      <c r="Q19" s="54" t="n"/>
-      <c r="R19" s="54" t="n"/>
-      <c r="S19" s="54" t="n"/>
-      <c r="T19" s="54" t="n"/>
-      <c r="U19" s="54" t="n"/>
-      <c r="V19" s="54" t="n"/>
-      <c r="W19" s="54" t="n"/>
-      <c r="X19" s="54" t="n"/>
-      <c r="Y19" s="54" t="n"/>
-      <c r="Z19" s="54" t="n"/>
-      <c r="AA19" s="54" t="n"/>
-      <c r="AB19" s="54" t="n"/>
-      <c r="AC19" s="54" t="n"/>
-      <c r="AD19" s="54" t="n"/>
-      <c r="AE19" s="54" t="n"/>
-      <c r="AF19" s="54" t="n"/>
-      <c r="AG19" s="54" t="n"/>
-      <c r="AH19" s="54" t="n"/>
-      <c r="AI19" s="54" t="n"/>
-      <c r="AJ19" s="54" t="n"/>
-      <c r="AK19" s="54" t="n"/>
-      <c r="AL19" s="54" t="n"/>
-      <c r="AM19" s="54" t="n"/>
-      <c r="AN19" s="54" t="n"/>
-      <c r="AO19" s="54" t="n"/>
-      <c r="AP19" s="54" t="n"/>
-      <c r="AQ19" s="54" t="n"/>
-      <c r="AR19" s="54" t="n"/>
-      <c r="AS19" s="54" t="n"/>
-      <c r="AT19" s="54" t="n"/>
-      <c r="AU19" s="54" t="n"/>
-      <c r="AV19" s="54" t="n"/>
-      <c r="AW19" s="54" t="n"/>
-      <c r="AX19" s="54" t="n"/>
-      <c r="AY19" s="54" t="n"/>
-      <c r="AZ19" s="54" t="n"/>
-      <c r="BA19" s="54" t="n"/>
-      <c r="BB19" s="54" t="n"/>
-      <c r="BC19" s="54" t="n"/>
-      <c r="BD19" s="54" t="n"/>
-      <c r="BE19" s="54" t="n"/>
-      <c r="BF19" s="54" t="n"/>
-      <c r="BG19" s="54" t="n"/>
-      <c r="BH19" s="54" t="n"/>
-      <c r="BI19" s="54" t="n"/>
+      <c r="J19" s="60" t="n"/>
+      <c r="K19" s="60" t="n"/>
+      <c r="L19" s="60" t="n"/>
+      <c r="M19" s="60" t="n"/>
+      <c r="N19" s="60" t="n"/>
+      <c r="O19" s="60" t="n"/>
+      <c r="P19" s="60" t="n"/>
+      <c r="Q19" s="60" t="n"/>
+      <c r="R19" s="60" t="n"/>
+      <c r="S19" s="60" t="n"/>
+      <c r="T19" s="60" t="n"/>
+      <c r="U19" s="60" t="n"/>
+      <c r="V19" s="60" t="n"/>
+      <c r="W19" s="60" t="n"/>
+      <c r="X19" s="60" t="n"/>
+      <c r="Y19" s="60" t="n"/>
+      <c r="Z19" s="60" t="n"/>
+      <c r="AA19" s="60" t="n"/>
+      <c r="AB19" s="60" t="n"/>
+      <c r="AC19" s="60" t="n"/>
+      <c r="AD19" s="60" t="n"/>
+      <c r="AE19" s="60" t="n"/>
+      <c r="AF19" s="60" t="n"/>
+      <c r="AG19" s="60" t="n"/>
+      <c r="AH19" s="60" t="n"/>
+      <c r="AI19" s="60" t="n"/>
+      <c r="AJ19" s="60" t="n"/>
+      <c r="AK19" s="60" t="n"/>
+      <c r="AL19" s="60" t="n"/>
+      <c r="AM19" s="60" t="n"/>
+      <c r="AN19" s="60" t="n"/>
+      <c r="AO19" s="60" t="n"/>
+      <c r="AP19" s="60" t="n"/>
+      <c r="AQ19" s="60" t="n"/>
+      <c r="AR19" s="60" t="n"/>
+      <c r="AS19" s="60" t="n"/>
+      <c r="AT19" s="60" t="n"/>
+      <c r="AU19" s="60" t="n"/>
+      <c r="AV19" s="60" t="n"/>
+      <c r="AW19" s="60" t="n"/>
+      <c r="AX19" s="60" t="n"/>
+      <c r="AY19" s="60" t="n"/>
+      <c r="AZ19" s="60" t="n"/>
+      <c r="BA19" s="60" t="n"/>
+      <c r="BB19" s="60" t="n"/>
+      <c r="BC19" s="60" t="n"/>
+      <c r="BD19" s="60" t="n"/>
+      <c r="BE19" s="60" t="n"/>
+      <c r="BF19" s="60" t="n"/>
+      <c r="BG19" s="60" t="n"/>
+      <c r="BH19" s="60" t="n"/>
+      <c r="BI19" s="60" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="48">
+      <c r="B20" s="54">
         <f>IF(D20="","",14)</f>
         <v/>
       </c>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>Revisión del tutor</t>
         </is>
       </c>
-      <c r="D20" s="49" t="inlineStr">
+      <c r="D20" s="55" t="inlineStr">
         <is>
           <t>Revisión del borrador completo</t>
         </is>
       </c>
-      <c r="E20" s="50" t="n">
+      <c r="E20" s="56" t="n">
         <v>46462</v>
       </c>
-      <c r="F20" s="50" t="n">
+      <c r="F20" s="56" t="n">
         <v>46477</v>
       </c>
-      <c r="G20" s="51" t="n">
+      <c r="G20" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="58">
         <f>IF(D20="","",IF(N(G20)&gt;=1,"Completada",IF(AND(N(F20)&gt;0,F20&lt;TODAY()),"Atrasada",IF(AND(N(E20)&gt;0,E20&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I20" s="53">
+      <c r="I20" s="59">
         <f>IF(OR(D20="",N(F20)=0,N(G20)&gt;=1),"",F20-TODAY())</f>
         <v/>
       </c>
-      <c r="J20" s="54" t="n"/>
-      <c r="K20" s="54" t="n"/>
-      <c r="L20" s="54" t="n"/>
-      <c r="M20" s="54" t="n"/>
-      <c r="N20" s="54" t="n"/>
-      <c r="O20" s="54" t="n"/>
-      <c r="P20" s="54" t="n"/>
-      <c r="Q20" s="54" t="n"/>
-      <c r="R20" s="54" t="n"/>
-      <c r="S20" s="54" t="n"/>
-      <c r="T20" s="54" t="n"/>
-      <c r="U20" s="54" t="n"/>
-      <c r="V20" s="54" t="n"/>
-      <c r="W20" s="54" t="n"/>
-      <c r="X20" s="54" t="n"/>
-      <c r="Y20" s="54" t="n"/>
-      <c r="Z20" s="54" t="n"/>
-      <c r="AA20" s="54" t="n"/>
-      <c r="AB20" s="54" t="n"/>
-      <c r="AC20" s="54" t="n"/>
-      <c r="AD20" s="54" t="n"/>
-      <c r="AE20" s="54" t="n"/>
-      <c r="AF20" s="54" t="n"/>
-      <c r="AG20" s="54" t="n"/>
-      <c r="AH20" s="54" t="n"/>
-      <c r="AI20" s="54" t="n"/>
-      <c r="AJ20" s="54" t="n"/>
-      <c r="AK20" s="54" t="n"/>
-      <c r="AL20" s="54" t="n"/>
-      <c r="AM20" s="54" t="n"/>
-      <c r="AN20" s="54" t="n"/>
-      <c r="AO20" s="54" t="n"/>
-      <c r="AP20" s="54" t="n"/>
-      <c r="AQ20" s="54" t="n"/>
-      <c r="AR20" s="54" t="n"/>
-      <c r="AS20" s="54" t="n"/>
-      <c r="AT20" s="54" t="n"/>
-      <c r="AU20" s="54" t="n"/>
-      <c r="AV20" s="54" t="n"/>
-      <c r="AW20" s="54" t="n"/>
-      <c r="AX20" s="54" t="n"/>
-      <c r="AY20" s="54" t="n"/>
-      <c r="AZ20" s="54" t="n"/>
-      <c r="BA20" s="54" t="n"/>
-      <c r="BB20" s="54" t="n"/>
-      <c r="BC20" s="54" t="n"/>
-      <c r="BD20" s="54" t="n"/>
-      <c r="BE20" s="54" t="n"/>
-      <c r="BF20" s="54" t="n"/>
-      <c r="BG20" s="54" t="n"/>
-      <c r="BH20" s="54" t="n"/>
-      <c r="BI20" s="54" t="n"/>
+      <c r="J20" s="60" t="n"/>
+      <c r="K20" s="60" t="n"/>
+      <c r="L20" s="60" t="n"/>
+      <c r="M20" s="60" t="n"/>
+      <c r="N20" s="60" t="n"/>
+      <c r="O20" s="60" t="n"/>
+      <c r="P20" s="60" t="n"/>
+      <c r="Q20" s="60" t="n"/>
+      <c r="R20" s="60" t="n"/>
+      <c r="S20" s="60" t="n"/>
+      <c r="T20" s="60" t="n"/>
+      <c r="U20" s="60" t="n"/>
+      <c r="V20" s="60" t="n"/>
+      <c r="W20" s="60" t="n"/>
+      <c r="X20" s="60" t="n"/>
+      <c r="Y20" s="60" t="n"/>
+      <c r="Z20" s="60" t="n"/>
+      <c r="AA20" s="60" t="n"/>
+      <c r="AB20" s="60" t="n"/>
+      <c r="AC20" s="60" t="n"/>
+      <c r="AD20" s="60" t="n"/>
+      <c r="AE20" s="60" t="n"/>
+      <c r="AF20" s="60" t="n"/>
+      <c r="AG20" s="60" t="n"/>
+      <c r="AH20" s="60" t="n"/>
+      <c r="AI20" s="60" t="n"/>
+      <c r="AJ20" s="60" t="n"/>
+      <c r="AK20" s="60" t="n"/>
+      <c r="AL20" s="60" t="n"/>
+      <c r="AM20" s="60" t="n"/>
+      <c r="AN20" s="60" t="n"/>
+      <c r="AO20" s="60" t="n"/>
+      <c r="AP20" s="60" t="n"/>
+      <c r="AQ20" s="60" t="n"/>
+      <c r="AR20" s="60" t="n"/>
+      <c r="AS20" s="60" t="n"/>
+      <c r="AT20" s="60" t="n"/>
+      <c r="AU20" s="60" t="n"/>
+      <c r="AV20" s="60" t="n"/>
+      <c r="AW20" s="60" t="n"/>
+      <c r="AX20" s="60" t="n"/>
+      <c r="AY20" s="60" t="n"/>
+      <c r="AZ20" s="60" t="n"/>
+      <c r="BA20" s="60" t="n"/>
+      <c r="BB20" s="60" t="n"/>
+      <c r="BC20" s="60" t="n"/>
+      <c r="BD20" s="60" t="n"/>
+      <c r="BE20" s="60" t="n"/>
+      <c r="BF20" s="60" t="n"/>
+      <c r="BG20" s="60" t="n"/>
+      <c r="BH20" s="60" t="n"/>
+      <c r="BI20" s="60" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="48">
+      <c r="B21" s="54">
         <f>IF(D21="","",15)</f>
         <v/>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>Revisión del tutor</t>
         </is>
       </c>
-      <c r="D21" s="49" t="inlineStr">
+      <c r="D21" s="55" t="inlineStr">
         <is>
           <t>Hacer las correcciones</t>
         </is>
       </c>
-      <c r="E21" s="50" t="n">
+      <c r="E21" s="56" t="n">
         <v>46478</v>
       </c>
-      <c r="F21" s="50" t="n">
+      <c r="F21" s="56" t="n">
         <v>46487</v>
       </c>
-      <c r="G21" s="51" t="n">
+      <c r="G21" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="58">
         <f>IF(D21="","",IF(N(G21)&gt;=1,"Completada",IF(AND(N(F21)&gt;0,F21&lt;TODAY()),"Atrasada",IF(AND(N(E21)&gt;0,E21&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I21" s="53">
+      <c r="I21" s="59">
         <f>IF(OR(D21="",N(F21)=0,N(G21)&gt;=1),"",F21-TODAY())</f>
         <v/>
       </c>
-      <c r="J21" s="54" t="n"/>
-      <c r="K21" s="54" t="n"/>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="54" t="n"/>
-      <c r="O21" s="54" t="n"/>
-      <c r="P21" s="54" t="n"/>
-      <c r="Q21" s="54" t="n"/>
-      <c r="R21" s="54" t="n"/>
-      <c r="S21" s="54" t="n"/>
-      <c r="T21" s="54" t="n"/>
-      <c r="U21" s="54" t="n"/>
-      <c r="V21" s="54" t="n"/>
-      <c r="W21" s="54" t="n"/>
-      <c r="X21" s="54" t="n"/>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="54" t="n"/>
-      <c r="AG21" s="54" t="n"/>
-      <c r="AH21" s="54" t="n"/>
-      <c r="AI21" s="54" t="n"/>
-      <c r="AJ21" s="54" t="n"/>
-      <c r="AK21" s="54" t="n"/>
-      <c r="AL21" s="54" t="n"/>
-      <c r="AM21" s="54" t="n"/>
-      <c r="AN21" s="54" t="n"/>
-      <c r="AO21" s="54" t="n"/>
-      <c r="AP21" s="54" t="n"/>
-      <c r="AQ21" s="54" t="n"/>
-      <c r="AR21" s="54" t="n"/>
-      <c r="AS21" s="54" t="n"/>
-      <c r="AT21" s="54" t="n"/>
-      <c r="AU21" s="54" t="n"/>
-      <c r="AV21" s="54" t="n"/>
-      <c r="AW21" s="54" t="n"/>
-      <c r="AX21" s="54" t="n"/>
-      <c r="AY21" s="54" t="n"/>
-      <c r="AZ21" s="54" t="n"/>
-      <c r="BA21" s="54" t="n"/>
-      <c r="BB21" s="54" t="n"/>
-      <c r="BC21" s="54" t="n"/>
-      <c r="BD21" s="54" t="n"/>
-      <c r="BE21" s="54" t="n"/>
-      <c r="BF21" s="54" t="n"/>
-      <c r="BG21" s="54" t="n"/>
-      <c r="BH21" s="54" t="n"/>
-      <c r="BI21" s="54" t="n"/>
+      <c r="J21" s="60" t="n"/>
+      <c r="K21" s="60" t="n"/>
+      <c r="L21" s="60" t="n"/>
+      <c r="M21" s="60" t="n"/>
+      <c r="N21" s="60" t="n"/>
+      <c r="O21" s="60" t="n"/>
+      <c r="P21" s="60" t="n"/>
+      <c r="Q21" s="60" t="n"/>
+      <c r="R21" s="60" t="n"/>
+      <c r="S21" s="60" t="n"/>
+      <c r="T21" s="60" t="n"/>
+      <c r="U21" s="60" t="n"/>
+      <c r="V21" s="60" t="n"/>
+      <c r="W21" s="60" t="n"/>
+      <c r="X21" s="60" t="n"/>
+      <c r="Y21" s="60" t="n"/>
+      <c r="Z21" s="60" t="n"/>
+      <c r="AA21" s="60" t="n"/>
+      <c r="AB21" s="60" t="n"/>
+      <c r="AC21" s="60" t="n"/>
+      <c r="AD21" s="60" t="n"/>
+      <c r="AE21" s="60" t="n"/>
+      <c r="AF21" s="60" t="n"/>
+      <c r="AG21" s="60" t="n"/>
+      <c r="AH21" s="60" t="n"/>
+      <c r="AI21" s="60" t="n"/>
+      <c r="AJ21" s="60" t="n"/>
+      <c r="AK21" s="60" t="n"/>
+      <c r="AL21" s="60" t="n"/>
+      <c r="AM21" s="60" t="n"/>
+      <c r="AN21" s="60" t="n"/>
+      <c r="AO21" s="60" t="n"/>
+      <c r="AP21" s="60" t="n"/>
+      <c r="AQ21" s="60" t="n"/>
+      <c r="AR21" s="60" t="n"/>
+      <c r="AS21" s="60" t="n"/>
+      <c r="AT21" s="60" t="n"/>
+      <c r="AU21" s="60" t="n"/>
+      <c r="AV21" s="60" t="n"/>
+      <c r="AW21" s="60" t="n"/>
+      <c r="AX21" s="60" t="n"/>
+      <c r="AY21" s="60" t="n"/>
+      <c r="AZ21" s="60" t="n"/>
+      <c r="BA21" s="60" t="n"/>
+      <c r="BB21" s="60" t="n"/>
+      <c r="BC21" s="60" t="n"/>
+      <c r="BD21" s="60" t="n"/>
+      <c r="BE21" s="60" t="n"/>
+      <c r="BF21" s="60" t="n"/>
+      <c r="BG21" s="60" t="n"/>
+      <c r="BH21" s="60" t="n"/>
+      <c r="BI21" s="60" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="B22" s="48">
+      <c r="B22" s="54">
         <f>IF(D22="","",16)</f>
         <v/>
       </c>
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="55" t="inlineStr">
         <is>
           <t>Formato y entrega</t>
         </is>
       </c>
-      <c r="D22" s="49" t="inlineStr">
+      <c r="D22" s="55" t="inlineStr">
         <is>
           <t>Formato, citas y referencias</t>
         </is>
       </c>
-      <c r="E22" s="50" t="n">
+      <c r="E22" s="56" t="n">
         <v>46478</v>
       </c>
-      <c r="F22" s="50" t="n">
+      <c r="F22" s="56" t="n">
         <v>46492</v>
       </c>
-      <c r="G22" s="51" t="n">
+      <c r="G22" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="58">
         <f>IF(D22="","",IF(N(G22)&gt;=1,"Completada",IF(AND(N(F22)&gt;0,F22&lt;TODAY()),"Atrasada",IF(AND(N(E22)&gt;0,E22&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I22" s="53">
+      <c r="I22" s="59">
         <f>IF(OR(D22="",N(F22)=0,N(G22)&gt;=1),"",F22-TODAY())</f>
         <v/>
       </c>
-      <c r="J22" s="54" t="n"/>
-      <c r="K22" s="54" t="n"/>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="54" t="n"/>
-      <c r="O22" s="54" t="n"/>
-      <c r="P22" s="54" t="n"/>
-      <c r="Q22" s="54" t="n"/>
-      <c r="R22" s="54" t="n"/>
-      <c r="S22" s="54" t="n"/>
-      <c r="T22" s="54" t="n"/>
-      <c r="U22" s="54" t="n"/>
-      <c r="V22" s="54" t="n"/>
-      <c r="W22" s="54" t="n"/>
-      <c r="X22" s="54" t="n"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="54" t="n"/>
-      <c r="AG22" s="54" t="n"/>
-      <c r="AH22" s="54" t="n"/>
-      <c r="AI22" s="54" t="n"/>
-      <c r="AJ22" s="54" t="n"/>
-      <c r="AK22" s="54" t="n"/>
-      <c r="AL22" s="54" t="n"/>
-      <c r="AM22" s="54" t="n"/>
-      <c r="AN22" s="54" t="n"/>
-      <c r="AO22" s="54" t="n"/>
-      <c r="AP22" s="54" t="n"/>
-      <c r="AQ22" s="54" t="n"/>
-      <c r="AR22" s="54" t="n"/>
-      <c r="AS22" s="54" t="n"/>
-      <c r="AT22" s="54" t="n"/>
-      <c r="AU22" s="54" t="n"/>
-      <c r="AV22" s="54" t="n"/>
-      <c r="AW22" s="54" t="n"/>
-      <c r="AX22" s="54" t="n"/>
-      <c r="AY22" s="54" t="n"/>
-      <c r="AZ22" s="54" t="n"/>
-      <c r="BA22" s="54" t="n"/>
-      <c r="BB22" s="54" t="n"/>
-      <c r="BC22" s="54" t="n"/>
-      <c r="BD22" s="54" t="n"/>
-      <c r="BE22" s="54" t="n"/>
-      <c r="BF22" s="54" t="n"/>
-      <c r="BG22" s="54" t="n"/>
-      <c r="BH22" s="54" t="n"/>
-      <c r="BI22" s="54" t="n"/>
+      <c r="J22" s="60" t="n"/>
+      <c r="K22" s="60" t="n"/>
+      <c r="L22" s="60" t="n"/>
+      <c r="M22" s="60" t="n"/>
+      <c r="N22" s="60" t="n"/>
+      <c r="O22" s="60" t="n"/>
+      <c r="P22" s="60" t="n"/>
+      <c r="Q22" s="60" t="n"/>
+      <c r="R22" s="60" t="n"/>
+      <c r="S22" s="60" t="n"/>
+      <c r="T22" s="60" t="n"/>
+      <c r="U22" s="60" t="n"/>
+      <c r="V22" s="60" t="n"/>
+      <c r="W22" s="60" t="n"/>
+      <c r="X22" s="60" t="n"/>
+      <c r="Y22" s="60" t="n"/>
+      <c r="Z22" s="60" t="n"/>
+      <c r="AA22" s="60" t="n"/>
+      <c r="AB22" s="60" t="n"/>
+      <c r="AC22" s="60" t="n"/>
+      <c r="AD22" s="60" t="n"/>
+      <c r="AE22" s="60" t="n"/>
+      <c r="AF22" s="60" t="n"/>
+      <c r="AG22" s="60" t="n"/>
+      <c r="AH22" s="60" t="n"/>
+      <c r="AI22" s="60" t="n"/>
+      <c r="AJ22" s="60" t="n"/>
+      <c r="AK22" s="60" t="n"/>
+      <c r="AL22" s="60" t="n"/>
+      <c r="AM22" s="60" t="n"/>
+      <c r="AN22" s="60" t="n"/>
+      <c r="AO22" s="60" t="n"/>
+      <c r="AP22" s="60" t="n"/>
+      <c r="AQ22" s="60" t="n"/>
+      <c r="AR22" s="60" t="n"/>
+      <c r="AS22" s="60" t="n"/>
+      <c r="AT22" s="60" t="n"/>
+      <c r="AU22" s="60" t="n"/>
+      <c r="AV22" s="60" t="n"/>
+      <c r="AW22" s="60" t="n"/>
+      <c r="AX22" s="60" t="n"/>
+      <c r="AY22" s="60" t="n"/>
+      <c r="AZ22" s="60" t="n"/>
+      <c r="BA22" s="60" t="n"/>
+      <c r="BB22" s="60" t="n"/>
+      <c r="BC22" s="60" t="n"/>
+      <c r="BD22" s="60" t="n"/>
+      <c r="BE22" s="60" t="n"/>
+      <c r="BF22" s="60" t="n"/>
+      <c r="BG22" s="60" t="n"/>
+      <c r="BH22" s="60" t="n"/>
+      <c r="BI22" s="60" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="B23" s="48">
+      <c r="B23" s="54">
         <f>IF(D23="","",17)</f>
         <v/>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>Formato y entrega</t>
         </is>
       </c>
-      <c r="D23" s="49" t="inlineStr">
+      <c r="D23" s="55" t="inlineStr">
         <is>
           <t>Entregar las copias</t>
         </is>
       </c>
-      <c r="E23" s="50" t="n">
+      <c r="E23" s="56" t="n">
         <v>46493</v>
       </c>
-      <c r="F23" s="50" t="n">
+      <c r="F23" s="56" t="n">
         <v>46497</v>
       </c>
-      <c r="G23" s="51" t="n">
+      <c r="G23" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="58">
         <f>IF(D23="","",IF(N(G23)&gt;=1,"Completada",IF(AND(N(F23)&gt;0,F23&lt;TODAY()),"Atrasada",IF(AND(N(E23)&gt;0,E23&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I23" s="53">
+      <c r="I23" s="59">
         <f>IF(OR(D23="",N(F23)=0,N(G23)&gt;=1),"",F23-TODAY())</f>
         <v/>
       </c>
-      <c r="J23" s="54" t="n"/>
-      <c r="K23" s="54" t="n"/>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="54" t="n"/>
-      <c r="O23" s="54" t="n"/>
-      <c r="P23" s="54" t="n"/>
-      <c r="Q23" s="54" t="n"/>
-      <c r="R23" s="54" t="n"/>
-      <c r="S23" s="54" t="n"/>
-      <c r="T23" s="54" t="n"/>
-      <c r="U23" s="54" t="n"/>
-      <c r="V23" s="54" t="n"/>
-      <c r="W23" s="54" t="n"/>
-      <c r="X23" s="54" t="n"/>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="54" t="n"/>
-      <c r="AG23" s="54" t="n"/>
-      <c r="AH23" s="54" t="n"/>
-      <c r="AI23" s="54" t="n"/>
-      <c r="AJ23" s="54" t="n"/>
-      <c r="AK23" s="54" t="n"/>
-      <c r="AL23" s="54" t="n"/>
-      <c r="AM23" s="54" t="n"/>
-      <c r="AN23" s="54" t="n"/>
-      <c r="AO23" s="54" t="n"/>
-      <c r="AP23" s="54" t="n"/>
-      <c r="AQ23" s="54" t="n"/>
-      <c r="AR23" s="54" t="n"/>
-      <c r="AS23" s="54" t="n"/>
-      <c r="AT23" s="54" t="n"/>
-      <c r="AU23" s="54" t="n"/>
-      <c r="AV23" s="54" t="n"/>
-      <c r="AW23" s="54" t="n"/>
-      <c r="AX23" s="54" t="n"/>
-      <c r="AY23" s="54" t="n"/>
-      <c r="AZ23" s="54" t="n"/>
-      <c r="BA23" s="54" t="n"/>
-      <c r="BB23" s="54" t="n"/>
-      <c r="BC23" s="54" t="n"/>
-      <c r="BD23" s="54" t="n"/>
-      <c r="BE23" s="54" t="n"/>
-      <c r="BF23" s="54" t="n"/>
-      <c r="BG23" s="54" t="n"/>
-      <c r="BH23" s="54" t="n"/>
-      <c r="BI23" s="54" t="n"/>
+      <c r="J23" s="60" t="n"/>
+      <c r="K23" s="60" t="n"/>
+      <c r="L23" s="60" t="n"/>
+      <c r="M23" s="60" t="n"/>
+      <c r="N23" s="60" t="n"/>
+      <c r="O23" s="60" t="n"/>
+      <c r="P23" s="60" t="n"/>
+      <c r="Q23" s="60" t="n"/>
+      <c r="R23" s="60" t="n"/>
+      <c r="S23" s="60" t="n"/>
+      <c r="T23" s="60" t="n"/>
+      <c r="U23" s="60" t="n"/>
+      <c r="V23" s="60" t="n"/>
+      <c r="W23" s="60" t="n"/>
+      <c r="X23" s="60" t="n"/>
+      <c r="Y23" s="60" t="n"/>
+      <c r="Z23" s="60" t="n"/>
+      <c r="AA23" s="60" t="n"/>
+      <c r="AB23" s="60" t="n"/>
+      <c r="AC23" s="60" t="n"/>
+      <c r="AD23" s="60" t="n"/>
+      <c r="AE23" s="60" t="n"/>
+      <c r="AF23" s="60" t="n"/>
+      <c r="AG23" s="60" t="n"/>
+      <c r="AH23" s="60" t="n"/>
+      <c r="AI23" s="60" t="n"/>
+      <c r="AJ23" s="60" t="n"/>
+      <c r="AK23" s="60" t="n"/>
+      <c r="AL23" s="60" t="n"/>
+      <c r="AM23" s="60" t="n"/>
+      <c r="AN23" s="60" t="n"/>
+      <c r="AO23" s="60" t="n"/>
+      <c r="AP23" s="60" t="n"/>
+      <c r="AQ23" s="60" t="n"/>
+      <c r="AR23" s="60" t="n"/>
+      <c r="AS23" s="60" t="n"/>
+      <c r="AT23" s="60" t="n"/>
+      <c r="AU23" s="60" t="n"/>
+      <c r="AV23" s="60" t="n"/>
+      <c r="AW23" s="60" t="n"/>
+      <c r="AX23" s="60" t="n"/>
+      <c r="AY23" s="60" t="n"/>
+      <c r="AZ23" s="60" t="n"/>
+      <c r="BA23" s="60" t="n"/>
+      <c r="BB23" s="60" t="n"/>
+      <c r="BC23" s="60" t="n"/>
+      <c r="BD23" s="60" t="n"/>
+      <c r="BE23" s="60" t="n"/>
+      <c r="BF23" s="60" t="n"/>
+      <c r="BG23" s="60" t="n"/>
+      <c r="BH23" s="60" t="n"/>
+      <c r="BI23" s="60" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="B24" s="48">
+      <c r="B24" s="54">
         <f>IF(D24="","",18)</f>
         <v/>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>Defensa</t>
         </is>
       </c>
-      <c r="D24" s="49" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>Preparar la presentación</t>
         </is>
       </c>
-      <c r="E24" s="50" t="n">
+      <c r="E24" s="56" t="n">
         <v>46487</v>
       </c>
-      <c r="F24" s="50" t="n">
+      <c r="F24" s="56" t="n">
         <v>46502</v>
       </c>
-      <c r="G24" s="51" t="n">
+      <c r="G24" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="58">
         <f>IF(D24="","",IF(N(G24)&gt;=1,"Completada",IF(AND(N(F24)&gt;0,F24&lt;TODAY()),"Atrasada",IF(AND(N(E24)&gt;0,E24&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I24" s="53">
+      <c r="I24" s="59">
         <f>IF(OR(D24="",N(F24)=0,N(G24)&gt;=1),"",F24-TODAY())</f>
         <v/>
       </c>
-      <c r="J24" s="54" t="n"/>
-      <c r="K24" s="54" t="n"/>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="54" t="n"/>
-      <c r="O24" s="54" t="n"/>
-      <c r="P24" s="54" t="n"/>
-      <c r="Q24" s="54" t="n"/>
-      <c r="R24" s="54" t="n"/>
-      <c r="S24" s="54" t="n"/>
-      <c r="T24" s="54" t="n"/>
-      <c r="U24" s="54" t="n"/>
-      <c r="V24" s="54" t="n"/>
-      <c r="W24" s="54" t="n"/>
-      <c r="X24" s="54" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="54" t="n"/>
-      <c r="AG24" s="54" t="n"/>
-      <c r="AH24" s="54" t="n"/>
-      <c r="AI24" s="54" t="n"/>
-      <c r="AJ24" s="54" t="n"/>
-      <c r="AK24" s="54" t="n"/>
-      <c r="AL24" s="54" t="n"/>
-      <c r="AM24" s="54" t="n"/>
-      <c r="AN24" s="54" t="n"/>
-      <c r="AO24" s="54" t="n"/>
-      <c r="AP24" s="54" t="n"/>
-      <c r="AQ24" s="54" t="n"/>
-      <c r="AR24" s="54" t="n"/>
-      <c r="AS24" s="54" t="n"/>
-      <c r="AT24" s="54" t="n"/>
-      <c r="AU24" s="54" t="n"/>
-      <c r="AV24" s="54" t="n"/>
-      <c r="AW24" s="54" t="n"/>
-      <c r="AX24" s="54" t="n"/>
-      <c r="AY24" s="54" t="n"/>
-      <c r="AZ24" s="54" t="n"/>
-      <c r="BA24" s="54" t="n"/>
-      <c r="BB24" s="54" t="n"/>
-      <c r="BC24" s="54" t="n"/>
-      <c r="BD24" s="54" t="n"/>
-      <c r="BE24" s="54" t="n"/>
-      <c r="BF24" s="54" t="n"/>
-      <c r="BG24" s="54" t="n"/>
-      <c r="BH24" s="54" t="n"/>
-      <c r="BI24" s="54" t="n"/>
+      <c r="J24" s="60" t="n"/>
+      <c r="K24" s="60" t="n"/>
+      <c r="L24" s="60" t="n"/>
+      <c r="M24" s="60" t="n"/>
+      <c r="N24" s="60" t="n"/>
+      <c r="O24" s="60" t="n"/>
+      <c r="P24" s="60" t="n"/>
+      <c r="Q24" s="60" t="n"/>
+      <c r="R24" s="60" t="n"/>
+      <c r="S24" s="60" t="n"/>
+      <c r="T24" s="60" t="n"/>
+      <c r="U24" s="60" t="n"/>
+      <c r="V24" s="60" t="n"/>
+      <c r="W24" s="60" t="n"/>
+      <c r="X24" s="60" t="n"/>
+      <c r="Y24" s="60" t="n"/>
+      <c r="Z24" s="60" t="n"/>
+      <c r="AA24" s="60" t="n"/>
+      <c r="AB24" s="60" t="n"/>
+      <c r="AC24" s="60" t="n"/>
+      <c r="AD24" s="60" t="n"/>
+      <c r="AE24" s="60" t="n"/>
+      <c r="AF24" s="60" t="n"/>
+      <c r="AG24" s="60" t="n"/>
+      <c r="AH24" s="60" t="n"/>
+      <c r="AI24" s="60" t="n"/>
+      <c r="AJ24" s="60" t="n"/>
+      <c r="AK24" s="60" t="n"/>
+      <c r="AL24" s="60" t="n"/>
+      <c r="AM24" s="60" t="n"/>
+      <c r="AN24" s="60" t="n"/>
+      <c r="AO24" s="60" t="n"/>
+      <c r="AP24" s="60" t="n"/>
+      <c r="AQ24" s="60" t="n"/>
+      <c r="AR24" s="60" t="n"/>
+      <c r="AS24" s="60" t="n"/>
+      <c r="AT24" s="60" t="n"/>
+      <c r="AU24" s="60" t="n"/>
+      <c r="AV24" s="60" t="n"/>
+      <c r="AW24" s="60" t="n"/>
+      <c r="AX24" s="60" t="n"/>
+      <c r="AY24" s="60" t="n"/>
+      <c r="AZ24" s="60" t="n"/>
+      <c r="BA24" s="60" t="n"/>
+      <c r="BB24" s="60" t="n"/>
+      <c r="BC24" s="60" t="n"/>
+      <c r="BD24" s="60" t="n"/>
+      <c r="BE24" s="60" t="n"/>
+      <c r="BF24" s="60" t="n"/>
+      <c r="BG24" s="60" t="n"/>
+      <c r="BH24" s="60" t="n"/>
+      <c r="BI24" s="60" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="48">
+      <c r="B25" s="54">
         <f>IF(D25="","",19)</f>
         <v/>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="55" t="inlineStr">
         <is>
           <t>Defensa</t>
         </is>
       </c>
-      <c r="D25" s="49" t="inlineStr">
+      <c r="D25" s="55" t="inlineStr">
         <is>
           <t>Defensa oral</t>
         </is>
       </c>
-      <c r="E25" s="50" t="n">
+      <c r="E25" s="56" t="n">
         <v>46507</v>
       </c>
-      <c r="F25" s="50" t="n">
+      <c r="F25" s="56" t="n">
         <v>46507</v>
       </c>
-      <c r="G25" s="51" t="n">
+      <c r="G25" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="58">
         <f>IF(D25="","",IF(N(G25)&gt;=1,"Completada",IF(AND(N(F25)&gt;0,F25&lt;TODAY()),"Atrasada",IF(AND(N(E25)&gt;0,E25&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I25" s="53">
+      <c r="I25" s="59">
         <f>IF(OR(D25="",N(F25)=0,N(G25)&gt;=1),"",F25-TODAY())</f>
         <v/>
       </c>
-      <c r="J25" s="54" t="n"/>
-      <c r="K25" s="54" t="n"/>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="54" t="n"/>
-      <c r="O25" s="54" t="n"/>
-      <c r="P25" s="54" t="n"/>
-      <c r="Q25" s="54" t="n"/>
-      <c r="R25" s="54" t="n"/>
-      <c r="S25" s="54" t="n"/>
-      <c r="T25" s="54" t="n"/>
-      <c r="U25" s="54" t="n"/>
-      <c r="V25" s="54" t="n"/>
-      <c r="W25" s="54" t="n"/>
-      <c r="X25" s="54" t="n"/>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="54" t="n"/>
-      <c r="AG25" s="54" t="n"/>
-      <c r="AH25" s="54" t="n"/>
-      <c r="AI25" s="54" t="n"/>
-      <c r="AJ25" s="54" t="n"/>
-      <c r="AK25" s="54" t="n"/>
-      <c r="AL25" s="54" t="n"/>
-      <c r="AM25" s="54" t="n"/>
-      <c r="AN25" s="54" t="n"/>
-      <c r="AO25" s="54" t="n"/>
-      <c r="AP25" s="54" t="n"/>
-      <c r="AQ25" s="54" t="n"/>
-      <c r="AR25" s="54" t="n"/>
-      <c r="AS25" s="54" t="n"/>
-      <c r="AT25" s="54" t="n"/>
-      <c r="AU25" s="54" t="n"/>
-      <c r="AV25" s="54" t="n"/>
-      <c r="AW25" s="54" t="n"/>
-      <c r="AX25" s="54" t="n"/>
-      <c r="AY25" s="54" t="n"/>
-      <c r="AZ25" s="54" t="n"/>
-      <c r="BA25" s="54" t="n"/>
-      <c r="BB25" s="54" t="n"/>
-      <c r="BC25" s="54" t="n"/>
-      <c r="BD25" s="54" t="n"/>
-      <c r="BE25" s="54" t="n"/>
-      <c r="BF25" s="54" t="n"/>
-      <c r="BG25" s="54" t="n"/>
-      <c r="BH25" s="54" t="n"/>
-      <c r="BI25" s="54" t="n"/>
+      <c r="J25" s="60" t="n"/>
+      <c r="K25" s="60" t="n"/>
+      <c r="L25" s="60" t="n"/>
+      <c r="M25" s="60" t="n"/>
+      <c r="N25" s="60" t="n"/>
+      <c r="O25" s="60" t="n"/>
+      <c r="P25" s="60" t="n"/>
+      <c r="Q25" s="60" t="n"/>
+      <c r="R25" s="60" t="n"/>
+      <c r="S25" s="60" t="n"/>
+      <c r="T25" s="60" t="n"/>
+      <c r="U25" s="60" t="n"/>
+      <c r="V25" s="60" t="n"/>
+      <c r="W25" s="60" t="n"/>
+      <c r="X25" s="60" t="n"/>
+      <c r="Y25" s="60" t="n"/>
+      <c r="Z25" s="60" t="n"/>
+      <c r="AA25" s="60" t="n"/>
+      <c r="AB25" s="60" t="n"/>
+      <c r="AC25" s="60" t="n"/>
+      <c r="AD25" s="60" t="n"/>
+      <c r="AE25" s="60" t="n"/>
+      <c r="AF25" s="60" t="n"/>
+      <c r="AG25" s="60" t="n"/>
+      <c r="AH25" s="60" t="n"/>
+      <c r="AI25" s="60" t="n"/>
+      <c r="AJ25" s="60" t="n"/>
+      <c r="AK25" s="60" t="n"/>
+      <c r="AL25" s="60" t="n"/>
+      <c r="AM25" s="60" t="n"/>
+      <c r="AN25" s="60" t="n"/>
+      <c r="AO25" s="60" t="n"/>
+      <c r="AP25" s="60" t="n"/>
+      <c r="AQ25" s="60" t="n"/>
+      <c r="AR25" s="60" t="n"/>
+      <c r="AS25" s="60" t="n"/>
+      <c r="AT25" s="60" t="n"/>
+      <c r="AU25" s="60" t="n"/>
+      <c r="AV25" s="60" t="n"/>
+      <c r="AW25" s="60" t="n"/>
+      <c r="AX25" s="60" t="n"/>
+      <c r="AY25" s="60" t="n"/>
+      <c r="AZ25" s="60" t="n"/>
+      <c r="BA25" s="60" t="n"/>
+      <c r="BB25" s="60" t="n"/>
+      <c r="BC25" s="60" t="n"/>
+      <c r="BD25" s="60" t="n"/>
+      <c r="BE25" s="60" t="n"/>
+      <c r="BF25" s="60" t="n"/>
+      <c r="BG25" s="60" t="n"/>
+      <c r="BH25" s="60" t="n"/>
+      <c r="BI25" s="60" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="B26" s="48">
+      <c r="B26" s="54">
         <f>IF(D26="","",20)</f>
         <v/>
       </c>
-      <c r="C26" s="49" t="n"/>
-      <c r="D26" s="49" t="n"/>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="50" t="n"/>
-      <c r="G26" s="51" t="n"/>
-      <c r="H26" s="52">
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="56" t="n"/>
+      <c r="F26" s="56" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="58">
         <f>IF(D26="","",IF(N(G26)&gt;=1,"Completada",IF(AND(N(F26)&gt;0,F26&lt;TODAY()),"Atrasada",IF(AND(N(E26)&gt;0,E26&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I26" s="53">
+      <c r="I26" s="59">
         <f>IF(OR(D26="",N(F26)=0,N(G26)&gt;=1),"",F26-TODAY())</f>
         <v/>
       </c>
-      <c r="J26" s="54" t="n"/>
-      <c r="K26" s="54" t="n"/>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="54" t="n"/>
-      <c r="O26" s="54" t="n"/>
-      <c r="P26" s="54" t="n"/>
-      <c r="Q26" s="54" t="n"/>
-      <c r="R26" s="54" t="n"/>
-      <c r="S26" s="54" t="n"/>
-      <c r="T26" s="54" t="n"/>
-      <c r="U26" s="54" t="n"/>
-      <c r="V26" s="54" t="n"/>
-      <c r="W26" s="54" t="n"/>
-      <c r="X26" s="54" t="n"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="54" t="n"/>
-      <c r="AG26" s="54" t="n"/>
-      <c r="AH26" s="54" t="n"/>
-      <c r="AI26" s="54" t="n"/>
-      <c r="AJ26" s="54" t="n"/>
-      <c r="AK26" s="54" t="n"/>
-      <c r="AL26" s="54" t="n"/>
-      <c r="AM26" s="54" t="n"/>
-      <c r="AN26" s="54" t="n"/>
-      <c r="AO26" s="54" t="n"/>
-      <c r="AP26" s="54" t="n"/>
-      <c r="AQ26" s="54" t="n"/>
-      <c r="AR26" s="54" t="n"/>
-      <c r="AS26" s="54" t="n"/>
-      <c r="AT26" s="54" t="n"/>
-      <c r="AU26" s="54" t="n"/>
-      <c r="AV26" s="54" t="n"/>
-      <c r="AW26" s="54" t="n"/>
-      <c r="AX26" s="54" t="n"/>
-      <c r="AY26" s="54" t="n"/>
-      <c r="AZ26" s="54" t="n"/>
-      <c r="BA26" s="54" t="n"/>
-      <c r="BB26" s="54" t="n"/>
-      <c r="BC26" s="54" t="n"/>
-      <c r="BD26" s="54" t="n"/>
-      <c r="BE26" s="54" t="n"/>
-      <c r="BF26" s="54" t="n"/>
-      <c r="BG26" s="54" t="n"/>
-      <c r="BH26" s="54" t="n"/>
-      <c r="BI26" s="54" t="n"/>
+      <c r="J26" s="60" t="n"/>
+      <c r="K26" s="60" t="n"/>
+      <c r="L26" s="60" t="n"/>
+      <c r="M26" s="60" t="n"/>
+      <c r="N26" s="60" t="n"/>
+      <c r="O26" s="60" t="n"/>
+      <c r="P26" s="60" t="n"/>
+      <c r="Q26" s="60" t="n"/>
+      <c r="R26" s="60" t="n"/>
+      <c r="S26" s="60" t="n"/>
+      <c r="T26" s="60" t="n"/>
+      <c r="U26" s="60" t="n"/>
+      <c r="V26" s="60" t="n"/>
+      <c r="W26" s="60" t="n"/>
+      <c r="X26" s="60" t="n"/>
+      <c r="Y26" s="60" t="n"/>
+      <c r="Z26" s="60" t="n"/>
+      <c r="AA26" s="60" t="n"/>
+      <c r="AB26" s="60" t="n"/>
+      <c r="AC26" s="60" t="n"/>
+      <c r="AD26" s="60" t="n"/>
+      <c r="AE26" s="60" t="n"/>
+      <c r="AF26" s="60" t="n"/>
+      <c r="AG26" s="60" t="n"/>
+      <c r="AH26" s="60" t="n"/>
+      <c r="AI26" s="60" t="n"/>
+      <c r="AJ26" s="60" t="n"/>
+      <c r="AK26" s="60" t="n"/>
+      <c r="AL26" s="60" t="n"/>
+      <c r="AM26" s="60" t="n"/>
+      <c r="AN26" s="60" t="n"/>
+      <c r="AO26" s="60" t="n"/>
+      <c r="AP26" s="60" t="n"/>
+      <c r="AQ26" s="60" t="n"/>
+      <c r="AR26" s="60" t="n"/>
+      <c r="AS26" s="60" t="n"/>
+      <c r="AT26" s="60" t="n"/>
+      <c r="AU26" s="60" t="n"/>
+      <c r="AV26" s="60" t="n"/>
+      <c r="AW26" s="60" t="n"/>
+      <c r="AX26" s="60" t="n"/>
+      <c r="AY26" s="60" t="n"/>
+      <c r="AZ26" s="60" t="n"/>
+      <c r="BA26" s="60" t="n"/>
+      <c r="BB26" s="60" t="n"/>
+      <c r="BC26" s="60" t="n"/>
+      <c r="BD26" s="60" t="n"/>
+      <c r="BE26" s="60" t="n"/>
+      <c r="BF26" s="60" t="n"/>
+      <c r="BG26" s="60" t="n"/>
+      <c r="BH26" s="60" t="n"/>
+      <c r="BI26" s="60" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="B27" s="48">
+      <c r="B27" s="54">
         <f>IF(D27="","",21)</f>
         <v/>
       </c>
-      <c r="C27" s="49" t="n"/>
-      <c r="D27" s="49" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
-      <c r="G27" s="51" t="n"/>
-      <c r="H27" s="52">
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="56" t="n"/>
+      <c r="G27" s="57" t="n"/>
+      <c r="H27" s="58">
         <f>IF(D27="","",IF(N(G27)&gt;=1,"Completada",IF(AND(N(F27)&gt;0,F27&lt;TODAY()),"Atrasada",IF(AND(N(E27)&gt;0,E27&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I27" s="53">
+      <c r="I27" s="59">
         <f>IF(OR(D27="",N(F27)=0,N(G27)&gt;=1),"",F27-TODAY())</f>
         <v/>
       </c>
-      <c r="J27" s="54" t="n"/>
-      <c r="K27" s="54" t="n"/>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="54" t="n"/>
-      <c r="O27" s="54" t="n"/>
-      <c r="P27" s="54" t="n"/>
-      <c r="Q27" s="54" t="n"/>
-      <c r="R27" s="54" t="n"/>
-      <c r="S27" s="54" t="n"/>
-      <c r="T27" s="54" t="n"/>
-      <c r="U27" s="54" t="n"/>
-      <c r="V27" s="54" t="n"/>
-      <c r="W27" s="54" t="n"/>
-      <c r="X27" s="54" t="n"/>
-      <c r="Y27" s="54" t="n"/>
-      <c r="Z27" s="54" t="n"/>
-      <c r="AA27" s="54" t="n"/>
-      <c r="AB27" s="54" t="n"/>
-      <c r="AC27" s="54" t="n"/>
-      <c r="AD27" s="54" t="n"/>
-      <c r="AE27" s="54" t="n"/>
-      <c r="AF27" s="54" t="n"/>
-      <c r="AG27" s="54" t="n"/>
-      <c r="AH27" s="54" t="n"/>
-      <c r="AI27" s="54" t="n"/>
-      <c r="AJ27" s="54" t="n"/>
-      <c r="AK27" s="54" t="n"/>
-      <c r="AL27" s="54" t="n"/>
-      <c r="AM27" s="54" t="n"/>
-      <c r="AN27" s="54" t="n"/>
-      <c r="AO27" s="54" t="n"/>
-      <c r="AP27" s="54" t="n"/>
-      <c r="AQ27" s="54" t="n"/>
-      <c r="AR27" s="54" t="n"/>
-      <c r="AS27" s="54" t="n"/>
-      <c r="AT27" s="54" t="n"/>
-      <c r="AU27" s="54" t="n"/>
-      <c r="AV27" s="54" t="n"/>
-      <c r="AW27" s="54" t="n"/>
-      <c r="AX27" s="54" t="n"/>
-      <c r="AY27" s="54" t="n"/>
-      <c r="AZ27" s="54" t="n"/>
-      <c r="BA27" s="54" t="n"/>
-      <c r="BB27" s="54" t="n"/>
-      <c r="BC27" s="54" t="n"/>
-      <c r="BD27" s="54" t="n"/>
-      <c r="BE27" s="54" t="n"/>
-      <c r="BF27" s="54" t="n"/>
-      <c r="BG27" s="54" t="n"/>
-      <c r="BH27" s="54" t="n"/>
-      <c r="BI27" s="54" t="n"/>
+      <c r="J27" s="60" t="n"/>
+      <c r="K27" s="60" t="n"/>
+      <c r="L27" s="60" t="n"/>
+      <c r="M27" s="60" t="n"/>
+      <c r="N27" s="60" t="n"/>
+      <c r="O27" s="60" t="n"/>
+      <c r="P27" s="60" t="n"/>
+      <c r="Q27" s="60" t="n"/>
+      <c r="R27" s="60" t="n"/>
+      <c r="S27" s="60" t="n"/>
+      <c r="T27" s="60" t="n"/>
+      <c r="U27" s="60" t="n"/>
+      <c r="V27" s="60" t="n"/>
+      <c r="W27" s="60" t="n"/>
+      <c r="X27" s="60" t="n"/>
+      <c r="Y27" s="60" t="n"/>
+      <c r="Z27" s="60" t="n"/>
+      <c r="AA27" s="60" t="n"/>
+      <c r="AB27" s="60" t="n"/>
+      <c r="AC27" s="60" t="n"/>
+      <c r="AD27" s="60" t="n"/>
+      <c r="AE27" s="60" t="n"/>
+      <c r="AF27" s="60" t="n"/>
+      <c r="AG27" s="60" t="n"/>
+      <c r="AH27" s="60" t="n"/>
+      <c r="AI27" s="60" t="n"/>
+      <c r="AJ27" s="60" t="n"/>
+      <c r="AK27" s="60" t="n"/>
+      <c r="AL27" s="60" t="n"/>
+      <c r="AM27" s="60" t="n"/>
+      <c r="AN27" s="60" t="n"/>
+      <c r="AO27" s="60" t="n"/>
+      <c r="AP27" s="60" t="n"/>
+      <c r="AQ27" s="60" t="n"/>
+      <c r="AR27" s="60" t="n"/>
+      <c r="AS27" s="60" t="n"/>
+      <c r="AT27" s="60" t="n"/>
+      <c r="AU27" s="60" t="n"/>
+      <c r="AV27" s="60" t="n"/>
+      <c r="AW27" s="60" t="n"/>
+      <c r="AX27" s="60" t="n"/>
+      <c r="AY27" s="60" t="n"/>
+      <c r="AZ27" s="60" t="n"/>
+      <c r="BA27" s="60" t="n"/>
+      <c r="BB27" s="60" t="n"/>
+      <c r="BC27" s="60" t="n"/>
+      <c r="BD27" s="60" t="n"/>
+      <c r="BE27" s="60" t="n"/>
+      <c r="BF27" s="60" t="n"/>
+      <c r="BG27" s="60" t="n"/>
+      <c r="BH27" s="60" t="n"/>
+      <c r="BI27" s="60" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="B28" s="48">
+      <c r="B28" s="54">
         <f>IF(D28="","",22)</f>
         <v/>
       </c>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="49" t="n"/>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="50" t="n"/>
-      <c r="G28" s="51" t="n"/>
-      <c r="H28" s="52">
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="56" t="n"/>
+      <c r="F28" s="56" t="n"/>
+      <c r="G28" s="57" t="n"/>
+      <c r="H28" s="58">
         <f>IF(D28="","",IF(N(G28)&gt;=1,"Completada",IF(AND(N(F28)&gt;0,F28&lt;TODAY()),"Atrasada",IF(AND(N(E28)&gt;0,E28&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I28" s="53">
+      <c r="I28" s="59">
         <f>IF(OR(D28="",N(F28)=0,N(G28)&gt;=1),"",F28-TODAY())</f>
         <v/>
       </c>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="54" t="n"/>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="54" t="n"/>
-      <c r="O28" s="54" t="n"/>
-      <c r="P28" s="54" t="n"/>
-      <c r="Q28" s="54" t="n"/>
-      <c r="R28" s="54" t="n"/>
-      <c r="S28" s="54" t="n"/>
-      <c r="T28" s="54" t="n"/>
-      <c r="U28" s="54" t="n"/>
-      <c r="V28" s="54" t="n"/>
-      <c r="W28" s="54" t="n"/>
-      <c r="X28" s="54" t="n"/>
-      <c r="Y28" s="54" t="n"/>
-      <c r="Z28" s="54" t="n"/>
-      <c r="AA28" s="54" t="n"/>
-      <c r="AB28" s="54" t="n"/>
-      <c r="AC28" s="54" t="n"/>
-      <c r="AD28" s="54" t="n"/>
-      <c r="AE28" s="54" t="n"/>
-      <c r="AF28" s="54" t="n"/>
-      <c r="AG28" s="54" t="n"/>
-      <c r="AH28" s="54" t="n"/>
-      <c r="AI28" s="54" t="n"/>
-      <c r="AJ28" s="54" t="n"/>
-      <c r="AK28" s="54" t="n"/>
-      <c r="AL28" s="54" t="n"/>
-      <c r="AM28" s="54" t="n"/>
-      <c r="AN28" s="54" t="n"/>
-      <c r="AO28" s="54" t="n"/>
-      <c r="AP28" s="54" t="n"/>
-      <c r="AQ28" s="54" t="n"/>
-      <c r="AR28" s="54" t="n"/>
-      <c r="AS28" s="54" t="n"/>
-      <c r="AT28" s="54" t="n"/>
-      <c r="AU28" s="54" t="n"/>
-      <c r="AV28" s="54" t="n"/>
-      <c r="AW28" s="54" t="n"/>
-      <c r="AX28" s="54" t="n"/>
-      <c r="AY28" s="54" t="n"/>
-      <c r="AZ28" s="54" t="n"/>
-      <c r="BA28" s="54" t="n"/>
-      <c r="BB28" s="54" t="n"/>
-      <c r="BC28" s="54" t="n"/>
-      <c r="BD28" s="54" t="n"/>
-      <c r="BE28" s="54" t="n"/>
-      <c r="BF28" s="54" t="n"/>
-      <c r="BG28" s="54" t="n"/>
-      <c r="BH28" s="54" t="n"/>
-      <c r="BI28" s="54" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
+      <c r="O28" s="60" t="n"/>
+      <c r="P28" s="60" t="n"/>
+      <c r="Q28" s="60" t="n"/>
+      <c r="R28" s="60" t="n"/>
+      <c r="S28" s="60" t="n"/>
+      <c r="T28" s="60" t="n"/>
+      <c r="U28" s="60" t="n"/>
+      <c r="V28" s="60" t="n"/>
+      <c r="W28" s="60" t="n"/>
+      <c r="X28" s="60" t="n"/>
+      <c r="Y28" s="60" t="n"/>
+      <c r="Z28" s="60" t="n"/>
+      <c r="AA28" s="60" t="n"/>
+      <c r="AB28" s="60" t="n"/>
+      <c r="AC28" s="60" t="n"/>
+      <c r="AD28" s="60" t="n"/>
+      <c r="AE28" s="60" t="n"/>
+      <c r="AF28" s="60" t="n"/>
+      <c r="AG28" s="60" t="n"/>
+      <c r="AH28" s="60" t="n"/>
+      <c r="AI28" s="60" t="n"/>
+      <c r="AJ28" s="60" t="n"/>
+      <c r="AK28" s="60" t="n"/>
+      <c r="AL28" s="60" t="n"/>
+      <c r="AM28" s="60" t="n"/>
+      <c r="AN28" s="60" t="n"/>
+      <c r="AO28" s="60" t="n"/>
+      <c r="AP28" s="60" t="n"/>
+      <c r="AQ28" s="60" t="n"/>
+      <c r="AR28" s="60" t="n"/>
+      <c r="AS28" s="60" t="n"/>
+      <c r="AT28" s="60" t="n"/>
+      <c r="AU28" s="60" t="n"/>
+      <c r="AV28" s="60" t="n"/>
+      <c r="AW28" s="60" t="n"/>
+      <c r="AX28" s="60" t="n"/>
+      <c r="AY28" s="60" t="n"/>
+      <c r="AZ28" s="60" t="n"/>
+      <c r="BA28" s="60" t="n"/>
+      <c r="BB28" s="60" t="n"/>
+      <c r="BC28" s="60" t="n"/>
+      <c r="BD28" s="60" t="n"/>
+      <c r="BE28" s="60" t="n"/>
+      <c r="BF28" s="60" t="n"/>
+      <c r="BG28" s="60" t="n"/>
+      <c r="BH28" s="60" t="n"/>
+      <c r="BI28" s="60" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="B29" s="48">
+      <c r="B29" s="54">
         <f>IF(D29="","",23)</f>
         <v/>
       </c>
-      <c r="C29" s="49" t="n"/>
-      <c r="D29" s="49" t="n"/>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="50" t="n"/>
-      <c r="G29" s="51" t="n"/>
-      <c r="H29" s="52">
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="56" t="n"/>
+      <c r="F29" s="56" t="n"/>
+      <c r="G29" s="57" t="n"/>
+      <c r="H29" s="58">
         <f>IF(D29="","",IF(N(G29)&gt;=1,"Completada",IF(AND(N(F29)&gt;0,F29&lt;TODAY()),"Atrasada",IF(AND(N(E29)&gt;0,E29&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I29" s="53">
+      <c r="I29" s="59">
         <f>IF(OR(D29="",N(F29)=0,N(G29)&gt;=1),"",F29-TODAY())</f>
         <v/>
       </c>
-      <c r="J29" s="54" t="n"/>
-      <c r="K29" s="54" t="n"/>
-      <c r="L29" s="54" t="n"/>
-      <c r="M29" s="54" t="n"/>
-      <c r="N29" s="54" t="n"/>
-      <c r="O29" s="54" t="n"/>
-      <c r="P29" s="54" t="n"/>
-      <c r="Q29" s="54" t="n"/>
-      <c r="R29" s="54" t="n"/>
-      <c r="S29" s="54" t="n"/>
-      <c r="T29" s="54" t="n"/>
-      <c r="U29" s="54" t="n"/>
-      <c r="V29" s="54" t="n"/>
-      <c r="W29" s="54" t="n"/>
-      <c r="X29" s="54" t="n"/>
-      <c r="Y29" s="54" t="n"/>
-      <c r="Z29" s="54" t="n"/>
-      <c r="AA29" s="54" t="n"/>
-      <c r="AB29" s="54" t="n"/>
-      <c r="AC29" s="54" t="n"/>
-      <c r="AD29" s="54" t="n"/>
-      <c r="AE29" s="54" t="n"/>
-      <c r="AF29" s="54" t="n"/>
-      <c r="AG29" s="54" t="n"/>
-      <c r="AH29" s="54" t="n"/>
-      <c r="AI29" s="54" t="n"/>
-      <c r="AJ29" s="54" t="n"/>
-      <c r="AK29" s="54" t="n"/>
-      <c r="AL29" s="54" t="n"/>
-      <c r="AM29" s="54" t="n"/>
-      <c r="AN29" s="54" t="n"/>
-      <c r="AO29" s="54" t="n"/>
-      <c r="AP29" s="54" t="n"/>
-      <c r="AQ29" s="54" t="n"/>
-      <c r="AR29" s="54" t="n"/>
-      <c r="AS29" s="54" t="n"/>
-      <c r="AT29" s="54" t="n"/>
-      <c r="AU29" s="54" t="n"/>
-      <c r="AV29" s="54" t="n"/>
-      <c r="AW29" s="54" t="n"/>
-      <c r="AX29" s="54" t="n"/>
-      <c r="AY29" s="54" t="n"/>
-      <c r="AZ29" s="54" t="n"/>
-      <c r="BA29" s="54" t="n"/>
-      <c r="BB29" s="54" t="n"/>
-      <c r="BC29" s="54" t="n"/>
-      <c r="BD29" s="54" t="n"/>
-      <c r="BE29" s="54" t="n"/>
-      <c r="BF29" s="54" t="n"/>
-      <c r="BG29" s="54" t="n"/>
-      <c r="BH29" s="54" t="n"/>
-      <c r="BI29" s="54" t="n"/>
+      <c r="J29" s="60" t="n"/>
+      <c r="K29" s="60" t="n"/>
+      <c r="L29" s="60" t="n"/>
+      <c r="M29" s="60" t="n"/>
+      <c r="N29" s="60" t="n"/>
+      <c r="O29" s="60" t="n"/>
+      <c r="P29" s="60" t="n"/>
+      <c r="Q29" s="60" t="n"/>
+      <c r="R29" s="60" t="n"/>
+      <c r="S29" s="60" t="n"/>
+      <c r="T29" s="60" t="n"/>
+      <c r="U29" s="60" t="n"/>
+      <c r="V29" s="60" t="n"/>
+      <c r="W29" s="60" t="n"/>
+      <c r="X29" s="60" t="n"/>
+      <c r="Y29" s="60" t="n"/>
+      <c r="Z29" s="60" t="n"/>
+      <c r="AA29" s="60" t="n"/>
+      <c r="AB29" s="60" t="n"/>
+      <c r="AC29" s="60" t="n"/>
+      <c r="AD29" s="60" t="n"/>
+      <c r="AE29" s="60" t="n"/>
+      <c r="AF29" s="60" t="n"/>
+      <c r="AG29" s="60" t="n"/>
+      <c r="AH29" s="60" t="n"/>
+      <c r="AI29" s="60" t="n"/>
+      <c r="AJ29" s="60" t="n"/>
+      <c r="AK29" s="60" t="n"/>
+      <c r="AL29" s="60" t="n"/>
+      <c r="AM29" s="60" t="n"/>
+      <c r="AN29" s="60" t="n"/>
+      <c r="AO29" s="60" t="n"/>
+      <c r="AP29" s="60" t="n"/>
+      <c r="AQ29" s="60" t="n"/>
+      <c r="AR29" s="60" t="n"/>
+      <c r="AS29" s="60" t="n"/>
+      <c r="AT29" s="60" t="n"/>
+      <c r="AU29" s="60" t="n"/>
+      <c r="AV29" s="60" t="n"/>
+      <c r="AW29" s="60" t="n"/>
+      <c r="AX29" s="60" t="n"/>
+      <c r="AY29" s="60" t="n"/>
+      <c r="AZ29" s="60" t="n"/>
+      <c r="BA29" s="60" t="n"/>
+      <c r="BB29" s="60" t="n"/>
+      <c r="BC29" s="60" t="n"/>
+      <c r="BD29" s="60" t="n"/>
+      <c r="BE29" s="60" t="n"/>
+      <c r="BF29" s="60" t="n"/>
+      <c r="BG29" s="60" t="n"/>
+      <c r="BH29" s="60" t="n"/>
+      <c r="BI29" s="60" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="B30" s="48">
+      <c r="B30" s="54">
         <f>IF(D30="","",24)</f>
         <v/>
       </c>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="49" t="n"/>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="50" t="n"/>
-      <c r="G30" s="51" t="n"/>
-      <c r="H30" s="52">
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="55" t="n"/>
+      <c r="E30" s="56" t="n"/>
+      <c r="F30" s="56" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="58">
         <f>IF(D30="","",IF(N(G30)&gt;=1,"Completada",IF(AND(N(F30)&gt;0,F30&lt;TODAY()),"Atrasada",IF(AND(N(E30)&gt;0,E30&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I30" s="53">
+      <c r="I30" s="59">
         <f>IF(OR(D30="",N(F30)=0,N(G30)&gt;=1),"",F30-TODAY())</f>
         <v/>
       </c>
-      <c r="J30" s="54" t="n"/>
-      <c r="K30" s="54" t="n"/>
-      <c r="L30" s="54" t="n"/>
-      <c r="M30" s="54" t="n"/>
-      <c r="N30" s="54" t="n"/>
-      <c r="O30" s="54" t="n"/>
-      <c r="P30" s="54" t="n"/>
-      <c r="Q30" s="54" t="n"/>
-      <c r="R30" s="54" t="n"/>
-      <c r="S30" s="54" t="n"/>
-      <c r="T30" s="54" t="n"/>
-      <c r="U30" s="54" t="n"/>
-      <c r="V30" s="54" t="n"/>
-      <c r="W30" s="54" t="n"/>
-      <c r="X30" s="54" t="n"/>
-      <c r="Y30" s="54" t="n"/>
-      <c r="Z30" s="54" t="n"/>
-      <c r="AA30" s="54" t="n"/>
-      <c r="AB30" s="54" t="n"/>
-      <c r="AC30" s="54" t="n"/>
-      <c r="AD30" s="54" t="n"/>
-      <c r="AE30" s="54" t="n"/>
-      <c r="AF30" s="54" t="n"/>
-      <c r="AG30" s="54" t="n"/>
-      <c r="AH30" s="54" t="n"/>
-      <c r="AI30" s="54" t="n"/>
-      <c r="AJ30" s="54" t="n"/>
-      <c r="AK30" s="54" t="n"/>
-      <c r="AL30" s="54" t="n"/>
-      <c r="AM30" s="54" t="n"/>
-      <c r="AN30" s="54" t="n"/>
-      <c r="AO30" s="54" t="n"/>
-      <c r="AP30" s="54" t="n"/>
-      <c r="AQ30" s="54" t="n"/>
-      <c r="AR30" s="54" t="n"/>
-      <c r="AS30" s="54" t="n"/>
-      <c r="AT30" s="54" t="n"/>
-      <c r="AU30" s="54" t="n"/>
-      <c r="AV30" s="54" t="n"/>
-      <c r="AW30" s="54" t="n"/>
-      <c r="AX30" s="54" t="n"/>
-      <c r="AY30" s="54" t="n"/>
-      <c r="AZ30" s="54" t="n"/>
-      <c r="BA30" s="54" t="n"/>
-      <c r="BB30" s="54" t="n"/>
-      <c r="BC30" s="54" t="n"/>
-      <c r="BD30" s="54" t="n"/>
-      <c r="BE30" s="54" t="n"/>
-      <c r="BF30" s="54" t="n"/>
-      <c r="BG30" s="54" t="n"/>
-      <c r="BH30" s="54" t="n"/>
-      <c r="BI30" s="54" t="n"/>
+      <c r="J30" s="60" t="n"/>
+      <c r="K30" s="60" t="n"/>
+      <c r="L30" s="60" t="n"/>
+      <c r="M30" s="60" t="n"/>
+      <c r="N30" s="60" t="n"/>
+      <c r="O30" s="60" t="n"/>
+      <c r="P30" s="60" t="n"/>
+      <c r="Q30" s="60" t="n"/>
+      <c r="R30" s="60" t="n"/>
+      <c r="S30" s="60" t="n"/>
+      <c r="T30" s="60" t="n"/>
+      <c r="U30" s="60" t="n"/>
+      <c r="V30" s="60" t="n"/>
+      <c r="W30" s="60" t="n"/>
+      <c r="X30" s="60" t="n"/>
+      <c r="Y30" s="60" t="n"/>
+      <c r="Z30" s="60" t="n"/>
+      <c r="AA30" s="60" t="n"/>
+      <c r="AB30" s="60" t="n"/>
+      <c r="AC30" s="60" t="n"/>
+      <c r="AD30" s="60" t="n"/>
+      <c r="AE30" s="60" t="n"/>
+      <c r="AF30" s="60" t="n"/>
+      <c r="AG30" s="60" t="n"/>
+      <c r="AH30" s="60" t="n"/>
+      <c r="AI30" s="60" t="n"/>
+      <c r="AJ30" s="60" t="n"/>
+      <c r="AK30" s="60" t="n"/>
+      <c r="AL30" s="60" t="n"/>
+      <c r="AM30" s="60" t="n"/>
+      <c r="AN30" s="60" t="n"/>
+      <c r="AO30" s="60" t="n"/>
+      <c r="AP30" s="60" t="n"/>
+      <c r="AQ30" s="60" t="n"/>
+      <c r="AR30" s="60" t="n"/>
+      <c r="AS30" s="60" t="n"/>
+      <c r="AT30" s="60" t="n"/>
+      <c r="AU30" s="60" t="n"/>
+      <c r="AV30" s="60" t="n"/>
+      <c r="AW30" s="60" t="n"/>
+      <c r="AX30" s="60" t="n"/>
+      <c r="AY30" s="60" t="n"/>
+      <c r="AZ30" s="60" t="n"/>
+      <c r="BA30" s="60" t="n"/>
+      <c r="BB30" s="60" t="n"/>
+      <c r="BC30" s="60" t="n"/>
+      <c r="BD30" s="60" t="n"/>
+      <c r="BE30" s="60" t="n"/>
+      <c r="BF30" s="60" t="n"/>
+      <c r="BG30" s="60" t="n"/>
+      <c r="BH30" s="60" t="n"/>
+      <c r="BI30" s="60" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="B31" s="48">
+      <c r="B31" s="54">
         <f>IF(D31="","",25)</f>
         <v/>
       </c>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="50" t="n"/>
-      <c r="G31" s="51" t="n"/>
-      <c r="H31" s="52">
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="55" t="n"/>
+      <c r="E31" s="56" t="n"/>
+      <c r="F31" s="56" t="n"/>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="58">
         <f>IF(D31="","",IF(N(G31)&gt;=1,"Completada",IF(AND(N(F31)&gt;0,F31&lt;TODAY()),"Atrasada",IF(AND(N(E31)&gt;0,E31&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I31" s="53">
+      <c r="I31" s="59">
         <f>IF(OR(D31="",N(F31)=0,N(G31)&gt;=1),"",F31-TODAY())</f>
         <v/>
       </c>
-      <c r="J31" s="54" t="n"/>
-      <c r="K31" s="54" t="n"/>
-      <c r="L31" s="54" t="n"/>
-      <c r="M31" s="54" t="n"/>
-      <c r="N31" s="54" t="n"/>
-      <c r="O31" s="54" t="n"/>
-      <c r="P31" s="54" t="n"/>
-      <c r="Q31" s="54" t="n"/>
-      <c r="R31" s="54" t="n"/>
-      <c r="S31" s="54" t="n"/>
-      <c r="T31" s="54" t="n"/>
-      <c r="U31" s="54" t="n"/>
-      <c r="V31" s="54" t="n"/>
-      <c r="W31" s="54" t="n"/>
-      <c r="X31" s="54" t="n"/>
-      <c r="Y31" s="54" t="n"/>
-      <c r="Z31" s="54" t="n"/>
-      <c r="AA31" s="54" t="n"/>
-      <c r="AB31" s="54" t="n"/>
-      <c r="AC31" s="54" t="n"/>
-      <c r="AD31" s="54" t="n"/>
-      <c r="AE31" s="54" t="n"/>
-      <c r="AF31" s="54" t="n"/>
-      <c r="AG31" s="54" t="n"/>
-      <c r="AH31" s="54" t="n"/>
-      <c r="AI31" s="54" t="n"/>
-      <c r="AJ31" s="54" t="n"/>
-      <c r="AK31" s="54" t="n"/>
-      <c r="AL31" s="54" t="n"/>
-      <c r="AM31" s="54" t="n"/>
-      <c r="AN31" s="54" t="n"/>
-      <c r="AO31" s="54" t="n"/>
-      <c r="AP31" s="54" t="n"/>
-      <c r="AQ31" s="54" t="n"/>
-      <c r="AR31" s="54" t="n"/>
-      <c r="AS31" s="54" t="n"/>
-      <c r="AT31" s="54" t="n"/>
-      <c r="AU31" s="54" t="n"/>
-      <c r="AV31" s="54" t="n"/>
-      <c r="AW31" s="54" t="n"/>
-      <c r="AX31" s="54" t="n"/>
-      <c r="AY31" s="54" t="n"/>
-      <c r="AZ31" s="54" t="n"/>
-      <c r="BA31" s="54" t="n"/>
-      <c r="BB31" s="54" t="n"/>
-      <c r="BC31" s="54" t="n"/>
-      <c r="BD31" s="54" t="n"/>
-      <c r="BE31" s="54" t="n"/>
-      <c r="BF31" s="54" t="n"/>
-      <c r="BG31" s="54" t="n"/>
-      <c r="BH31" s="54" t="n"/>
-      <c r="BI31" s="54" t="n"/>
+      <c r="J31" s="60" t="n"/>
+      <c r="K31" s="60" t="n"/>
+      <c r="L31" s="60" t="n"/>
+      <c r="M31" s="60" t="n"/>
+      <c r="N31" s="60" t="n"/>
+      <c r="O31" s="60" t="n"/>
+      <c r="P31" s="60" t="n"/>
+      <c r="Q31" s="60" t="n"/>
+      <c r="R31" s="60" t="n"/>
+      <c r="S31" s="60" t="n"/>
+      <c r="T31" s="60" t="n"/>
+      <c r="U31" s="60" t="n"/>
+      <c r="V31" s="60" t="n"/>
+      <c r="W31" s="60" t="n"/>
+      <c r="X31" s="60" t="n"/>
+      <c r="Y31" s="60" t="n"/>
+      <c r="Z31" s="60" t="n"/>
+      <c r="AA31" s="60" t="n"/>
+      <c r="AB31" s="60" t="n"/>
+      <c r="AC31" s="60" t="n"/>
+      <c r="AD31" s="60" t="n"/>
+      <c r="AE31" s="60" t="n"/>
+      <c r="AF31" s="60" t="n"/>
+      <c r="AG31" s="60" t="n"/>
+      <c r="AH31" s="60" t="n"/>
+      <c r="AI31" s="60" t="n"/>
+      <c r="AJ31" s="60" t="n"/>
+      <c r="AK31" s="60" t="n"/>
+      <c r="AL31" s="60" t="n"/>
+      <c r="AM31" s="60" t="n"/>
+      <c r="AN31" s="60" t="n"/>
+      <c r="AO31" s="60" t="n"/>
+      <c r="AP31" s="60" t="n"/>
+      <c r="AQ31" s="60" t="n"/>
+      <c r="AR31" s="60" t="n"/>
+      <c r="AS31" s="60" t="n"/>
+      <c r="AT31" s="60" t="n"/>
+      <c r="AU31" s="60" t="n"/>
+      <c r="AV31" s="60" t="n"/>
+      <c r="AW31" s="60" t="n"/>
+      <c r="AX31" s="60" t="n"/>
+      <c r="AY31" s="60" t="n"/>
+      <c r="AZ31" s="60" t="n"/>
+      <c r="BA31" s="60" t="n"/>
+      <c r="BB31" s="60" t="n"/>
+      <c r="BC31" s="60" t="n"/>
+      <c r="BD31" s="60" t="n"/>
+      <c r="BE31" s="60" t="n"/>
+      <c r="BF31" s="60" t="n"/>
+      <c r="BG31" s="60" t="n"/>
+      <c r="BH31" s="60" t="n"/>
+      <c r="BI31" s="60" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="B32" s="48">
+      <c r="B32" s="54">
         <f>IF(D32="","",26)</f>
         <v/>
       </c>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="51" t="n"/>
-      <c r="H32" s="52">
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="55" t="n"/>
+      <c r="E32" s="56" t="n"/>
+      <c r="F32" s="56" t="n"/>
+      <c r="G32" s="57" t="n"/>
+      <c r="H32" s="58">
         <f>IF(D32="","",IF(N(G32)&gt;=1,"Completada",IF(AND(N(F32)&gt;0,F32&lt;TODAY()),"Atrasada",IF(AND(N(E32)&gt;0,E32&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I32" s="53">
+      <c r="I32" s="59">
         <f>IF(OR(D32="",N(F32)=0,N(G32)&gt;=1),"",F32-TODAY())</f>
         <v/>
       </c>
-      <c r="J32" s="54" t="n"/>
-      <c r="K32" s="54" t="n"/>
-      <c r="L32" s="54" t="n"/>
-      <c r="M32" s="54" t="n"/>
-      <c r="N32" s="54" t="n"/>
-      <c r="O32" s="54" t="n"/>
-      <c r="P32" s="54" t="n"/>
-      <c r="Q32" s="54" t="n"/>
-      <c r="R32" s="54" t="n"/>
-      <c r="S32" s="54" t="n"/>
-      <c r="T32" s="54" t="n"/>
-      <c r="U32" s="54" t="n"/>
-      <c r="V32" s="54" t="n"/>
-      <c r="W32" s="54" t="n"/>
-      <c r="X32" s="54" t="n"/>
-      <c r="Y32" s="54" t="n"/>
-      <c r="Z32" s="54" t="n"/>
-      <c r="AA32" s="54" t="n"/>
-      <c r="AB32" s="54" t="n"/>
-      <c r="AC32" s="54" t="n"/>
-      <c r="AD32" s="54" t="n"/>
-      <c r="AE32" s="54" t="n"/>
-      <c r="AF32" s="54" t="n"/>
-      <c r="AG32" s="54" t="n"/>
-      <c r="AH32" s="54" t="n"/>
-      <c r="AI32" s="54" t="n"/>
-      <c r="AJ32" s="54" t="n"/>
-      <c r="AK32" s="54" t="n"/>
-      <c r="AL32" s="54" t="n"/>
-      <c r="AM32" s="54" t="n"/>
-      <c r="AN32" s="54" t="n"/>
-      <c r="AO32" s="54" t="n"/>
-      <c r="AP32" s="54" t="n"/>
-      <c r="AQ32" s="54" t="n"/>
-      <c r="AR32" s="54" t="n"/>
-      <c r="AS32" s="54" t="n"/>
-      <c r="AT32" s="54" t="n"/>
-      <c r="AU32" s="54" t="n"/>
-      <c r="AV32" s="54" t="n"/>
-      <c r="AW32" s="54" t="n"/>
-      <c r="AX32" s="54" t="n"/>
-      <c r="AY32" s="54" t="n"/>
-      <c r="AZ32" s="54" t="n"/>
-      <c r="BA32" s="54" t="n"/>
-      <c r="BB32" s="54" t="n"/>
-      <c r="BC32" s="54" t="n"/>
-      <c r="BD32" s="54" t="n"/>
-      <c r="BE32" s="54" t="n"/>
-      <c r="BF32" s="54" t="n"/>
-      <c r="BG32" s="54" t="n"/>
-      <c r="BH32" s="54" t="n"/>
-      <c r="BI32" s="54" t="n"/>
+      <c r="J32" s="60" t="n"/>
+      <c r="K32" s="60" t="n"/>
+      <c r="L32" s="60" t="n"/>
+      <c r="M32" s="60" t="n"/>
+      <c r="N32" s="60" t="n"/>
+      <c r="O32" s="60" t="n"/>
+      <c r="P32" s="60" t="n"/>
+      <c r="Q32" s="60" t="n"/>
+      <c r="R32" s="60" t="n"/>
+      <c r="S32" s="60" t="n"/>
+      <c r="T32" s="60" t="n"/>
+      <c r="U32" s="60" t="n"/>
+      <c r="V32" s="60" t="n"/>
+      <c r="W32" s="60" t="n"/>
+      <c r="X32" s="60" t="n"/>
+      <c r="Y32" s="60" t="n"/>
+      <c r="Z32" s="60" t="n"/>
+      <c r="AA32" s="60" t="n"/>
+      <c r="AB32" s="60" t="n"/>
+      <c r="AC32" s="60" t="n"/>
+      <c r="AD32" s="60" t="n"/>
+      <c r="AE32" s="60" t="n"/>
+      <c r="AF32" s="60" t="n"/>
+      <c r="AG32" s="60" t="n"/>
+      <c r="AH32" s="60" t="n"/>
+      <c r="AI32" s="60" t="n"/>
+      <c r="AJ32" s="60" t="n"/>
+      <c r="AK32" s="60" t="n"/>
+      <c r="AL32" s="60" t="n"/>
+      <c r="AM32" s="60" t="n"/>
+      <c r="AN32" s="60" t="n"/>
+      <c r="AO32" s="60" t="n"/>
+      <c r="AP32" s="60" t="n"/>
+      <c r="AQ32" s="60" t="n"/>
+      <c r="AR32" s="60" t="n"/>
+      <c r="AS32" s="60" t="n"/>
+      <c r="AT32" s="60" t="n"/>
+      <c r="AU32" s="60" t="n"/>
+      <c r="AV32" s="60" t="n"/>
+      <c r="AW32" s="60" t="n"/>
+      <c r="AX32" s="60" t="n"/>
+      <c r="AY32" s="60" t="n"/>
+      <c r="AZ32" s="60" t="n"/>
+      <c r="BA32" s="60" t="n"/>
+      <c r="BB32" s="60" t="n"/>
+      <c r="BC32" s="60" t="n"/>
+      <c r="BD32" s="60" t="n"/>
+      <c r="BE32" s="60" t="n"/>
+      <c r="BF32" s="60" t="n"/>
+      <c r="BG32" s="60" t="n"/>
+      <c r="BH32" s="60" t="n"/>
+      <c r="BI32" s="60" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="B33" s="48">
+      <c r="B33" s="54">
         <f>IF(D33="","",27)</f>
         <v/>
       </c>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="50" t="n"/>
-      <c r="G33" s="51" t="n"/>
-      <c r="H33" s="52">
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="56" t="n"/>
+      <c r="F33" s="56" t="n"/>
+      <c r="G33" s="57" t="n"/>
+      <c r="H33" s="58">
         <f>IF(D33="","",IF(N(G33)&gt;=1,"Completada",IF(AND(N(F33)&gt;0,F33&lt;TODAY()),"Atrasada",IF(AND(N(E33)&gt;0,E33&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I33" s="53">
+      <c r="I33" s="59">
         <f>IF(OR(D33="",N(F33)=0,N(G33)&gt;=1),"",F33-TODAY())</f>
         <v/>
       </c>
-      <c r="J33" s="54" t="n"/>
-      <c r="K33" s="54" t="n"/>
-      <c r="L33" s="54" t="n"/>
-      <c r="M33" s="54" t="n"/>
-      <c r="N33" s="54" t="n"/>
-      <c r="O33" s="54" t="n"/>
-      <c r="P33" s="54" t="n"/>
-      <c r="Q33" s="54" t="n"/>
-      <c r="R33" s="54" t="n"/>
-      <c r="S33" s="54" t="n"/>
-      <c r="T33" s="54" t="n"/>
-      <c r="U33" s="54" t="n"/>
-      <c r="V33" s="54" t="n"/>
-      <c r="W33" s="54" t="n"/>
-      <c r="X33" s="54" t="n"/>
-      <c r="Y33" s="54" t="n"/>
-      <c r="Z33" s="54" t="n"/>
-      <c r="AA33" s="54" t="n"/>
-      <c r="AB33" s="54" t="n"/>
-      <c r="AC33" s="54" t="n"/>
-      <c r="AD33" s="54" t="n"/>
-      <c r="AE33" s="54" t="n"/>
-      <c r="AF33" s="54" t="n"/>
-      <c r="AG33" s="54" t="n"/>
-      <c r="AH33" s="54" t="n"/>
-      <c r="AI33" s="54" t="n"/>
-      <c r="AJ33" s="54" t="n"/>
-      <c r="AK33" s="54" t="n"/>
-      <c r="AL33" s="54" t="n"/>
-      <c r="AM33" s="54" t="n"/>
-      <c r="AN33" s="54" t="n"/>
-      <c r="AO33" s="54" t="n"/>
-      <c r="AP33" s="54" t="n"/>
-      <c r="AQ33" s="54" t="n"/>
-      <c r="AR33" s="54" t="n"/>
-      <c r="AS33" s="54" t="n"/>
-      <c r="AT33" s="54" t="n"/>
-      <c r="AU33" s="54" t="n"/>
-      <c r="AV33" s="54" t="n"/>
-      <c r="AW33" s="54" t="n"/>
-      <c r="AX33" s="54" t="n"/>
-      <c r="AY33" s="54" t="n"/>
-      <c r="AZ33" s="54" t="n"/>
-      <c r="BA33" s="54" t="n"/>
-      <c r="BB33" s="54" t="n"/>
-      <c r="BC33" s="54" t="n"/>
-      <c r="BD33" s="54" t="n"/>
-      <c r="BE33" s="54" t="n"/>
-      <c r="BF33" s="54" t="n"/>
-      <c r="BG33" s="54" t="n"/>
-      <c r="BH33" s="54" t="n"/>
-      <c r="BI33" s="54" t="n"/>
+      <c r="J33" s="60" t="n"/>
+      <c r="K33" s="60" t="n"/>
+      <c r="L33" s="60" t="n"/>
+      <c r="M33" s="60" t="n"/>
+      <c r="N33" s="60" t="n"/>
+      <c r="O33" s="60" t="n"/>
+      <c r="P33" s="60" t="n"/>
+      <c r="Q33" s="60" t="n"/>
+      <c r="R33" s="60" t="n"/>
+      <c r="S33" s="60" t="n"/>
+      <c r="T33" s="60" t="n"/>
+      <c r="U33" s="60" t="n"/>
+      <c r="V33" s="60" t="n"/>
+      <c r="W33" s="60" t="n"/>
+      <c r="X33" s="60" t="n"/>
+      <c r="Y33" s="60" t="n"/>
+      <c r="Z33" s="60" t="n"/>
+      <c r="AA33" s="60" t="n"/>
+      <c r="AB33" s="60" t="n"/>
+      <c r="AC33" s="60" t="n"/>
+      <c r="AD33" s="60" t="n"/>
+      <c r="AE33" s="60" t="n"/>
+      <c r="AF33" s="60" t="n"/>
+      <c r="AG33" s="60" t="n"/>
+      <c r="AH33" s="60" t="n"/>
+      <c r="AI33" s="60" t="n"/>
+      <c r="AJ33" s="60" t="n"/>
+      <c r="AK33" s="60" t="n"/>
+      <c r="AL33" s="60" t="n"/>
+      <c r="AM33" s="60" t="n"/>
+      <c r="AN33" s="60" t="n"/>
+      <c r="AO33" s="60" t="n"/>
+      <c r="AP33" s="60" t="n"/>
+      <c r="AQ33" s="60" t="n"/>
+      <c r="AR33" s="60" t="n"/>
+      <c r="AS33" s="60" t="n"/>
+      <c r="AT33" s="60" t="n"/>
+      <c r="AU33" s="60" t="n"/>
+      <c r="AV33" s="60" t="n"/>
+      <c r="AW33" s="60" t="n"/>
+      <c r="AX33" s="60" t="n"/>
+      <c r="AY33" s="60" t="n"/>
+      <c r="AZ33" s="60" t="n"/>
+      <c r="BA33" s="60" t="n"/>
+      <c r="BB33" s="60" t="n"/>
+      <c r="BC33" s="60" t="n"/>
+      <c r="BD33" s="60" t="n"/>
+      <c r="BE33" s="60" t="n"/>
+      <c r="BF33" s="60" t="n"/>
+      <c r="BG33" s="60" t="n"/>
+      <c r="BH33" s="60" t="n"/>
+      <c r="BI33" s="60" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="B34" s="48">
+      <c r="B34" s="54">
         <f>IF(D34="","",28)</f>
         <v/>
       </c>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="50" t="n"/>
-      <c r="G34" s="51" t="n"/>
-      <c r="H34" s="52">
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="56" t="n"/>
+      <c r="F34" s="56" t="n"/>
+      <c r="G34" s="57" t="n"/>
+      <c r="H34" s="58">
         <f>IF(D34="","",IF(N(G34)&gt;=1,"Completada",IF(AND(N(F34)&gt;0,F34&lt;TODAY()),"Atrasada",IF(AND(N(E34)&gt;0,E34&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I34" s="53">
+      <c r="I34" s="59">
         <f>IF(OR(D34="",N(F34)=0,N(G34)&gt;=1),"",F34-TODAY())</f>
         <v/>
       </c>
-      <c r="J34" s="54" t="n"/>
-      <c r="K34" s="54" t="n"/>
-      <c r="L34" s="54" t="n"/>
-      <c r="M34" s="54" t="n"/>
-      <c r="N34" s="54" t="n"/>
-      <c r="O34" s="54" t="n"/>
-      <c r="P34" s="54" t="n"/>
-      <c r="Q34" s="54" t="n"/>
-      <c r="R34" s="54" t="n"/>
-      <c r="S34" s="54" t="n"/>
-      <c r="T34" s="54" t="n"/>
-      <c r="U34" s="54" t="n"/>
-      <c r="V34" s="54" t="n"/>
-      <c r="W34" s="54" t="n"/>
-      <c r="X34" s="54" t="n"/>
-      <c r="Y34" s="54" t="n"/>
-      <c r="Z34" s="54" t="n"/>
-      <c r="AA34" s="54" t="n"/>
-      <c r="AB34" s="54" t="n"/>
-      <c r="AC34" s="54" t="n"/>
-      <c r="AD34" s="54" t="n"/>
-      <c r="AE34" s="54" t="n"/>
-      <c r="AF34" s="54" t="n"/>
-      <c r="AG34" s="54" t="n"/>
-      <c r="AH34" s="54" t="n"/>
-      <c r="AI34" s="54" t="n"/>
-      <c r="AJ34" s="54" t="n"/>
-      <c r="AK34" s="54" t="n"/>
-      <c r="AL34" s="54" t="n"/>
-      <c r="AM34" s="54" t="n"/>
-      <c r="AN34" s="54" t="n"/>
-      <c r="AO34" s="54" t="n"/>
-      <c r="AP34" s="54" t="n"/>
-      <c r="AQ34" s="54" t="n"/>
-      <c r="AR34" s="54" t="n"/>
-      <c r="AS34" s="54" t="n"/>
-      <c r="AT34" s="54" t="n"/>
-      <c r="AU34" s="54" t="n"/>
-      <c r="AV34" s="54" t="n"/>
-      <c r="AW34" s="54" t="n"/>
-      <c r="AX34" s="54" t="n"/>
-      <c r="AY34" s="54" t="n"/>
-      <c r="AZ34" s="54" t="n"/>
-      <c r="BA34" s="54" t="n"/>
-      <c r="BB34" s="54" t="n"/>
-      <c r="BC34" s="54" t="n"/>
-      <c r="BD34" s="54" t="n"/>
-      <c r="BE34" s="54" t="n"/>
-      <c r="BF34" s="54" t="n"/>
-      <c r="BG34" s="54" t="n"/>
-      <c r="BH34" s="54" t="n"/>
-      <c r="BI34" s="54" t="n"/>
+      <c r="J34" s="60" t="n"/>
+      <c r="K34" s="60" t="n"/>
+      <c r="L34" s="60" t="n"/>
+      <c r="M34" s="60" t="n"/>
+      <c r="N34" s="60" t="n"/>
+      <c r="O34" s="60" t="n"/>
+      <c r="P34" s="60" t="n"/>
+      <c r="Q34" s="60" t="n"/>
+      <c r="R34" s="60" t="n"/>
+      <c r="S34" s="60" t="n"/>
+      <c r="T34" s="60" t="n"/>
+      <c r="U34" s="60" t="n"/>
+      <c r="V34" s="60" t="n"/>
+      <c r="W34" s="60" t="n"/>
+      <c r="X34" s="60" t="n"/>
+      <c r="Y34" s="60" t="n"/>
+      <c r="Z34" s="60" t="n"/>
+      <c r="AA34" s="60" t="n"/>
+      <c r="AB34" s="60" t="n"/>
+      <c r="AC34" s="60" t="n"/>
+      <c r="AD34" s="60" t="n"/>
+      <c r="AE34" s="60" t="n"/>
+      <c r="AF34" s="60" t="n"/>
+      <c r="AG34" s="60" t="n"/>
+      <c r="AH34" s="60" t="n"/>
+      <c r="AI34" s="60" t="n"/>
+      <c r="AJ34" s="60" t="n"/>
+      <c r="AK34" s="60" t="n"/>
+      <c r="AL34" s="60" t="n"/>
+      <c r="AM34" s="60" t="n"/>
+      <c r="AN34" s="60" t="n"/>
+      <c r="AO34" s="60" t="n"/>
+      <c r="AP34" s="60" t="n"/>
+      <c r="AQ34" s="60" t="n"/>
+      <c r="AR34" s="60" t="n"/>
+      <c r="AS34" s="60" t="n"/>
+      <c r="AT34" s="60" t="n"/>
+      <c r="AU34" s="60" t="n"/>
+      <c r="AV34" s="60" t="n"/>
+      <c r="AW34" s="60" t="n"/>
+      <c r="AX34" s="60" t="n"/>
+      <c r="AY34" s="60" t="n"/>
+      <c r="AZ34" s="60" t="n"/>
+      <c r="BA34" s="60" t="n"/>
+      <c r="BB34" s="60" t="n"/>
+      <c r="BC34" s="60" t="n"/>
+      <c r="BD34" s="60" t="n"/>
+      <c r="BE34" s="60" t="n"/>
+      <c r="BF34" s="60" t="n"/>
+      <c r="BG34" s="60" t="n"/>
+      <c r="BH34" s="60" t="n"/>
+      <c r="BI34" s="60" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="B35" s="48">
+      <c r="B35" s="54">
         <f>IF(D35="","",29)</f>
         <v/>
       </c>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="50" t="n"/>
-      <c r="G35" s="51" t="n"/>
-      <c r="H35" s="52">
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
+      <c r="E35" s="56" t="n"/>
+      <c r="F35" s="56" t="n"/>
+      <c r="G35" s="57" t="n"/>
+      <c r="H35" s="58">
         <f>IF(D35="","",IF(N(G35)&gt;=1,"Completada",IF(AND(N(F35)&gt;0,F35&lt;TODAY()),"Atrasada",IF(AND(N(E35)&gt;0,E35&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I35" s="53">
+      <c r="I35" s="59">
         <f>IF(OR(D35="",N(F35)=0,N(G35)&gt;=1),"",F35-TODAY())</f>
         <v/>
       </c>
-      <c r="J35" s="54" t="n"/>
-      <c r="K35" s="54" t="n"/>
-      <c r="L35" s="54" t="n"/>
-      <c r="M35" s="54" t="n"/>
-      <c r="N35" s="54" t="n"/>
-      <c r="O35" s="54" t="n"/>
-      <c r="P35" s="54" t="n"/>
-      <c r="Q35" s="54" t="n"/>
-      <c r="R35" s="54" t="n"/>
-      <c r="S35" s="54" t="n"/>
-      <c r="T35" s="54" t="n"/>
-      <c r="U35" s="54" t="n"/>
-      <c r="V35" s="54" t="n"/>
-      <c r="W35" s="54" t="n"/>
-      <c r="X35" s="54" t="n"/>
-      <c r="Y35" s="54" t="n"/>
-      <c r="Z35" s="54" t="n"/>
-      <c r="AA35" s="54" t="n"/>
-      <c r="AB35" s="54" t="n"/>
-      <c r="AC35" s="54" t="n"/>
-      <c r="AD35" s="54" t="n"/>
-      <c r="AE35" s="54" t="n"/>
-      <c r="AF35" s="54" t="n"/>
-      <c r="AG35" s="54" t="n"/>
-      <c r="AH35" s="54" t="n"/>
-      <c r="AI35" s="54" t="n"/>
-      <c r="AJ35" s="54" t="n"/>
-      <c r="AK35" s="54" t="n"/>
-      <c r="AL35" s="54" t="n"/>
-      <c r="AM35" s="54" t="n"/>
-      <c r="AN35" s="54" t="n"/>
-      <c r="AO35" s="54" t="n"/>
-      <c r="AP35" s="54" t="n"/>
-      <c r="AQ35" s="54" t="n"/>
-      <c r="AR35" s="54" t="n"/>
-      <c r="AS35" s="54" t="n"/>
-      <c r="AT35" s="54" t="n"/>
-      <c r="AU35" s="54" t="n"/>
-      <c r="AV35" s="54" t="n"/>
-      <c r="AW35" s="54" t="n"/>
-      <c r="AX35" s="54" t="n"/>
-      <c r="AY35" s="54" t="n"/>
-      <c r="AZ35" s="54" t="n"/>
-      <c r="BA35" s="54" t="n"/>
-      <c r="BB35" s="54" t="n"/>
-      <c r="BC35" s="54" t="n"/>
-      <c r="BD35" s="54" t="n"/>
-      <c r="BE35" s="54" t="n"/>
-      <c r="BF35" s="54" t="n"/>
-      <c r="BG35" s="54" t="n"/>
-      <c r="BH35" s="54" t="n"/>
-      <c r="BI35" s="54" t="n"/>
+      <c r="J35" s="60" t="n"/>
+      <c r="K35" s="60" t="n"/>
+      <c r="L35" s="60" t="n"/>
+      <c r="M35" s="60" t="n"/>
+      <c r="N35" s="60" t="n"/>
+      <c r="O35" s="60" t="n"/>
+      <c r="P35" s="60" t="n"/>
+      <c r="Q35" s="60" t="n"/>
+      <c r="R35" s="60" t="n"/>
+      <c r="S35" s="60" t="n"/>
+      <c r="T35" s="60" t="n"/>
+      <c r="U35" s="60" t="n"/>
+      <c r="V35" s="60" t="n"/>
+      <c r="W35" s="60" t="n"/>
+      <c r="X35" s="60" t="n"/>
+      <c r="Y35" s="60" t="n"/>
+      <c r="Z35" s="60" t="n"/>
+      <c r="AA35" s="60" t="n"/>
+      <c r="AB35" s="60" t="n"/>
+      <c r="AC35" s="60" t="n"/>
+      <c r="AD35" s="60" t="n"/>
+      <c r="AE35" s="60" t="n"/>
+      <c r="AF35" s="60" t="n"/>
+      <c r="AG35" s="60" t="n"/>
+      <c r="AH35" s="60" t="n"/>
+      <c r="AI35" s="60" t="n"/>
+      <c r="AJ35" s="60" t="n"/>
+      <c r="AK35" s="60" t="n"/>
+      <c r="AL35" s="60" t="n"/>
+      <c r="AM35" s="60" t="n"/>
+      <c r="AN35" s="60" t="n"/>
+      <c r="AO35" s="60" t="n"/>
+      <c r="AP35" s="60" t="n"/>
+      <c r="AQ35" s="60" t="n"/>
+      <c r="AR35" s="60" t="n"/>
+      <c r="AS35" s="60" t="n"/>
+      <c r="AT35" s="60" t="n"/>
+      <c r="AU35" s="60" t="n"/>
+      <c r="AV35" s="60" t="n"/>
+      <c r="AW35" s="60" t="n"/>
+      <c r="AX35" s="60" t="n"/>
+      <c r="AY35" s="60" t="n"/>
+      <c r="AZ35" s="60" t="n"/>
+      <c r="BA35" s="60" t="n"/>
+      <c r="BB35" s="60" t="n"/>
+      <c r="BC35" s="60" t="n"/>
+      <c r="BD35" s="60" t="n"/>
+      <c r="BE35" s="60" t="n"/>
+      <c r="BF35" s="60" t="n"/>
+      <c r="BG35" s="60" t="n"/>
+      <c r="BH35" s="60" t="n"/>
+      <c r="BI35" s="60" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="B36" s="48">
+      <c r="B36" s="54">
         <f>IF(D36="","",30)</f>
         <v/>
       </c>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="50" t="n"/>
-      <c r="F36" s="50" t="n"/>
-      <c r="G36" s="51" t="n"/>
-      <c r="H36" s="52">
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="56" t="n"/>
+      <c r="F36" s="56" t="n"/>
+      <c r="G36" s="57" t="n"/>
+      <c r="H36" s="58">
         <f>IF(D36="","",IF(N(G36)&gt;=1,"Completada",IF(AND(N(F36)&gt;0,F36&lt;TODAY()),"Atrasada",IF(AND(N(E36)&gt;0,E36&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I36" s="53">
+      <c r="I36" s="59">
         <f>IF(OR(D36="",N(F36)=0,N(G36)&gt;=1),"",F36-TODAY())</f>
         <v/>
       </c>
-      <c r="J36" s="54" t="n"/>
-      <c r="K36" s="54" t="n"/>
-      <c r="L36" s="54" t="n"/>
-      <c r="M36" s="54" t="n"/>
-      <c r="N36" s="54" t="n"/>
-      <c r="O36" s="54" t="n"/>
-      <c r="P36" s="54" t="n"/>
-      <c r="Q36" s="54" t="n"/>
-      <c r="R36" s="54" t="n"/>
-      <c r="S36" s="54" t="n"/>
-      <c r="T36" s="54" t="n"/>
-      <c r="U36" s="54" t="n"/>
-      <c r="V36" s="54" t="n"/>
-      <c r="W36" s="54" t="n"/>
-      <c r="X36" s="54" t="n"/>
-      <c r="Y36" s="54" t="n"/>
-      <c r="Z36" s="54" t="n"/>
-      <c r="AA36" s="54" t="n"/>
-      <c r="AB36" s="54" t="n"/>
-      <c r="AC36" s="54" t="n"/>
-      <c r="AD36" s="54" t="n"/>
-      <c r="AE36" s="54" t="n"/>
-      <c r="AF36" s="54" t="n"/>
-      <c r="AG36" s="54" t="n"/>
-      <c r="AH36" s="54" t="n"/>
-      <c r="AI36" s="54" t="n"/>
-      <c r="AJ36" s="54" t="n"/>
-      <c r="AK36" s="54" t="n"/>
-      <c r="AL36" s="54" t="n"/>
-      <c r="AM36" s="54" t="n"/>
-      <c r="AN36" s="54" t="n"/>
-      <c r="AO36" s="54" t="n"/>
-      <c r="AP36" s="54" t="n"/>
-      <c r="AQ36" s="54" t="n"/>
-      <c r="AR36" s="54" t="n"/>
-      <c r="AS36" s="54" t="n"/>
-      <c r="AT36" s="54" t="n"/>
-      <c r="AU36" s="54" t="n"/>
-      <c r="AV36" s="54" t="n"/>
-      <c r="AW36" s="54" t="n"/>
-      <c r="AX36" s="54" t="n"/>
-      <c r="AY36" s="54" t="n"/>
-      <c r="AZ36" s="54" t="n"/>
-      <c r="BA36" s="54" t="n"/>
-      <c r="BB36" s="54" t="n"/>
-      <c r="BC36" s="54" t="n"/>
-      <c r="BD36" s="54" t="n"/>
-      <c r="BE36" s="54" t="n"/>
-      <c r="BF36" s="54" t="n"/>
-      <c r="BG36" s="54" t="n"/>
-      <c r="BH36" s="54" t="n"/>
-      <c r="BI36" s="54" t="n"/>
+      <c r="J36" s="60" t="n"/>
+      <c r="K36" s="60" t="n"/>
+      <c r="L36" s="60" t="n"/>
+      <c r="M36" s="60" t="n"/>
+      <c r="N36" s="60" t="n"/>
+      <c r="O36" s="60" t="n"/>
+      <c r="P36" s="60" t="n"/>
+      <c r="Q36" s="60" t="n"/>
+      <c r="R36" s="60" t="n"/>
+      <c r="S36" s="60" t="n"/>
+      <c r="T36" s="60" t="n"/>
+      <c r="U36" s="60" t="n"/>
+      <c r="V36" s="60" t="n"/>
+      <c r="W36" s="60" t="n"/>
+      <c r="X36" s="60" t="n"/>
+      <c r="Y36" s="60" t="n"/>
+      <c r="Z36" s="60" t="n"/>
+      <c r="AA36" s="60" t="n"/>
+      <c r="AB36" s="60" t="n"/>
+      <c r="AC36" s="60" t="n"/>
+      <c r="AD36" s="60" t="n"/>
+      <c r="AE36" s="60" t="n"/>
+      <c r="AF36" s="60" t="n"/>
+      <c r="AG36" s="60" t="n"/>
+      <c r="AH36" s="60" t="n"/>
+      <c r="AI36" s="60" t="n"/>
+      <c r="AJ36" s="60" t="n"/>
+      <c r="AK36" s="60" t="n"/>
+      <c r="AL36" s="60" t="n"/>
+      <c r="AM36" s="60" t="n"/>
+      <c r="AN36" s="60" t="n"/>
+      <c r="AO36" s="60" t="n"/>
+      <c r="AP36" s="60" t="n"/>
+      <c r="AQ36" s="60" t="n"/>
+      <c r="AR36" s="60" t="n"/>
+      <c r="AS36" s="60" t="n"/>
+      <c r="AT36" s="60" t="n"/>
+      <c r="AU36" s="60" t="n"/>
+      <c r="AV36" s="60" t="n"/>
+      <c r="AW36" s="60" t="n"/>
+      <c r="AX36" s="60" t="n"/>
+      <c r="AY36" s="60" t="n"/>
+      <c r="AZ36" s="60" t="n"/>
+      <c r="BA36" s="60" t="n"/>
+      <c r="BB36" s="60" t="n"/>
+      <c r="BC36" s="60" t="n"/>
+      <c r="BD36" s="60" t="n"/>
+      <c r="BE36" s="60" t="n"/>
+      <c r="BF36" s="60" t="n"/>
+      <c r="BG36" s="60" t="n"/>
+      <c r="BH36" s="60" t="n"/>
+      <c r="BI36" s="60" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="B37" s="48">
+      <c r="B37" s="54">
         <f>IF(D37="","",31)</f>
         <v/>
       </c>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="50" t="n"/>
-      <c r="F37" s="50" t="n"/>
-      <c r="G37" s="51" t="n"/>
-      <c r="H37" s="52">
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="56" t="n"/>
+      <c r="F37" s="56" t="n"/>
+      <c r="G37" s="57" t="n"/>
+      <c r="H37" s="58">
         <f>IF(D37="","",IF(N(G37)&gt;=1,"Completada",IF(AND(N(F37)&gt;0,F37&lt;TODAY()),"Atrasada",IF(AND(N(E37)&gt;0,E37&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I37" s="53">
+      <c r="I37" s="59">
         <f>IF(OR(D37="",N(F37)=0,N(G37)&gt;=1),"",F37-TODAY())</f>
         <v/>
       </c>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="54" t="n"/>
-      <c r="O37" s="54" t="n"/>
-      <c r="P37" s="54" t="n"/>
-      <c r="Q37" s="54" t="n"/>
-      <c r="R37" s="54" t="n"/>
-      <c r="S37" s="54" t="n"/>
-      <c r="T37" s="54" t="n"/>
-      <c r="U37" s="54" t="n"/>
-      <c r="V37" s="54" t="n"/>
-      <c r="W37" s="54" t="n"/>
-      <c r="X37" s="54" t="n"/>
-      <c r="Y37" s="54" t="n"/>
-      <c r="Z37" s="54" t="n"/>
-      <c r="AA37" s="54" t="n"/>
-      <c r="AB37" s="54" t="n"/>
-      <c r="AC37" s="54" t="n"/>
-      <c r="AD37" s="54" t="n"/>
-      <c r="AE37" s="54" t="n"/>
-      <c r="AF37" s="54" t="n"/>
-      <c r="AG37" s="54" t="n"/>
-      <c r="AH37" s="54" t="n"/>
-      <c r="AI37" s="54" t="n"/>
-      <c r="AJ37" s="54" t="n"/>
-      <c r="AK37" s="54" t="n"/>
-      <c r="AL37" s="54" t="n"/>
-      <c r="AM37" s="54" t="n"/>
-      <c r="AN37" s="54" t="n"/>
-      <c r="AO37" s="54" t="n"/>
-      <c r="AP37" s="54" t="n"/>
-      <c r="AQ37" s="54" t="n"/>
-      <c r="AR37" s="54" t="n"/>
-      <c r="AS37" s="54" t="n"/>
-      <c r="AT37" s="54" t="n"/>
-      <c r="AU37" s="54" t="n"/>
-      <c r="AV37" s="54" t="n"/>
-      <c r="AW37" s="54" t="n"/>
-      <c r="AX37" s="54" t="n"/>
-      <c r="AY37" s="54" t="n"/>
-      <c r="AZ37" s="54" t="n"/>
-      <c r="BA37" s="54" t="n"/>
-      <c r="BB37" s="54" t="n"/>
-      <c r="BC37" s="54" t="n"/>
-      <c r="BD37" s="54" t="n"/>
-      <c r="BE37" s="54" t="n"/>
-      <c r="BF37" s="54" t="n"/>
-      <c r="BG37" s="54" t="n"/>
-      <c r="BH37" s="54" t="n"/>
-      <c r="BI37" s="54" t="n"/>
+      <c r="J37" s="60" t="n"/>
+      <c r="K37" s="60" t="n"/>
+      <c r="L37" s="60" t="n"/>
+      <c r="M37" s="60" t="n"/>
+      <c r="N37" s="60" t="n"/>
+      <c r="O37" s="60" t="n"/>
+      <c r="P37" s="60" t="n"/>
+      <c r="Q37" s="60" t="n"/>
+      <c r="R37" s="60" t="n"/>
+      <c r="S37" s="60" t="n"/>
+      <c r="T37" s="60" t="n"/>
+      <c r="U37" s="60" t="n"/>
+      <c r="V37" s="60" t="n"/>
+      <c r="W37" s="60" t="n"/>
+      <c r="X37" s="60" t="n"/>
+      <c r="Y37" s="60" t="n"/>
+      <c r="Z37" s="60" t="n"/>
+      <c r="AA37" s="60" t="n"/>
+      <c r="AB37" s="60" t="n"/>
+      <c r="AC37" s="60" t="n"/>
+      <c r="AD37" s="60" t="n"/>
+      <c r="AE37" s="60" t="n"/>
+      <c r="AF37" s="60" t="n"/>
+      <c r="AG37" s="60" t="n"/>
+      <c r="AH37" s="60" t="n"/>
+      <c r="AI37" s="60" t="n"/>
+      <c r="AJ37" s="60" t="n"/>
+      <c r="AK37" s="60" t="n"/>
+      <c r="AL37" s="60" t="n"/>
+      <c r="AM37" s="60" t="n"/>
+      <c r="AN37" s="60" t="n"/>
+      <c r="AO37" s="60" t="n"/>
+      <c r="AP37" s="60" t="n"/>
+      <c r="AQ37" s="60" t="n"/>
+      <c r="AR37" s="60" t="n"/>
+      <c r="AS37" s="60" t="n"/>
+      <c r="AT37" s="60" t="n"/>
+      <c r="AU37" s="60" t="n"/>
+      <c r="AV37" s="60" t="n"/>
+      <c r="AW37" s="60" t="n"/>
+      <c r="AX37" s="60" t="n"/>
+      <c r="AY37" s="60" t="n"/>
+      <c r="AZ37" s="60" t="n"/>
+      <c r="BA37" s="60" t="n"/>
+      <c r="BB37" s="60" t="n"/>
+      <c r="BC37" s="60" t="n"/>
+      <c r="BD37" s="60" t="n"/>
+      <c r="BE37" s="60" t="n"/>
+      <c r="BF37" s="60" t="n"/>
+      <c r="BG37" s="60" t="n"/>
+      <c r="BH37" s="60" t="n"/>
+      <c r="BI37" s="60" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="B38" s="48">
+      <c r="B38" s="54">
         <f>IF(D38="","",32)</f>
         <v/>
       </c>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="50" t="n"/>
-      <c r="F38" s="50" t="n"/>
-      <c r="G38" s="51" t="n"/>
-      <c r="H38" s="52">
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="56" t="n"/>
+      <c r="F38" s="56" t="n"/>
+      <c r="G38" s="57" t="n"/>
+      <c r="H38" s="58">
         <f>IF(D38="","",IF(N(G38)&gt;=1,"Completada",IF(AND(N(F38)&gt;0,F38&lt;TODAY()),"Atrasada",IF(AND(N(E38)&gt;0,E38&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I38" s="53">
+      <c r="I38" s="59">
         <f>IF(OR(D38="",N(F38)=0,N(G38)&gt;=1),"",F38-TODAY())</f>
         <v/>
       </c>
-      <c r="J38" s="54" t="n"/>
-      <c r="K38" s="54" t="n"/>
-      <c r="L38" s="54" t="n"/>
-      <c r="M38" s="54" t="n"/>
-      <c r="N38" s="54" t="n"/>
-      <c r="O38" s="54" t="n"/>
-      <c r="P38" s="54" t="n"/>
-      <c r="Q38" s="54" t="n"/>
-      <c r="R38" s="54" t="n"/>
-      <c r="S38" s="54" t="n"/>
-      <c r="T38" s="54" t="n"/>
-      <c r="U38" s="54" t="n"/>
-      <c r="V38" s="54" t="n"/>
-      <c r="W38" s="54" t="n"/>
-      <c r="X38" s="54" t="n"/>
-      <c r="Y38" s="54" t="n"/>
-      <c r="Z38" s="54" t="n"/>
-      <c r="AA38" s="54" t="n"/>
-      <c r="AB38" s="54" t="n"/>
-      <c r="AC38" s="54" t="n"/>
-      <c r="AD38" s="54" t="n"/>
-      <c r="AE38" s="54" t="n"/>
-      <c r="AF38" s="54" t="n"/>
-      <c r="AG38" s="54" t="n"/>
-      <c r="AH38" s="54" t="n"/>
-      <c r="AI38" s="54" t="n"/>
-      <c r="AJ38" s="54" t="n"/>
-      <c r="AK38" s="54" t="n"/>
-      <c r="AL38" s="54" t="n"/>
-      <c r="AM38" s="54" t="n"/>
-      <c r="AN38" s="54" t="n"/>
-      <c r="AO38" s="54" t="n"/>
-      <c r="AP38" s="54" t="n"/>
-      <c r="AQ38" s="54" t="n"/>
-      <c r="AR38" s="54" t="n"/>
-      <c r="AS38" s="54" t="n"/>
-      <c r="AT38" s="54" t="n"/>
-      <c r="AU38" s="54" t="n"/>
-      <c r="AV38" s="54" t="n"/>
-      <c r="AW38" s="54" t="n"/>
-      <c r="AX38" s="54" t="n"/>
-      <c r="AY38" s="54" t="n"/>
-      <c r="AZ38" s="54" t="n"/>
-      <c r="BA38" s="54" t="n"/>
-      <c r="BB38" s="54" t="n"/>
-      <c r="BC38" s="54" t="n"/>
-      <c r="BD38" s="54" t="n"/>
-      <c r="BE38" s="54" t="n"/>
-      <c r="BF38" s="54" t="n"/>
-      <c r="BG38" s="54" t="n"/>
-      <c r="BH38" s="54" t="n"/>
-      <c r="BI38" s="54" t="n"/>
+      <c r="J38" s="60" t="n"/>
+      <c r="K38" s="60" t="n"/>
+      <c r="L38" s="60" t="n"/>
+      <c r="M38" s="60" t="n"/>
+      <c r="N38" s="60" t="n"/>
+      <c r="O38" s="60" t="n"/>
+      <c r="P38" s="60" t="n"/>
+      <c r="Q38" s="60" t="n"/>
+      <c r="R38" s="60" t="n"/>
+      <c r="S38" s="60" t="n"/>
+      <c r="T38" s="60" t="n"/>
+      <c r="U38" s="60" t="n"/>
+      <c r="V38" s="60" t="n"/>
+      <c r="W38" s="60" t="n"/>
+      <c r="X38" s="60" t="n"/>
+      <c r="Y38" s="60" t="n"/>
+      <c r="Z38" s="60" t="n"/>
+      <c r="AA38" s="60" t="n"/>
+      <c r="AB38" s="60" t="n"/>
+      <c r="AC38" s="60" t="n"/>
+      <c r="AD38" s="60" t="n"/>
+      <c r="AE38" s="60" t="n"/>
+      <c r="AF38" s="60" t="n"/>
+      <c r="AG38" s="60" t="n"/>
+      <c r="AH38" s="60" t="n"/>
+      <c r="AI38" s="60" t="n"/>
+      <c r="AJ38" s="60" t="n"/>
+      <c r="AK38" s="60" t="n"/>
+      <c r="AL38" s="60" t="n"/>
+      <c r="AM38" s="60" t="n"/>
+      <c r="AN38" s="60" t="n"/>
+      <c r="AO38" s="60" t="n"/>
+      <c r="AP38" s="60" t="n"/>
+      <c r="AQ38" s="60" t="n"/>
+      <c r="AR38" s="60" t="n"/>
+      <c r="AS38" s="60" t="n"/>
+      <c r="AT38" s="60" t="n"/>
+      <c r="AU38" s="60" t="n"/>
+      <c r="AV38" s="60" t="n"/>
+      <c r="AW38" s="60" t="n"/>
+      <c r="AX38" s="60" t="n"/>
+      <c r="AY38" s="60" t="n"/>
+      <c r="AZ38" s="60" t="n"/>
+      <c r="BA38" s="60" t="n"/>
+      <c r="BB38" s="60" t="n"/>
+      <c r="BC38" s="60" t="n"/>
+      <c r="BD38" s="60" t="n"/>
+      <c r="BE38" s="60" t="n"/>
+      <c r="BF38" s="60" t="n"/>
+      <c r="BG38" s="60" t="n"/>
+      <c r="BH38" s="60" t="n"/>
+      <c r="BI38" s="60" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="B39" s="48">
+      <c r="B39" s="54">
         <f>IF(D39="","",33)</f>
         <v/>
       </c>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="50" t="n"/>
-      <c r="F39" s="50" t="n"/>
-      <c r="G39" s="51" t="n"/>
-      <c r="H39" s="52">
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="56" t="n"/>
+      <c r="F39" s="56" t="n"/>
+      <c r="G39" s="57" t="n"/>
+      <c r="H39" s="58">
         <f>IF(D39="","",IF(N(G39)&gt;=1,"Completada",IF(AND(N(F39)&gt;0,F39&lt;TODAY()),"Atrasada",IF(AND(N(E39)&gt;0,E39&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I39" s="53">
+      <c r="I39" s="59">
         <f>IF(OR(D39="",N(F39)=0,N(G39)&gt;=1),"",F39-TODAY())</f>
         <v/>
       </c>
-      <c r="J39" s="54" t="n"/>
-      <c r="K39" s="54" t="n"/>
-      <c r="L39" s="54" t="n"/>
-      <c r="M39" s="54" t="n"/>
-      <c r="N39" s="54" t="n"/>
-      <c r="O39" s="54" t="n"/>
-      <c r="P39" s="54" t="n"/>
-      <c r="Q39" s="54" t="n"/>
-      <c r="R39" s="54" t="n"/>
-      <c r="S39" s="54" t="n"/>
-      <c r="T39" s="54" t="n"/>
-      <c r="U39" s="54" t="n"/>
-      <c r="V39" s="54" t="n"/>
-      <c r="W39" s="54" t="n"/>
-      <c r="X39" s="54" t="n"/>
-      <c r="Y39" s="54" t="n"/>
-      <c r="Z39" s="54" t="n"/>
-      <c r="AA39" s="54" t="n"/>
-      <c r="AB39" s="54" t="n"/>
-      <c r="AC39" s="54" t="n"/>
-      <c r="AD39" s="54" t="n"/>
-      <c r="AE39" s="54" t="n"/>
-      <c r="AF39" s="54" t="n"/>
-      <c r="AG39" s="54" t="n"/>
-      <c r="AH39" s="54" t="n"/>
-      <c r="AI39" s="54" t="n"/>
-      <c r="AJ39" s="54" t="n"/>
-      <c r="AK39" s="54" t="n"/>
-      <c r="AL39" s="54" t="n"/>
-      <c r="AM39" s="54" t="n"/>
-      <c r="AN39" s="54" t="n"/>
-      <c r="AO39" s="54" t="n"/>
-      <c r="AP39" s="54" t="n"/>
-      <c r="AQ39" s="54" t="n"/>
-      <c r="AR39" s="54" t="n"/>
-      <c r="AS39" s="54" t="n"/>
-      <c r="AT39" s="54" t="n"/>
-      <c r="AU39" s="54" t="n"/>
-      <c r="AV39" s="54" t="n"/>
-      <c r="AW39" s="54" t="n"/>
-      <c r="AX39" s="54" t="n"/>
-      <c r="AY39" s="54" t="n"/>
-      <c r="AZ39" s="54" t="n"/>
-      <c r="BA39" s="54" t="n"/>
-      <c r="BB39" s="54" t="n"/>
-      <c r="BC39" s="54" t="n"/>
-      <c r="BD39" s="54" t="n"/>
-      <c r="BE39" s="54" t="n"/>
-      <c r="BF39" s="54" t="n"/>
-      <c r="BG39" s="54" t="n"/>
-      <c r="BH39" s="54" t="n"/>
-      <c r="BI39" s="54" t="n"/>
+      <c r="J39" s="60" t="n"/>
+      <c r="K39" s="60" t="n"/>
+      <c r="L39" s="60" t="n"/>
+      <c r="M39" s="60" t="n"/>
+      <c r="N39" s="60" t="n"/>
+      <c r="O39" s="60" t="n"/>
+      <c r="P39" s="60" t="n"/>
+      <c r="Q39" s="60" t="n"/>
+      <c r="R39" s="60" t="n"/>
+      <c r="S39" s="60" t="n"/>
+      <c r="T39" s="60" t="n"/>
+      <c r="U39" s="60" t="n"/>
+      <c r="V39" s="60" t="n"/>
+      <c r="W39" s="60" t="n"/>
+      <c r="X39" s="60" t="n"/>
+      <c r="Y39" s="60" t="n"/>
+      <c r="Z39" s="60" t="n"/>
+      <c r="AA39" s="60" t="n"/>
+      <c r="AB39" s="60" t="n"/>
+      <c r="AC39" s="60" t="n"/>
+      <c r="AD39" s="60" t="n"/>
+      <c r="AE39" s="60" t="n"/>
+      <c r="AF39" s="60" t="n"/>
+      <c r="AG39" s="60" t="n"/>
+      <c r="AH39" s="60" t="n"/>
+      <c r="AI39" s="60" t="n"/>
+      <c r="AJ39" s="60" t="n"/>
+      <c r="AK39" s="60" t="n"/>
+      <c r="AL39" s="60" t="n"/>
+      <c r="AM39" s="60" t="n"/>
+      <c r="AN39" s="60" t="n"/>
+      <c r="AO39" s="60" t="n"/>
+      <c r="AP39" s="60" t="n"/>
+      <c r="AQ39" s="60" t="n"/>
+      <c r="AR39" s="60" t="n"/>
+      <c r="AS39" s="60" t="n"/>
+      <c r="AT39" s="60" t="n"/>
+      <c r="AU39" s="60" t="n"/>
+      <c r="AV39" s="60" t="n"/>
+      <c r="AW39" s="60" t="n"/>
+      <c r="AX39" s="60" t="n"/>
+      <c r="AY39" s="60" t="n"/>
+      <c r="AZ39" s="60" t="n"/>
+      <c r="BA39" s="60" t="n"/>
+      <c r="BB39" s="60" t="n"/>
+      <c r="BC39" s="60" t="n"/>
+      <c r="BD39" s="60" t="n"/>
+      <c r="BE39" s="60" t="n"/>
+      <c r="BF39" s="60" t="n"/>
+      <c r="BG39" s="60" t="n"/>
+      <c r="BH39" s="60" t="n"/>
+      <c r="BI39" s="60" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="B40" s="48">
+      <c r="B40" s="54">
         <f>IF(D40="","",34)</f>
         <v/>
       </c>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="50" t="n"/>
-      <c r="F40" s="50" t="n"/>
-      <c r="G40" s="51" t="n"/>
-      <c r="H40" s="52">
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="56" t="n"/>
+      <c r="F40" s="56" t="n"/>
+      <c r="G40" s="57" t="n"/>
+      <c r="H40" s="58">
         <f>IF(D40="","",IF(N(G40)&gt;=1,"Completada",IF(AND(N(F40)&gt;0,F40&lt;TODAY()),"Atrasada",IF(AND(N(E40)&gt;0,E40&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I40" s="53">
+      <c r="I40" s="59">
         <f>IF(OR(D40="",N(F40)=0,N(G40)&gt;=1),"",F40-TODAY())</f>
         <v/>
       </c>
-      <c r="J40" s="54" t="n"/>
-      <c r="K40" s="54" t="n"/>
-      <c r="L40" s="54" t="n"/>
-      <c r="M40" s="54" t="n"/>
-      <c r="N40" s="54" t="n"/>
-      <c r="O40" s="54" t="n"/>
-      <c r="P40" s="54" t="n"/>
-      <c r="Q40" s="54" t="n"/>
-      <c r="R40" s="54" t="n"/>
-      <c r="S40" s="54" t="n"/>
-      <c r="T40" s="54" t="n"/>
-      <c r="U40" s="54" t="n"/>
-      <c r="V40" s="54" t="n"/>
-      <c r="W40" s="54" t="n"/>
-      <c r="X40" s="54" t="n"/>
-      <c r="Y40" s="54" t="n"/>
-      <c r="Z40" s="54" t="n"/>
-      <c r="AA40" s="54" t="n"/>
-      <c r="AB40" s="54" t="n"/>
-      <c r="AC40" s="54" t="n"/>
-      <c r="AD40" s="54" t="n"/>
-      <c r="AE40" s="54" t="n"/>
-      <c r="AF40" s="54" t="n"/>
-      <c r="AG40" s="54" t="n"/>
-      <c r="AH40" s="54" t="n"/>
-      <c r="AI40" s="54" t="n"/>
-      <c r="AJ40" s="54" t="n"/>
-      <c r="AK40" s="54" t="n"/>
-      <c r="AL40" s="54" t="n"/>
-      <c r="AM40" s="54" t="n"/>
-      <c r="AN40" s="54" t="n"/>
-      <c r="AO40" s="54" t="n"/>
-      <c r="AP40" s="54" t="n"/>
-      <c r="AQ40" s="54" t="n"/>
-      <c r="AR40" s="54" t="n"/>
-      <c r="AS40" s="54" t="n"/>
-      <c r="AT40" s="54" t="n"/>
-      <c r="AU40" s="54" t="n"/>
-      <c r="AV40" s="54" t="n"/>
-      <c r="AW40" s="54" t="n"/>
-      <c r="AX40" s="54" t="n"/>
-      <c r="AY40" s="54" t="n"/>
-      <c r="AZ40" s="54" t="n"/>
-      <c r="BA40" s="54" t="n"/>
-      <c r="BB40" s="54" t="n"/>
-      <c r="BC40" s="54" t="n"/>
-      <c r="BD40" s="54" t="n"/>
-      <c r="BE40" s="54" t="n"/>
-      <c r="BF40" s="54" t="n"/>
-      <c r="BG40" s="54" t="n"/>
-      <c r="BH40" s="54" t="n"/>
-      <c r="BI40" s="54" t="n"/>
+      <c r="J40" s="60" t="n"/>
+      <c r="K40" s="60" t="n"/>
+      <c r="L40" s="60" t="n"/>
+      <c r="M40" s="60" t="n"/>
+      <c r="N40" s="60" t="n"/>
+      <c r="O40" s="60" t="n"/>
+      <c r="P40" s="60" t="n"/>
+      <c r="Q40" s="60" t="n"/>
+      <c r="R40" s="60" t="n"/>
+      <c r="S40" s="60" t="n"/>
+      <c r="T40" s="60" t="n"/>
+      <c r="U40" s="60" t="n"/>
+      <c r="V40" s="60" t="n"/>
+      <c r="W40" s="60" t="n"/>
+      <c r="X40" s="60" t="n"/>
+      <c r="Y40" s="60" t="n"/>
+      <c r="Z40" s="60" t="n"/>
+      <c r="AA40" s="60" t="n"/>
+      <c r="AB40" s="60" t="n"/>
+      <c r="AC40" s="60" t="n"/>
+      <c r="AD40" s="60" t="n"/>
+      <c r="AE40" s="60" t="n"/>
+      <c r="AF40" s="60" t="n"/>
+      <c r="AG40" s="60" t="n"/>
+      <c r="AH40" s="60" t="n"/>
+      <c r="AI40" s="60" t="n"/>
+      <c r="AJ40" s="60" t="n"/>
+      <c r="AK40" s="60" t="n"/>
+      <c r="AL40" s="60" t="n"/>
+      <c r="AM40" s="60" t="n"/>
+      <c r="AN40" s="60" t="n"/>
+      <c r="AO40" s="60" t="n"/>
+      <c r="AP40" s="60" t="n"/>
+      <c r="AQ40" s="60" t="n"/>
+      <c r="AR40" s="60" t="n"/>
+      <c r="AS40" s="60" t="n"/>
+      <c r="AT40" s="60" t="n"/>
+      <c r="AU40" s="60" t="n"/>
+      <c r="AV40" s="60" t="n"/>
+      <c r="AW40" s="60" t="n"/>
+      <c r="AX40" s="60" t="n"/>
+      <c r="AY40" s="60" t="n"/>
+      <c r="AZ40" s="60" t="n"/>
+      <c r="BA40" s="60" t="n"/>
+      <c r="BB40" s="60" t="n"/>
+      <c r="BC40" s="60" t="n"/>
+      <c r="BD40" s="60" t="n"/>
+      <c r="BE40" s="60" t="n"/>
+      <c r="BF40" s="60" t="n"/>
+      <c r="BG40" s="60" t="n"/>
+      <c r="BH40" s="60" t="n"/>
+      <c r="BI40" s="60" t="n"/>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="B41" s="48">
+      <c r="B41" s="54">
         <f>IF(D41="","",35)</f>
         <v/>
       </c>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
-      <c r="E41" s="50" t="n"/>
-      <c r="F41" s="50" t="n"/>
-      <c r="G41" s="51" t="n"/>
-      <c r="H41" s="52">
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="56" t="n"/>
+      <c r="F41" s="56" t="n"/>
+      <c r="G41" s="57" t="n"/>
+      <c r="H41" s="58">
         <f>IF(D41="","",IF(N(G41)&gt;=1,"Completada",IF(AND(N(F41)&gt;0,F41&lt;TODAY()),"Atrasada",IF(AND(N(E41)&gt;0,E41&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I41" s="53">
+      <c r="I41" s="59">
         <f>IF(OR(D41="",N(F41)=0,N(G41)&gt;=1),"",F41-TODAY())</f>
         <v/>
       </c>
-      <c r="J41" s="54" t="n"/>
-      <c r="K41" s="54" t="n"/>
-      <c r="L41" s="54" t="n"/>
-      <c r="M41" s="54" t="n"/>
-      <c r="N41" s="54" t="n"/>
-      <c r="O41" s="54" t="n"/>
-      <c r="P41" s="54" t="n"/>
-      <c r="Q41" s="54" t="n"/>
-      <c r="R41" s="54" t="n"/>
-      <c r="S41" s="54" t="n"/>
-      <c r="T41" s="54" t="n"/>
-      <c r="U41" s="54" t="n"/>
-      <c r="V41" s="54" t="n"/>
-      <c r="W41" s="54" t="n"/>
-      <c r="X41" s="54" t="n"/>
-      <c r="Y41" s="54" t="n"/>
-      <c r="Z41" s="54" t="n"/>
-      <c r="AA41" s="54" t="n"/>
-      <c r="AB41" s="54" t="n"/>
-      <c r="AC41" s="54" t="n"/>
-      <c r="AD41" s="54" t="n"/>
-      <c r="AE41" s="54" t="n"/>
-      <c r="AF41" s="54" t="n"/>
-      <c r="AG41" s="54" t="n"/>
-      <c r="AH41" s="54" t="n"/>
-      <c r="AI41" s="54" t="n"/>
-      <c r="AJ41" s="54" t="n"/>
-      <c r="AK41" s="54" t="n"/>
-      <c r="AL41" s="54" t="n"/>
-      <c r="AM41" s="54" t="n"/>
-      <c r="AN41" s="54" t="n"/>
-      <c r="AO41" s="54" t="n"/>
-      <c r="AP41" s="54" t="n"/>
-      <c r="AQ41" s="54" t="n"/>
-      <c r="AR41" s="54" t="n"/>
-      <c r="AS41" s="54" t="n"/>
-      <c r="AT41" s="54" t="n"/>
-      <c r="AU41" s="54" t="n"/>
-      <c r="AV41" s="54" t="n"/>
-      <c r="AW41" s="54" t="n"/>
-      <c r="AX41" s="54" t="n"/>
-      <c r="AY41" s="54" t="n"/>
-      <c r="AZ41" s="54" t="n"/>
-      <c r="BA41" s="54" t="n"/>
-      <c r="BB41" s="54" t="n"/>
-      <c r="BC41" s="54" t="n"/>
-      <c r="BD41" s="54" t="n"/>
-      <c r="BE41" s="54" t="n"/>
-      <c r="BF41" s="54" t="n"/>
-      <c r="BG41" s="54" t="n"/>
-      <c r="BH41" s="54" t="n"/>
-      <c r="BI41" s="54" t="n"/>
+      <c r="J41" s="60" t="n"/>
+      <c r="K41" s="60" t="n"/>
+      <c r="L41" s="60" t="n"/>
+      <c r="M41" s="60" t="n"/>
+      <c r="N41" s="60" t="n"/>
+      <c r="O41" s="60" t="n"/>
+      <c r="P41" s="60" t="n"/>
+      <c r="Q41" s="60" t="n"/>
+      <c r="R41" s="60" t="n"/>
+      <c r="S41" s="60" t="n"/>
+      <c r="T41" s="60" t="n"/>
+      <c r="U41" s="60" t="n"/>
+      <c r="V41" s="60" t="n"/>
+      <c r="W41" s="60" t="n"/>
+      <c r="X41" s="60" t="n"/>
+      <c r="Y41" s="60" t="n"/>
+      <c r="Z41" s="60" t="n"/>
+      <c r="AA41" s="60" t="n"/>
+      <c r="AB41" s="60" t="n"/>
+      <c r="AC41" s="60" t="n"/>
+      <c r="AD41" s="60" t="n"/>
+      <c r="AE41" s="60" t="n"/>
+      <c r="AF41" s="60" t="n"/>
+      <c r="AG41" s="60" t="n"/>
+      <c r="AH41" s="60" t="n"/>
+      <c r="AI41" s="60" t="n"/>
+      <c r="AJ41" s="60" t="n"/>
+      <c r="AK41" s="60" t="n"/>
+      <c r="AL41" s="60" t="n"/>
+      <c r="AM41" s="60" t="n"/>
+      <c r="AN41" s="60" t="n"/>
+      <c r="AO41" s="60" t="n"/>
+      <c r="AP41" s="60" t="n"/>
+      <c r="AQ41" s="60" t="n"/>
+      <c r="AR41" s="60" t="n"/>
+      <c r="AS41" s="60" t="n"/>
+      <c r="AT41" s="60" t="n"/>
+      <c r="AU41" s="60" t="n"/>
+      <c r="AV41" s="60" t="n"/>
+      <c r="AW41" s="60" t="n"/>
+      <c r="AX41" s="60" t="n"/>
+      <c r="AY41" s="60" t="n"/>
+      <c r="AZ41" s="60" t="n"/>
+      <c r="BA41" s="60" t="n"/>
+      <c r="BB41" s="60" t="n"/>
+      <c r="BC41" s="60" t="n"/>
+      <c r="BD41" s="60" t="n"/>
+      <c r="BE41" s="60" t="n"/>
+      <c r="BF41" s="60" t="n"/>
+      <c r="BG41" s="60" t="n"/>
+      <c r="BH41" s="60" t="n"/>
+      <c r="BI41" s="60" t="n"/>
     </row>
     <row r="42" ht="19" customHeight="1">
-      <c r="B42" s="48">
+      <c r="B42" s="54">
         <f>IF(D42="","",36)</f>
         <v/>
       </c>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
-      <c r="E42" s="50" t="n"/>
-      <c r="F42" s="50" t="n"/>
-      <c r="G42" s="51" t="n"/>
-      <c r="H42" s="52">
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="56" t="n"/>
+      <c r="F42" s="56" t="n"/>
+      <c r="G42" s="57" t="n"/>
+      <c r="H42" s="58">
         <f>IF(D42="","",IF(N(G42)&gt;=1,"Completada",IF(AND(N(F42)&gt;0,F42&lt;TODAY()),"Atrasada",IF(AND(N(E42)&gt;0,E42&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I42" s="53">
+      <c r="I42" s="59">
         <f>IF(OR(D42="",N(F42)=0,N(G42)&gt;=1),"",F42-TODAY())</f>
         <v/>
       </c>
-      <c r="J42" s="54" t="n"/>
-      <c r="K42" s="54" t="n"/>
-      <c r="L42" s="54" t="n"/>
-      <c r="M42" s="54" t="n"/>
-      <c r="N42" s="54" t="n"/>
-      <c r="O42" s="54" t="n"/>
-      <c r="P42" s="54" t="n"/>
-      <c r="Q42" s="54" t="n"/>
-      <c r="R42" s="54" t="n"/>
-      <c r="S42" s="54" t="n"/>
-      <c r="T42" s="54" t="n"/>
-      <c r="U42" s="54" t="n"/>
-      <c r="V42" s="54" t="n"/>
-      <c r="W42" s="54" t="n"/>
-      <c r="X42" s="54" t="n"/>
-      <c r="Y42" s="54" t="n"/>
-      <c r="Z42" s="54" t="n"/>
-      <c r="AA42" s="54" t="n"/>
-      <c r="AB42" s="54" t="n"/>
-      <c r="AC42" s="54" t="n"/>
-      <c r="AD42" s="54" t="n"/>
-      <c r="AE42" s="54" t="n"/>
-      <c r="AF42" s="54" t="n"/>
-      <c r="AG42" s="54" t="n"/>
-      <c r="AH42" s="54" t="n"/>
-      <c r="AI42" s="54" t="n"/>
-      <c r="AJ42" s="54" t="n"/>
-      <c r="AK42" s="54" t="n"/>
-      <c r="AL42" s="54" t="n"/>
-      <c r="AM42" s="54" t="n"/>
-      <c r="AN42" s="54" t="n"/>
-      <c r="AO42" s="54" t="n"/>
-      <c r="AP42" s="54" t="n"/>
-      <c r="AQ42" s="54" t="n"/>
-      <c r="AR42" s="54" t="n"/>
-      <c r="AS42" s="54" t="n"/>
-      <c r="AT42" s="54" t="n"/>
-      <c r="AU42" s="54" t="n"/>
-      <c r="AV42" s="54" t="n"/>
-      <c r="AW42" s="54" t="n"/>
-      <c r="AX42" s="54" t="n"/>
-      <c r="AY42" s="54" t="n"/>
-      <c r="AZ42" s="54" t="n"/>
-      <c r="BA42" s="54" t="n"/>
-      <c r="BB42" s="54" t="n"/>
-      <c r="BC42" s="54" t="n"/>
-      <c r="BD42" s="54" t="n"/>
-      <c r="BE42" s="54" t="n"/>
-      <c r="BF42" s="54" t="n"/>
-      <c r="BG42" s="54" t="n"/>
-      <c r="BH42" s="54" t="n"/>
-      <c r="BI42" s="54" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+      <c r="N42" s="60" t="n"/>
+      <c r="O42" s="60" t="n"/>
+      <c r="P42" s="60" t="n"/>
+      <c r="Q42" s="60" t="n"/>
+      <c r="R42" s="60" t="n"/>
+      <c r="S42" s="60" t="n"/>
+      <c r="T42" s="60" t="n"/>
+      <c r="U42" s="60" t="n"/>
+      <c r="V42" s="60" t="n"/>
+      <c r="W42" s="60" t="n"/>
+      <c r="X42" s="60" t="n"/>
+      <c r="Y42" s="60" t="n"/>
+      <c r="Z42" s="60" t="n"/>
+      <c r="AA42" s="60" t="n"/>
+      <c r="AB42" s="60" t="n"/>
+      <c r="AC42" s="60" t="n"/>
+      <c r="AD42" s="60" t="n"/>
+      <c r="AE42" s="60" t="n"/>
+      <c r="AF42" s="60" t="n"/>
+      <c r="AG42" s="60" t="n"/>
+      <c r="AH42" s="60" t="n"/>
+      <c r="AI42" s="60" t="n"/>
+      <c r="AJ42" s="60" t="n"/>
+      <c r="AK42" s="60" t="n"/>
+      <c r="AL42" s="60" t="n"/>
+      <c r="AM42" s="60" t="n"/>
+      <c r="AN42" s="60" t="n"/>
+      <c r="AO42" s="60" t="n"/>
+      <c r="AP42" s="60" t="n"/>
+      <c r="AQ42" s="60" t="n"/>
+      <c r="AR42" s="60" t="n"/>
+      <c r="AS42" s="60" t="n"/>
+      <c r="AT42" s="60" t="n"/>
+      <c r="AU42" s="60" t="n"/>
+      <c r="AV42" s="60" t="n"/>
+      <c r="AW42" s="60" t="n"/>
+      <c r="AX42" s="60" t="n"/>
+      <c r="AY42" s="60" t="n"/>
+      <c r="AZ42" s="60" t="n"/>
+      <c r="BA42" s="60" t="n"/>
+      <c r="BB42" s="60" t="n"/>
+      <c r="BC42" s="60" t="n"/>
+      <c r="BD42" s="60" t="n"/>
+      <c r="BE42" s="60" t="n"/>
+      <c r="BF42" s="60" t="n"/>
+      <c r="BG42" s="60" t="n"/>
+      <c r="BH42" s="60" t="n"/>
+      <c r="BI42" s="60" t="n"/>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="B43" s="48">
+      <c r="B43" s="54">
         <f>IF(D43="","",37)</f>
         <v/>
       </c>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="49" t="n"/>
-      <c r="E43" s="50" t="n"/>
-      <c r="F43" s="50" t="n"/>
-      <c r="G43" s="51" t="n"/>
-      <c r="H43" s="52">
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="56" t="n"/>
+      <c r="F43" s="56" t="n"/>
+      <c r="G43" s="57" t="n"/>
+      <c r="H43" s="58">
         <f>IF(D43="","",IF(N(G43)&gt;=1,"Completada",IF(AND(N(F43)&gt;0,F43&lt;TODAY()),"Atrasada",IF(AND(N(E43)&gt;0,E43&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I43" s="53">
+      <c r="I43" s="59">
         <f>IF(OR(D43="",N(F43)=0,N(G43)&gt;=1),"",F43-TODAY())</f>
         <v/>
       </c>
-      <c r="J43" s="54" t="n"/>
-      <c r="K43" s="54" t="n"/>
-      <c r="L43" s="54" t="n"/>
-      <c r="M43" s="54" t="n"/>
-      <c r="N43" s="54" t="n"/>
-      <c r="O43" s="54" t="n"/>
-      <c r="P43" s="54" t="n"/>
-      <c r="Q43" s="54" t="n"/>
-      <c r="R43" s="54" t="n"/>
-      <c r="S43" s="54" t="n"/>
-      <c r="T43" s="54" t="n"/>
-      <c r="U43" s="54" t="n"/>
-      <c r="V43" s="54" t="n"/>
-      <c r="W43" s="54" t="n"/>
-      <c r="X43" s="54" t="n"/>
-      <c r="Y43" s="54" t="n"/>
-      <c r="Z43" s="54" t="n"/>
-      <c r="AA43" s="54" t="n"/>
-      <c r="AB43" s="54" t="n"/>
-      <c r="AC43" s="54" t="n"/>
-      <c r="AD43" s="54" t="n"/>
-      <c r="AE43" s="54" t="n"/>
-      <c r="AF43" s="54" t="n"/>
-      <c r="AG43" s="54" t="n"/>
-      <c r="AH43" s="54" t="n"/>
-      <c r="AI43" s="54" t="n"/>
-      <c r="AJ43" s="54" t="n"/>
-      <c r="AK43" s="54" t="n"/>
-      <c r="AL43" s="54" t="n"/>
-      <c r="AM43" s="54" t="n"/>
-      <c r="AN43" s="54" t="n"/>
-      <c r="AO43" s="54" t="n"/>
-      <c r="AP43" s="54" t="n"/>
-      <c r="AQ43" s="54" t="n"/>
-      <c r="AR43" s="54" t="n"/>
-      <c r="AS43" s="54" t="n"/>
-      <c r="AT43" s="54" t="n"/>
-      <c r="AU43" s="54" t="n"/>
-      <c r="AV43" s="54" t="n"/>
-      <c r="AW43" s="54" t="n"/>
-      <c r="AX43" s="54" t="n"/>
-      <c r="AY43" s="54" t="n"/>
-      <c r="AZ43" s="54" t="n"/>
-      <c r="BA43" s="54" t="n"/>
-      <c r="BB43" s="54" t="n"/>
-      <c r="BC43" s="54" t="n"/>
-      <c r="BD43" s="54" t="n"/>
-      <c r="BE43" s="54" t="n"/>
-      <c r="BF43" s="54" t="n"/>
-      <c r="BG43" s="54" t="n"/>
-      <c r="BH43" s="54" t="n"/>
-      <c r="BI43" s="54" t="n"/>
+      <c r="J43" s="60" t="n"/>
+      <c r="K43" s="60" t="n"/>
+      <c r="L43" s="60" t="n"/>
+      <c r="M43" s="60" t="n"/>
+      <c r="N43" s="60" t="n"/>
+      <c r="O43" s="60" t="n"/>
+      <c r="P43" s="60" t="n"/>
+      <c r="Q43" s="60" t="n"/>
+      <c r="R43" s="60" t="n"/>
+      <c r="S43" s="60" t="n"/>
+      <c r="T43" s="60" t="n"/>
+      <c r="U43" s="60" t="n"/>
+      <c r="V43" s="60" t="n"/>
+      <c r="W43" s="60" t="n"/>
+      <c r="X43" s="60" t="n"/>
+      <c r="Y43" s="60" t="n"/>
+      <c r="Z43" s="60" t="n"/>
+      <c r="AA43" s="60" t="n"/>
+      <c r="AB43" s="60" t="n"/>
+      <c r="AC43" s="60" t="n"/>
+      <c r="AD43" s="60" t="n"/>
+      <c r="AE43" s="60" t="n"/>
+      <c r="AF43" s="60" t="n"/>
+      <c r="AG43" s="60" t="n"/>
+      <c r="AH43" s="60" t="n"/>
+      <c r="AI43" s="60" t="n"/>
+      <c r="AJ43" s="60" t="n"/>
+      <c r="AK43" s="60" t="n"/>
+      <c r="AL43" s="60" t="n"/>
+      <c r="AM43" s="60" t="n"/>
+      <c r="AN43" s="60" t="n"/>
+      <c r="AO43" s="60" t="n"/>
+      <c r="AP43" s="60" t="n"/>
+      <c r="AQ43" s="60" t="n"/>
+      <c r="AR43" s="60" t="n"/>
+      <c r="AS43" s="60" t="n"/>
+      <c r="AT43" s="60" t="n"/>
+      <c r="AU43" s="60" t="n"/>
+      <c r="AV43" s="60" t="n"/>
+      <c r="AW43" s="60" t="n"/>
+      <c r="AX43" s="60" t="n"/>
+      <c r="AY43" s="60" t="n"/>
+      <c r="AZ43" s="60" t="n"/>
+      <c r="BA43" s="60" t="n"/>
+      <c r="BB43" s="60" t="n"/>
+      <c r="BC43" s="60" t="n"/>
+      <c r="BD43" s="60" t="n"/>
+      <c r="BE43" s="60" t="n"/>
+      <c r="BF43" s="60" t="n"/>
+      <c r="BG43" s="60" t="n"/>
+      <c r="BH43" s="60" t="n"/>
+      <c r="BI43" s="60" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="B44" s="48">
+      <c r="B44" s="54">
         <f>IF(D44="","",38)</f>
         <v/>
       </c>
-      <c r="C44" s="49" t="n"/>
-      <c r="D44" s="49" t="n"/>
-      <c r="E44" s="50" t="n"/>
-      <c r="F44" s="50" t="n"/>
-      <c r="G44" s="51" t="n"/>
-      <c r="H44" s="52">
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
+      <c r="E44" s="56" t="n"/>
+      <c r="F44" s="56" t="n"/>
+      <c r="G44" s="57" t="n"/>
+      <c r="H44" s="58">
         <f>IF(D44="","",IF(N(G44)&gt;=1,"Completada",IF(AND(N(F44)&gt;0,F44&lt;TODAY()),"Atrasada",IF(AND(N(E44)&gt;0,E44&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I44" s="53">
+      <c r="I44" s="59">
         <f>IF(OR(D44="",N(F44)=0,N(G44)&gt;=1),"",F44-TODAY())</f>
         <v/>
       </c>
-      <c r="J44" s="54" t="n"/>
-      <c r="K44" s="54" t="n"/>
-      <c r="L44" s="54" t="n"/>
-      <c r="M44" s="54" t="n"/>
-      <c r="N44" s="54" t="n"/>
-      <c r="O44" s="54" t="n"/>
-      <c r="P44" s="54" t="n"/>
-      <c r="Q44" s="54" t="n"/>
-      <c r="R44" s="54" t="n"/>
-      <c r="S44" s="54" t="n"/>
-      <c r="T44" s="54" t="n"/>
-      <c r="U44" s="54" t="n"/>
-      <c r="V44" s="54" t="n"/>
-      <c r="W44" s="54" t="n"/>
-      <c r="X44" s="54" t="n"/>
-      <c r="Y44" s="54" t="n"/>
-      <c r="Z44" s="54" t="n"/>
-      <c r="AA44" s="54" t="n"/>
-      <c r="AB44" s="54" t="n"/>
-      <c r="AC44" s="54" t="n"/>
-      <c r="AD44" s="54" t="n"/>
-      <c r="AE44" s="54" t="n"/>
-      <c r="AF44" s="54" t="n"/>
-      <c r="AG44" s="54" t="n"/>
-      <c r="AH44" s="54" t="n"/>
-      <c r="AI44" s="54" t="n"/>
-      <c r="AJ44" s="54" t="n"/>
-      <c r="AK44" s="54" t="n"/>
-      <c r="AL44" s="54" t="n"/>
-      <c r="AM44" s="54" t="n"/>
-      <c r="AN44" s="54" t="n"/>
-      <c r="AO44" s="54" t="n"/>
-      <c r="AP44" s="54" t="n"/>
-      <c r="AQ44" s="54" t="n"/>
-      <c r="AR44" s="54" t="n"/>
-      <c r="AS44" s="54" t="n"/>
-      <c r="AT44" s="54" t="n"/>
-      <c r="AU44" s="54" t="n"/>
-      <c r="AV44" s="54" t="n"/>
-      <c r="AW44" s="54" t="n"/>
-      <c r="AX44" s="54" t="n"/>
-      <c r="AY44" s="54" t="n"/>
-      <c r="AZ44" s="54" t="n"/>
-      <c r="BA44" s="54" t="n"/>
-      <c r="BB44" s="54" t="n"/>
-      <c r="BC44" s="54" t="n"/>
-      <c r="BD44" s="54" t="n"/>
-      <c r="BE44" s="54" t="n"/>
-      <c r="BF44" s="54" t="n"/>
-      <c r="BG44" s="54" t="n"/>
-      <c r="BH44" s="54" t="n"/>
-      <c r="BI44" s="54" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="60" t="n"/>
+      <c r="L44" s="60" t="n"/>
+      <c r="M44" s="60" t="n"/>
+      <c r="N44" s="60" t="n"/>
+      <c r="O44" s="60" t="n"/>
+      <c r="P44" s="60" t="n"/>
+      <c r="Q44" s="60" t="n"/>
+      <c r="R44" s="60" t="n"/>
+      <c r="S44" s="60" t="n"/>
+      <c r="T44" s="60" t="n"/>
+      <c r="U44" s="60" t="n"/>
+      <c r="V44" s="60" t="n"/>
+      <c r="W44" s="60" t="n"/>
+      <c r="X44" s="60" t="n"/>
+      <c r="Y44" s="60" t="n"/>
+      <c r="Z44" s="60" t="n"/>
+      <c r="AA44" s="60" t="n"/>
+      <c r="AB44" s="60" t="n"/>
+      <c r="AC44" s="60" t="n"/>
+      <c r="AD44" s="60" t="n"/>
+      <c r="AE44" s="60" t="n"/>
+      <c r="AF44" s="60" t="n"/>
+      <c r="AG44" s="60" t="n"/>
+      <c r="AH44" s="60" t="n"/>
+      <c r="AI44" s="60" t="n"/>
+      <c r="AJ44" s="60" t="n"/>
+      <c r="AK44" s="60" t="n"/>
+      <c r="AL44" s="60" t="n"/>
+      <c r="AM44" s="60" t="n"/>
+      <c r="AN44" s="60" t="n"/>
+      <c r="AO44" s="60" t="n"/>
+      <c r="AP44" s="60" t="n"/>
+      <c r="AQ44" s="60" t="n"/>
+      <c r="AR44" s="60" t="n"/>
+      <c r="AS44" s="60" t="n"/>
+      <c r="AT44" s="60" t="n"/>
+      <c r="AU44" s="60" t="n"/>
+      <c r="AV44" s="60" t="n"/>
+      <c r="AW44" s="60" t="n"/>
+      <c r="AX44" s="60" t="n"/>
+      <c r="AY44" s="60" t="n"/>
+      <c r="AZ44" s="60" t="n"/>
+      <c r="BA44" s="60" t="n"/>
+      <c r="BB44" s="60" t="n"/>
+      <c r="BC44" s="60" t="n"/>
+      <c r="BD44" s="60" t="n"/>
+      <c r="BE44" s="60" t="n"/>
+      <c r="BF44" s="60" t="n"/>
+      <c r="BG44" s="60" t="n"/>
+      <c r="BH44" s="60" t="n"/>
+      <c r="BI44" s="60" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="B45" s="48">
+      <c r="B45" s="54">
         <f>IF(D45="","",39)</f>
         <v/>
       </c>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
-      <c r="E45" s="50" t="n"/>
-      <c r="F45" s="50" t="n"/>
-      <c r="G45" s="51" t="n"/>
-      <c r="H45" s="52">
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="55" t="n"/>
+      <c r="E45" s="56" t="n"/>
+      <c r="F45" s="56" t="n"/>
+      <c r="G45" s="57" t="n"/>
+      <c r="H45" s="58">
         <f>IF(D45="","",IF(N(G45)&gt;=1,"Completada",IF(AND(N(F45)&gt;0,F45&lt;TODAY()),"Atrasada",IF(AND(N(E45)&gt;0,E45&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I45" s="53">
+      <c r="I45" s="59">
         <f>IF(OR(D45="",N(F45)=0,N(G45)&gt;=1),"",F45-TODAY())</f>
         <v/>
       </c>
-      <c r="J45" s="54" t="n"/>
-      <c r="K45" s="54" t="n"/>
-      <c r="L45" s="54" t="n"/>
-      <c r="M45" s="54" t="n"/>
-      <c r="N45" s="54" t="n"/>
-      <c r="O45" s="54" t="n"/>
-      <c r="P45" s="54" t="n"/>
-      <c r="Q45" s="54" t="n"/>
-      <c r="R45" s="54" t="n"/>
-      <c r="S45" s="54" t="n"/>
-      <c r="T45" s="54" t="n"/>
-      <c r="U45" s="54" t="n"/>
-      <c r="V45" s="54" t="n"/>
-      <c r="W45" s="54" t="n"/>
-      <c r="X45" s="54" t="n"/>
-      <c r="Y45" s="54" t="n"/>
-      <c r="Z45" s="54" t="n"/>
-      <c r="AA45" s="54" t="n"/>
-      <c r="AB45" s="54" t="n"/>
-      <c r="AC45" s="54" t="n"/>
-      <c r="AD45" s="54" t="n"/>
-      <c r="AE45" s="54" t="n"/>
-      <c r="AF45" s="54" t="n"/>
-      <c r="AG45" s="54" t="n"/>
-      <c r="AH45" s="54" t="n"/>
-      <c r="AI45" s="54" t="n"/>
-      <c r="AJ45" s="54" t="n"/>
-      <c r="AK45" s="54" t="n"/>
-      <c r="AL45" s="54" t="n"/>
-      <c r="AM45" s="54" t="n"/>
-      <c r="AN45" s="54" t="n"/>
-      <c r="AO45" s="54" t="n"/>
-      <c r="AP45" s="54" t="n"/>
-      <c r="AQ45" s="54" t="n"/>
-      <c r="AR45" s="54" t="n"/>
-      <c r="AS45" s="54" t="n"/>
-      <c r="AT45" s="54" t="n"/>
-      <c r="AU45" s="54" t="n"/>
-      <c r="AV45" s="54" t="n"/>
-      <c r="AW45" s="54" t="n"/>
-      <c r="AX45" s="54" t="n"/>
-      <c r="AY45" s="54" t="n"/>
-      <c r="AZ45" s="54" t="n"/>
-      <c r="BA45" s="54" t="n"/>
-      <c r="BB45" s="54" t="n"/>
-      <c r="BC45" s="54" t="n"/>
-      <c r="BD45" s="54" t="n"/>
-      <c r="BE45" s="54" t="n"/>
-      <c r="BF45" s="54" t="n"/>
-      <c r="BG45" s="54" t="n"/>
-      <c r="BH45" s="54" t="n"/>
-      <c r="BI45" s="54" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="60" t="n"/>
+      <c r="L45" s="60" t="n"/>
+      <c r="M45" s="60" t="n"/>
+      <c r="N45" s="60" t="n"/>
+      <c r="O45" s="60" t="n"/>
+      <c r="P45" s="60" t="n"/>
+      <c r="Q45" s="60" t="n"/>
+      <c r="R45" s="60" t="n"/>
+      <c r="S45" s="60" t="n"/>
+      <c r="T45" s="60" t="n"/>
+      <c r="U45" s="60" t="n"/>
+      <c r="V45" s="60" t="n"/>
+      <c r="W45" s="60" t="n"/>
+      <c r="X45" s="60" t="n"/>
+      <c r="Y45" s="60" t="n"/>
+      <c r="Z45" s="60" t="n"/>
+      <c r="AA45" s="60" t="n"/>
+      <c r="AB45" s="60" t="n"/>
+      <c r="AC45" s="60" t="n"/>
+      <c r="AD45" s="60" t="n"/>
+      <c r="AE45" s="60" t="n"/>
+      <c r="AF45" s="60" t="n"/>
+      <c r="AG45" s="60" t="n"/>
+      <c r="AH45" s="60" t="n"/>
+      <c r="AI45" s="60" t="n"/>
+      <c r="AJ45" s="60" t="n"/>
+      <c r="AK45" s="60" t="n"/>
+      <c r="AL45" s="60" t="n"/>
+      <c r="AM45" s="60" t="n"/>
+      <c r="AN45" s="60" t="n"/>
+      <c r="AO45" s="60" t="n"/>
+      <c r="AP45" s="60" t="n"/>
+      <c r="AQ45" s="60" t="n"/>
+      <c r="AR45" s="60" t="n"/>
+      <c r="AS45" s="60" t="n"/>
+      <c r="AT45" s="60" t="n"/>
+      <c r="AU45" s="60" t="n"/>
+      <c r="AV45" s="60" t="n"/>
+      <c r="AW45" s="60" t="n"/>
+      <c r="AX45" s="60" t="n"/>
+      <c r="AY45" s="60" t="n"/>
+      <c r="AZ45" s="60" t="n"/>
+      <c r="BA45" s="60" t="n"/>
+      <c r="BB45" s="60" t="n"/>
+      <c r="BC45" s="60" t="n"/>
+      <c r="BD45" s="60" t="n"/>
+      <c r="BE45" s="60" t="n"/>
+      <c r="BF45" s="60" t="n"/>
+      <c r="BG45" s="60" t="n"/>
+      <c r="BH45" s="60" t="n"/>
+      <c r="BI45" s="60" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="B46" s="48">
+      <c r="B46" s="54">
         <f>IF(D46="","",40)</f>
         <v/>
       </c>
-      <c r="C46" s="49" t="n"/>
-      <c r="D46" s="49" t="n"/>
-      <c r="E46" s="50" t="n"/>
-      <c r="F46" s="50" t="n"/>
-      <c r="G46" s="51" t="n"/>
-      <c r="H46" s="52">
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="55" t="n"/>
+      <c r="E46" s="56" t="n"/>
+      <c r="F46" s="56" t="n"/>
+      <c r="G46" s="57" t="n"/>
+      <c r="H46" s="58">
         <f>IF(D46="","",IF(N(G46)&gt;=1,"Completada",IF(AND(N(F46)&gt;0,F46&lt;TODAY()),"Atrasada",IF(AND(N(E46)&gt;0,E46&lt;=TODAY()),"En curso","Por empezar"))))</f>
         <v/>
       </c>
-      <c r="I46" s="53">
+      <c r="I46" s="59">
         <f>IF(OR(D46="",N(F46)=0,N(G46)&gt;=1),"",F46-TODAY())</f>
         <v/>
       </c>
-      <c r="J46" s="54" t="n"/>
-      <c r="K46" s="54" t="n"/>
-      <c r="L46" s="54" t="n"/>
-      <c r="M46" s="54" t="n"/>
-      <c r="N46" s="54" t="n"/>
-      <c r="O46" s="54" t="n"/>
-      <c r="P46" s="54" t="n"/>
-      <c r="Q46" s="54" t="n"/>
-      <c r="R46" s="54" t="n"/>
-      <c r="S46" s="54" t="n"/>
-      <c r="T46" s="54" t="n"/>
-      <c r="U46" s="54" t="n"/>
-      <c r="V46" s="54" t="n"/>
-      <c r="W46" s="54" t="n"/>
-      <c r="X46" s="54" t="n"/>
-      <c r="Y46" s="54" t="n"/>
-      <c r="Z46" s="54" t="n"/>
-      <c r="AA46" s="54" t="n"/>
-      <c r="AB46" s="54" t="n"/>
-      <c r="AC46" s="54" t="n"/>
-      <c r="AD46" s="54" t="n"/>
-      <c r="AE46" s="54" t="n"/>
-      <c r="AF46" s="54" t="n"/>
-      <c r="AG46" s="54" t="n"/>
-      <c r="AH46" s="54" t="n"/>
-      <c r="AI46" s="54" t="n"/>
-      <c r="AJ46" s="54" t="n"/>
-      <c r="AK46" s="54" t="n"/>
-      <c r="AL46" s="54" t="n"/>
-      <c r="AM46" s="54" t="n"/>
-      <c r="AN46" s="54" t="n"/>
-      <c r="AO46" s="54" t="n"/>
-      <c r="AP46" s="54" t="n"/>
-      <c r="AQ46" s="54" t="n"/>
-      <c r="AR46" s="54" t="n"/>
-      <c r="AS46" s="54" t="n"/>
-      <c r="AT46" s="54" t="n"/>
-      <c r="AU46" s="54" t="n"/>
-      <c r="AV46" s="54" t="n"/>
-      <c r="AW46" s="54" t="n"/>
-      <c r="AX46" s="54" t="n"/>
-      <c r="AY46" s="54" t="n"/>
-      <c r="AZ46" s="54" t="n"/>
-      <c r="BA46" s="54" t="n"/>
-      <c r="BB46" s="54" t="n"/>
-      <c r="BC46" s="54" t="n"/>
-      <c r="BD46" s="54" t="n"/>
-      <c r="BE46" s="54" t="n"/>
-      <c r="BF46" s="54" t="n"/>
-      <c r="BG46" s="54" t="n"/>
-      <c r="BH46" s="54" t="n"/>
-      <c r="BI46" s="54" t="n"/>
+      <c r="J46" s="60" t="n"/>
+      <c r="K46" s="60" t="n"/>
+      <c r="L46" s="60" t="n"/>
+      <c r="M46" s="60" t="n"/>
+      <c r="N46" s="60" t="n"/>
+      <c r="O46" s="60" t="n"/>
+      <c r="P46" s="60" t="n"/>
+      <c r="Q46" s="60" t="n"/>
+      <c r="R46" s="60" t="n"/>
+      <c r="S46" s="60" t="n"/>
+      <c r="T46" s="60" t="n"/>
+      <c r="U46" s="60" t="n"/>
+      <c r="V46" s="60" t="n"/>
+      <c r="W46" s="60" t="n"/>
+      <c r="X46" s="60" t="n"/>
+      <c r="Y46" s="60" t="n"/>
+      <c r="Z46" s="60" t="n"/>
+      <c r="AA46" s="60" t="n"/>
+      <c r="AB46" s="60" t="n"/>
+      <c r="AC46" s="60" t="n"/>
+      <c r="AD46" s="60" t="n"/>
+      <c r="AE46" s="60" t="n"/>
+      <c r="AF46" s="60" t="n"/>
+      <c r="AG46" s="60" t="n"/>
+      <c r="AH46" s="60" t="n"/>
+      <c r="AI46" s="60" t="n"/>
+      <c r="AJ46" s="60" t="n"/>
+      <c r="AK46" s="60" t="n"/>
+      <c r="AL46" s="60" t="n"/>
+      <c r="AM46" s="60" t="n"/>
+      <c r="AN46" s="60" t="n"/>
+      <c r="AO46" s="60" t="n"/>
+      <c r="AP46" s="60" t="n"/>
+      <c r="AQ46" s="60" t="n"/>
+      <c r="AR46" s="60" t="n"/>
+      <c r="AS46" s="60" t="n"/>
+      <c r="AT46" s="60" t="n"/>
+      <c r="AU46" s="60" t="n"/>
+      <c r="AV46" s="60" t="n"/>
+      <c r="AW46" s="60" t="n"/>
+      <c r="AX46" s="60" t="n"/>
+      <c r="AY46" s="60" t="n"/>
+      <c r="AZ46" s="60" t="n"/>
+      <c r="BA46" s="60" t="n"/>
+      <c r="BB46" s="60" t="n"/>
+      <c r="BC46" s="60" t="n"/>
+      <c r="BD46" s="60" t="n"/>
+      <c r="BE46" s="60" t="n"/>
+      <c r="BF46" s="60" t="n"/>
+      <c r="BG46" s="60" t="n"/>
+      <c r="BH46" s="60" t="n"/>
+      <c r="BI46" s="60" t="n"/>
     </row>
     <row r="48" ht="8" customHeight="1">
-      <c r="B48" s="42" t="n"/>
+      <c r="B48" s="48" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="B49" s="43" t="inlineStr">
+      <c r="B49" s="49" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="B50" s="44" t="inlineStr">
+      <c r="B50" s="50" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY  →  mixshopdigital.com.py</t>
         </is>
@@ -5359,8 +5593,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="B962"/>
-  <mergeCells count="10">
-    <mergeCell ref="B3:T3"/>
+  <mergeCells count="9">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B50:T50"/>
     <mergeCell ref="C5:D5"/>
@@ -5443,6 +5676,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5462,436 +5696,437 @@
     <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>REUNIONES</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Lo que hablás con tu tutor</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Anotá cada reunión, también las que ya agendaste para más adelante. El PANEL te muestra la última y la próxima.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Tema tratado</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Acuerdos y tareas pendientes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="56" t="n">
         <v>46183</v>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Elección del tema</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>Delimitar el problema y entregar el anteproyecto.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="56" t="n">
         <v>46211</v>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
         <is>
           <t>Anteproyecto</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>Ajustar los objetivos. Buscar 15 antecedentes.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="56" t="n">
         <v>46246</v>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>Antecedentes</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>Ordenar las fuentes por tema.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="56" t="n">
         <v>46281</v>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
         <is>
           <t>Marco teórico</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>Corregir citas y completar el capítulo 2.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="50" t="n">
+      <c r="B11" s="56" t="n">
         <v>46309</v>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>Encuesta</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="55" t="inlineStr">
         <is>
           <t>Validar la encuesta antes de aplicarla.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="50" t="n">
+      <c r="B12" s="56" t="n">
         <v>46337</v>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>Avance del trabajo de campo</t>
         </is>
       </c>
-      <c r="D12" s="49" t="n"/>
+      <c r="D12" s="55" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="56" t="n">
         <v>46365</v>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>Primeros resultados</t>
         </is>
       </c>
-      <c r="D13" s="49" t="n"/>
+      <c r="D13" s="55" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
+      <c r="B14" s="56" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
+      <c r="B15" s="56" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="50" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
+      <c r="B16" s="56" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="50" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
+      <c r="B17" s="56" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="50" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
+      <c r="B18" s="56" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
+      <c r="B19" s="56" t="n"/>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
+      <c r="B20" s="56" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="49" t="n"/>
-      <c r="D21" s="49" t="n"/>
+      <c r="B21" s="56" t="n"/>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
+      <c r="B22" s="56" t="n"/>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="50" t="n"/>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
+      <c r="B23" s="56" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="49" t="n"/>
-      <c r="D24" s="49" t="n"/>
+      <c r="B24" s="56" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="49" t="n"/>
-      <c r="D25" s="49" t="n"/>
+      <c r="B25" s="56" t="n"/>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="49" t="n"/>
-      <c r="D26" s="49" t="n"/>
+      <c r="B26" s="56" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="49" t="n"/>
-      <c r="D27" s="49" t="n"/>
+      <c r="B27" s="56" t="n"/>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="50" t="n"/>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="49" t="n"/>
+      <c r="B28" s="56" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="50" t="n"/>
-      <c r="C29" s="49" t="n"/>
-      <c r="D29" s="49" t="n"/>
+      <c r="B29" s="56" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="50" t="n"/>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="49" t="n"/>
+      <c r="B30" s="56" t="n"/>
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="55" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="49" t="n"/>
+      <c r="B31" s="56" t="n"/>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="55" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="49" t="n"/>
+      <c r="B32" s="56" t="n"/>
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="55" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
+      <c r="B33" s="56" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
+      <c r="B34" s="56" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
+      <c r="B35" s="56" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
+      <c r="B36" s="56" t="n"/>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
+      <c r="B40" s="56" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
+      <c r="B41" s="56" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
+      <c r="B42" s="56" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="50" t="n"/>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="49" t="n"/>
+      <c r="B43" s="56" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="50" t="n"/>
-      <c r="C44" s="49" t="n"/>
-      <c r="D44" s="49" t="n"/>
+      <c r="B44" s="56" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="50" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
+      <c r="B45" s="56" t="n"/>
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="55" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="50" t="n"/>
-      <c r="C46" s="49" t="n"/>
-      <c r="D46" s="49" t="n"/>
+      <c r="B46" s="56" t="n"/>
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="55" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="50" t="n"/>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
+      <c r="B47" s="56" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="55" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="50" t="n"/>
-      <c r="C48" s="49" t="n"/>
-      <c r="D48" s="49" t="n"/>
+      <c r="B48" s="56" t="n"/>
+      <c r="C48" s="55" t="n"/>
+      <c r="D48" s="55" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="50" t="n"/>
-      <c r="C49" s="49" t="n"/>
-      <c r="D49" s="49" t="n"/>
+      <c r="B49" s="56" t="n"/>
+      <c r="C49" s="55" t="n"/>
+      <c r="D49" s="55" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="50" t="n"/>
-      <c r="C50" s="49" t="n"/>
-      <c r="D50" s="49" t="n"/>
+      <c r="B50" s="56" t="n"/>
+      <c r="C50" s="55" t="n"/>
+      <c r="D50" s="55" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="50" t="n"/>
-      <c r="C51" s="49" t="n"/>
-      <c r="D51" s="49" t="n"/>
+      <c r="B51" s="56" t="n"/>
+      <c r="C51" s="55" t="n"/>
+      <c r="D51" s="55" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="50" t="n"/>
-      <c r="C52" s="49" t="n"/>
-      <c r="D52" s="49" t="n"/>
+      <c r="B52" s="56" t="n"/>
+      <c r="C52" s="55" t="n"/>
+      <c r="D52" s="55" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="50" t="n"/>
-      <c r="C53" s="49" t="n"/>
-      <c r="D53" s="49" t="n"/>
+      <c r="B53" s="56" t="n"/>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="55" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="50" t="n"/>
-      <c r="C54" s="49" t="n"/>
-      <c r="D54" s="49" t="n"/>
+      <c r="B54" s="56" t="n"/>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="55" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="50" t="n"/>
-      <c r="C55" s="49" t="n"/>
-      <c r="D55" s="49" t="n"/>
+      <c r="B55" s="56" t="n"/>
+      <c r="C55" s="55" t="n"/>
+      <c r="D55" s="55" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="50" t="n"/>
-      <c r="C56" s="49" t="n"/>
-      <c r="D56" s="49" t="n"/>
+      <c r="B56" s="56" t="n"/>
+      <c r="C56" s="55" t="n"/>
+      <c r="D56" s="55" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="50" t="n"/>
-      <c r="C57" s="49" t="n"/>
-      <c r="D57" s="49" t="n"/>
+      <c r="B57" s="56" t="n"/>
+      <c r="C57" s="55" t="n"/>
+      <c r="D57" s="55" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="50" t="n"/>
-      <c r="C58" s="49" t="n"/>
-      <c r="D58" s="49" t="n"/>
+      <c r="B58" s="56" t="n"/>
+      <c r="C58" s="55" t="n"/>
+      <c r="D58" s="55" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="50" t="n"/>
-      <c r="C59" s="49" t="n"/>
-      <c r="D59" s="49" t="n"/>
+      <c r="B59" s="56" t="n"/>
+      <c r="C59" s="55" t="n"/>
+      <c r="D59" s="55" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="50" t="n"/>
-      <c r="C60" s="49" t="n"/>
-      <c r="D60" s="49" t="n"/>
+      <c r="B60" s="56" t="n"/>
+      <c r="C60" s="55" t="n"/>
+      <c r="D60" s="55" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="50" t="n"/>
-      <c r="C61" s="49" t="n"/>
-      <c r="D61" s="49" t="n"/>
+      <c r="B61" s="56" t="n"/>
+      <c r="C61" s="55" t="n"/>
+      <c r="D61" s="55" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="50" t="n"/>
-      <c r="C62" s="49" t="n"/>
-      <c r="D62" s="49" t="n"/>
+      <c r="B62" s="56" t="n"/>
+      <c r="C62" s="55" t="n"/>
+      <c r="D62" s="55" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="50" t="n"/>
-      <c r="C63" s="49" t="n"/>
-      <c r="D63" s="49" t="n"/>
+      <c r="B63" s="56" t="n"/>
+      <c r="C63" s="55" t="n"/>
+      <c r="D63" s="55" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="50" t="n"/>
-      <c r="C64" s="49" t="n"/>
-      <c r="D64" s="49" t="n"/>
+      <c r="B64" s="56" t="n"/>
+      <c r="C64" s="55" t="n"/>
+      <c r="D64" s="55" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="50" t="n"/>
-      <c r="C65" s="49" t="n"/>
-      <c r="D65" s="49" t="n"/>
+      <c r="B65" s="56" t="n"/>
+      <c r="C65" s="55" t="n"/>
+      <c r="D65" s="55" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="50" t="n"/>
-      <c r="C66" s="49" t="n"/>
-      <c r="D66" s="49" t="n"/>
+      <c r="B66" s="56" t="n"/>
+      <c r="C66" s="55" t="n"/>
+      <c r="D66" s="55" t="n"/>
     </row>
     <row r="68" ht="8" customHeight="1">
-      <c r="B68" s="42" t="n"/>
+      <c r="B68" s="48" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="B69" s="43" t="inlineStr">
+      <c r="B69" s="49" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="B70" s="44" t="inlineStr">
+      <c r="B70" s="50" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY  →  mixshopdigital.com.py</t>
         </is>
@@ -5899,14 +6134,13 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B962"/>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="B70:E70"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:D66">
     <cfRule type="expression" priority="1" dxfId="7">
@@ -5934,6 +6168,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5953,227 +6188,226 @@
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>AJUSTES</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Cargalos una sola vez</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="10" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Completá solamente las celdas amarillas. Estos datos alimentan las demás hojas automáticamente.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>1. TU TESIS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>Título del trabajo</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>Lectura y rendimiento escolar (EJEMPLO)</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>Aparece en el PANEL.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>Opcional.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>Tutor</t>
         </is>
       </c>
-      <c r="C9" s="56" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>Prof. Ramírez</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>Opcional.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Fecha de inicio</t>
         </is>
       </c>
-      <c r="C10" s="58" t="n">
+      <c r="C10" s="64" t="n">
         <v>46174</v>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>El día en que empezaste (o vas a empezar). El diagrama arranca esa semana.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>Fecha de entrega o defensa</t>
         </is>
       </c>
-      <c r="C11" s="58" t="n">
+      <c r="C11" s="64" t="n">
         <v>46507</v>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>Tu fecha límite. El PANEL cuenta los días que faltan.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>2. ETAPAS DE TU TESIS (podés renombrarlas)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Se usan en la lista desplegable de CRONOGRAMA. Cambiá el nombre, pero no dejes huecos entre medio.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>Tema y proyecto</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Hasta 9 etapas.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="56" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Marco teórico</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>Metodología</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t>Trabajo de campo</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>Análisis de datos</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>Redacción</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>Revisión del tutor</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="56" t="inlineStr">
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t>Formato y entrega</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>Defensa</t>
         </is>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="B26" s="42" t="n"/>
+      <c r="B26" s="48" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="50" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY  →  mixshopdigital.com.py</t>
         </is>
@@ -6181,9 +6415,8 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="B962"/>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B3:D3"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="B26:D26"/>
@@ -6213,6 +6446,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6236,197 +6470,204 @@
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>AYUDA</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Se aprende en 2 minutos</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Leé esta hoja una vez. Después ya no la vas a necesitar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>¿PARA QUÉ SIRVE?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>Para planificar tu tesis de principio a fin, ver semana a semana qué te toca hacer y saber si vas a llegar a tu fecha de entrega. Sin fórmulas y sin Internet.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>EMPEZÁ EN 3 PASOS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1">
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>1) En AJUSTES poné el título de tu tesis, tu fecha de inicio y tu fecha de entrega o defensa. Si querés, renombrá las etapas.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>2) En CRONOGRAMA anotá cada tarea: etapa, descripción, fecha de inicio, fecha de fin y cuánto avanzaste. El diagrama de barras se dibuja solo.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1">
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>3) Mirá el PANEL: avance general, días que faltan, tareas atrasadas y un aviso que te dice cómo vas. Anotá tus reuniones con el tutor en REUNIONES.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>COLORES DEL DIAGRAMA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1">
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>Azul: tarea en marcha o por empezar.   Verde: tarea completada.   Coral: tarea atrasada.   Columna dorada: la semana de hoy.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>PREGUNTAS FRECUENTES</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18.5" customHeight="1">
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>• Veo todo en cero: hacé clic en «Habilitar edición» en la barra amarilla de Excel.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18.5" customHeight="1">
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>• ¿Cómo completo una tarea? Poné 100 % en la columna Avance.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>• ¿Por qué una tarea figura como atrasada? Porque pasó su fecha de fin y todavía no está al 100 %. Corregí el avance o movela de fecha.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33" customHeight="1">
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>• ¿Por qué no veo la barra de una tarea? Revisá que tenga fecha de inicio y de fin, y que estén dentro de las 52 semanas desde tu fecha de inicio.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18.5" customHeight="1">
-      <c r="B22" s="59" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>• ¿Cuántas tareas entran? 40 tareas y 60 reuniones. Cuando se llene, duplicá el archivo.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33" customHeight="1">
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>• Solo se editan las celdas amarillas: el resto está protegido para que no se rompan las fórmulas por accidente.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>SOBRE LA PROTECCIÓN</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18.5" customHeight="1">
-      <c r="B26" s="59" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>La protección de Excel evita borrados accidentales, pero no es un sistema de seguridad criptográfico.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL Y TESIS PRO PY</t>
         </is>
       </c>
     </row>
     <row r="29" ht="47.5" customHeight="1">
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>Esta planilla es una herramienta gratuita de Mix Shop Digital. Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY, la herramienta para seguir el avance de todos tus tesistas en un solo lugar.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="67" t="inlineStr">
         <is>
           <t>→ mixshopdigital.com.py</t>
         </is>
       </c>
     </row>
     <row r="32" ht="8" customHeight="1">
-      <c r="B32" s="42" t="n"/>
+      <c r="B32" s="48" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Si sos tutor de tesis y acompañás a varios estudiantes, conocé TESIS PRO PY  →  mixshopdigital.com.py</t>
         </is>
@@ -6434,7 +6675,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="B962"/>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="B6:H6"/>
@@ -6449,7 +6690,6 @@
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
@@ -6481,5 +6721,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>